--- a/physical_location_labelling/physical_location_by_context/results/v02_manual_annotation/kohasonad_margendus.xlsx
+++ b/physical_location_labelling/physical_location_by_context/results/v02_manual_annotation/kohasonad_margendus.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28528"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eestikeeleinstituut-my.sharepoint.com/personal/kertu_saul_eki_ee/Documents/Dokumendid/doktoritoo/estnltk_syntax_repo_kloon/physical_location_labelling/results/testmaterjal/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eestikeeleinstituut-my.sharepoint.com/personal/kertu_saul_eki_ee/Documents/Dokumendid/doktoritoo/estnltk_syntax_repo_kloon/physical_location_labelling/physical_location_by_context/results/v02_manual_annotation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="65" documentId="6_{96325085-7035-41B9-BB6E-38A7F2056715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F66B3396-6D8B-4D0C-BB59-5C06EA2A5A24}"/>
+  <xr:revisionPtr revIDLastSave="78" documentId="6_{96325085-7035-41B9-BB6E-38A7F2056715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97BFBD6C-6CC1-4666-A1F1-A84F0AE5E284}"/>
   <bookViews>
-    <workbookView xWindow="1954" yWindow="146" windowWidth="17452" windowHeight="11545" xr2:uid="{01384FF5-142F-4704-AF05-EBE9DDF051EF}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11949" xr2:uid="{01384FF5-142F-4704-AF05-EBE9DDF051EF}"/>
   </bookViews>
   <sheets>
     <sheet name="kohasonad_margendus" sheetId="10" r:id="rId1"/>
@@ -12032,7 +12032,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -12534,48 +12534,48 @@
     </xf>
   </cellXfs>
   <cellStyles count="42">
-    <cellStyle name="20% – rõhk1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% – rõhk2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% – rõhk3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% – rõhk4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% – rõhk5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% – rõhk6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% – rõhk1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% – rõhk2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% – rõhk3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% – rõhk4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% – rõhk5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% – rõhk6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% – rõhk1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% – rõhk2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% – rõhk3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% – rõhk4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% – rõhk5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% – rõhk6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Arvutus" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Halb" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Hea" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Hoiatuse tekst" xfId="14" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="Kokku" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Kontrolli lahtrit" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Lingitud lahter" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Märkus" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Neutraalne" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="Normaallaad" xfId="0" builtinId="0"/>
-    <cellStyle name="Pealkiri 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Pealkiri 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Pealkiri 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Pealkiri 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Rõhk1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Rõhk2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Rõhk3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Rõhk4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Rõhk5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Rõhk6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Selgitav tekst" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Sisend" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Väljund" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Üldpealkiri" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -12597,9 +12597,19 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{D89AEE72-3D45-418F-A280-BD318B20165F}" name="Table9" displayName="Table9" ref="A1:F1048576" totalsRowShown="0">
-  <autoFilter ref="A1:F1048576" xr:uid="{D89AEE72-3D45-418F-A280-BD318B20165F}"/>
+  <autoFilter ref="A1:F1048576" xr:uid="{D89AEE72-3D45-418F-A280-BD318B20165F}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="event"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{D4E5CA33-BFA0-4952-9DA8-670923E0026B}" name="lemma"/>
     <tableColumn id="2" xr3:uid="{A41228A5-4A05-4045-A620-76EF56282A21}" name="form"/>
@@ -12930,16 +12940,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEBDE73A-9B9F-4192-A2EC-3F733C111886}">
   <dimension ref="A1:F1001"/>
-  <sheetFormatPr defaultRowHeight="14.65"/>
+  <sheetFormatPr defaultRowHeight="14.6" zeroHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="2" width="18.85546875" customWidth="1"/>
-    <col min="3" max="3" width="32.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.85546875" customWidth="1"/>
-    <col min="5" max="5" width="64.42578125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18.85546875" customWidth="1"/>
+    <col min="1" max="2" width="18.84375" customWidth="1"/>
+    <col min="3" max="3" width="32.15234375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.84375" customWidth="1"/>
+    <col min="5" max="5" width="64.3828125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18.84375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -12959,7 +12969,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="29.1">
+    <row r="2" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -12979,7 +12989,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -12999,7 +13009,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="29.1">
+    <row r="4" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -13019,7 +13029,7 @@
         <v>2886</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="29.1">
+    <row r="5" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -13039,7 +13049,7 @@
         <v>2898</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="29.1">
+    <row r="6" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -13059,7 +13069,7 @@
         <v>3305</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="29.1">
+    <row r="7" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -13079,7 +13089,7 @@
         <v>3752</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="43.7">
+    <row r="8" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>34</v>
       </c>
@@ -13099,7 +13109,7 @@
         <v>5695</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="43.7">
+    <row r="9" spans="1:6" ht="43.75" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>39</v>
       </c>
@@ -13119,7 +13129,7 @@
         <v>5695</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="29.1">
+    <row r="10" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>42</v>
       </c>
@@ -13139,7 +13149,7 @@
         <v>6520</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="29.1">
+    <row r="11" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>46</v>
       </c>
@@ -13159,7 +13169,7 @@
         <v>7872</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="29.1">
+    <row r="12" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>50</v>
       </c>
@@ -13179,7 +13189,7 @@
         <v>8798</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="29.1">
+    <row r="13" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>54</v>
       </c>
@@ -13199,7 +13209,7 @@
         <v>11874</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="29.1">
+    <row r="14" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>58</v>
       </c>
@@ -13219,7 +13229,7 @@
         <v>15259</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="29.1">
+    <row r="15" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>62</v>
       </c>
@@ -13239,7 +13249,7 @@
         <v>16511</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="29.1">
+    <row r="16" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>66</v>
       </c>
@@ -13259,7 +13269,7 @@
         <v>17128</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="43.7">
+    <row r="17" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>70</v>
       </c>
@@ -13279,7 +13289,7 @@
         <v>19785</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>74</v>
       </c>
@@ -13299,7 +13309,7 @@
         <v>21315</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>78</v>
       </c>
@@ -13319,7 +13329,7 @@
         <v>23000</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>82</v>
       </c>
@@ -13339,7 +13349,7 @@
         <v>27200</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>86</v>
       </c>
@@ -13359,7 +13369,7 @@
         <v>29795</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="29.1">
+    <row r="22" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>90</v>
       </c>
@@ -13379,7 +13389,7 @@
         <v>30567</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="43.7">
+    <row r="23" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
         <v>94</v>
       </c>
@@ -13399,7 +13409,7 @@
         <v>32958</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="29.1">
+    <row r="24" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
         <v>99</v>
       </c>
@@ -13419,7 +13429,7 @@
         <v>33090</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="29.1">
+    <row r="25" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
         <v>103</v>
       </c>
@@ -13439,7 +13449,7 @@
         <v>35094</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
         <v>107</v>
       </c>
@@ -13459,7 +13469,7 @@
         <v>37886</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
         <v>111</v>
       </c>
@@ -13479,7 +13489,7 @@
         <v>41437</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="29.1">
+    <row r="28" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
         <v>116</v>
       </c>
@@ -13499,7 +13509,7 @@
         <v>43916</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
         <v>120</v>
       </c>
@@ -13519,7 +13529,7 @@
         <v>47141</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
         <v>124</v>
       </c>
@@ -13539,7 +13549,7 @@
         <v>47808</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="29.1">
+    <row r="31" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
         <v>128</v>
       </c>
@@ -13559,7 +13569,7 @@
         <v>49878</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
         <v>132</v>
       </c>
@@ -13579,7 +13589,7 @@
         <v>50376</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
         <v>136</v>
       </c>
@@ -13599,7 +13609,7 @@
         <v>50839</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="29.1">
+    <row r="34" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
         <v>140</v>
       </c>
@@ -13619,7 +13629,7 @@
         <v>54296</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="29.1">
+    <row r="35" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
         <v>144</v>
       </c>
@@ -13639,7 +13649,7 @@
         <v>55053</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
         <v>148</v>
       </c>
@@ -13659,7 +13669,7 @@
         <v>56670</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="43.7">
+    <row r="37" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
         <v>152</v>
       </c>
@@ -13679,7 +13689,7 @@
         <v>57337</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="29.1">
+    <row r="38" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
         <v>156</v>
       </c>
@@ -13699,7 +13709,7 @@
         <v>60401</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="29.1">
+    <row r="39" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
         <v>160</v>
       </c>
@@ -13719,7 +13729,7 @@
         <v>71170</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="29.1">
+    <row r="40" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
         <v>164</v>
       </c>
@@ -13739,7 +13749,7 @@
         <v>71637</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="29.1">
+    <row r="41" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
         <v>169</v>
       </c>
@@ -13759,7 +13769,7 @@
         <v>78001</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
         <v>173</v>
       </c>
@@ -13779,7 +13789,7 @@
         <v>81699</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
         <v>177</v>
       </c>
@@ -13799,7 +13809,7 @@
         <v>88332</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="29.1">
+    <row r="44" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
         <v>181</v>
       </c>
@@ -13819,7 +13829,7 @@
         <v>89531</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="43.7">
+    <row r="45" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
         <v>185</v>
       </c>
@@ -13839,7 +13849,7 @@
         <v>97110</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="29.1">
+    <row r="46" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
         <v>189</v>
       </c>
@@ -13859,7 +13869,7 @@
         <v>102110</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="58.35">
+    <row r="47" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
         <v>193</v>
       </c>
@@ -13879,7 +13889,7 @@
         <v>126110</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="58.35">
+    <row r="48" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
         <v>197</v>
       </c>
@@ -13899,7 +13909,7 @@
         <v>135656</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="58.35">
+    <row r="49" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
         <v>202</v>
       </c>
@@ -13919,7 +13929,7 @@
         <v>140421</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="29.1">
+    <row r="50" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
         <v>206</v>
       </c>
@@ -13939,7 +13949,7 @@
         <v>143536</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="29.1">
+    <row r="51" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
         <v>210</v>
       </c>
@@ -13959,7 +13969,7 @@
         <v>146036</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="29.1">
+    <row r="52" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
         <v>214</v>
       </c>
@@ -13979,7 +13989,7 @@
         <v>153263</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="29.1">
+    <row r="53" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
         <v>218</v>
       </c>
@@ -13999,7 +14009,7 @@
         <v>161125</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="43.7">
+    <row r="54" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
         <v>222</v>
       </c>
@@ -14019,7 +14029,7 @@
         <v>166403</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
+    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
         <v>226</v>
       </c>
@@ -14039,7 +14049,7 @@
         <v>171855</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="29.1">
+    <row r="56" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
         <v>230</v>
       </c>
@@ -14059,7 +14069,7 @@
         <v>176315</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="29.1">
+    <row r="57" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
         <v>234</v>
       </c>
@@ -14079,7 +14089,7 @@
         <v>178666</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="29.1">
+    <row r="58" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
         <v>238</v>
       </c>
@@ -14099,7 +14109,7 @@
         <v>180365</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="29.1">
+    <row r="59" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
         <v>242</v>
       </c>
@@ -14119,7 +14129,7 @@
         <v>183404</v>
       </c>
     </row>
-    <row r="60" spans="1:6">
+    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
         <v>246</v>
       </c>
@@ -14139,7 +14149,7 @@
         <v>187694</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="43.7">
+    <row r="61" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
         <v>250</v>
       </c>
@@ -14159,7 +14169,7 @@
         <v>204251</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="43.7">
+    <row r="62" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
         <v>254</v>
       </c>
@@ -14179,7 +14189,7 @@
         <v>214317</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="29.1">
+    <row r="63" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
         <v>258</v>
       </c>
@@ -14199,7 +14209,7 @@
         <v>217037</v>
       </c>
     </row>
-    <row r="64" spans="1:6" ht="58.35">
+    <row r="64" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
         <v>262</v>
       </c>
@@ -14219,7 +14229,7 @@
         <v>233281</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="29.1">
+    <row r="65" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
         <v>266</v>
       </c>
@@ -14239,7 +14249,7 @@
         <v>239086</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
         <v>270</v>
       </c>
@@ -14259,7 +14269,7 @@
         <v>243363</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="29.1">
+    <row r="67" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
         <v>274</v>
       </c>
@@ -14279,7 +14289,7 @@
         <v>249280</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="43.7">
+    <row r="68" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
         <v>278</v>
       </c>
@@ -14299,7 +14309,7 @@
         <v>251641</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="29.1">
+    <row r="69" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A69" t="s">
         <v>282</v>
       </c>
@@ -14319,7 +14329,7 @@
         <v>259464</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="43.7">
+    <row r="70" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
         <v>286</v>
       </c>
@@ -14339,7 +14349,7 @@
         <v>266002</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="29.1">
+    <row r="71" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
         <v>290</v>
       </c>
@@ -14359,7 +14369,7 @@
         <v>267804</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="29.1">
+    <row r="72" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
         <v>294</v>
       </c>
@@ -14379,7 +14389,7 @@
         <v>286715</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="29.1">
+    <row r="73" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
         <v>298</v>
       </c>
@@ -14399,7 +14409,7 @@
         <v>287782</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
         <v>302</v>
       </c>
@@ -14419,7 +14429,7 @@
         <v>309008</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="29.1">
+    <row r="75" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A75" t="s">
         <v>306</v>
       </c>
@@ -14439,7 +14449,7 @@
         <v>309055</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="43.7">
+    <row r="76" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A76" t="s">
         <v>310</v>
       </c>
@@ -14459,7 +14469,7 @@
         <v>309667</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
+    <row r="77" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
         <v>314</v>
       </c>
@@ -14479,7 +14489,7 @@
         <v>315868</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="29.1">
+    <row r="78" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
         <v>318</v>
       </c>
@@ -14499,7 +14509,7 @@
         <v>320413</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="43.7">
+    <row r="79" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A79" t="s">
         <v>322</v>
       </c>
@@ -14519,7 +14529,7 @@
         <v>323448</v>
       </c>
     </row>
-    <row r="80" spans="1:6" ht="72.95">
+    <row r="80" spans="1:6" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A80" t="s">
         <v>326</v>
       </c>
@@ -14539,7 +14549,7 @@
         <v>346052</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="43.7">
+    <row r="81" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
         <v>330</v>
       </c>
@@ -14559,7 +14569,7 @@
         <v>348213</v>
       </c>
     </row>
-    <row r="82" spans="1:6" ht="29.1">
+    <row r="82" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
         <v>334</v>
       </c>
@@ -14579,7 +14589,7 @@
         <v>351962</v>
       </c>
     </row>
-    <row r="83" spans="1:6" ht="43.7">
+    <row r="83" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
         <v>338</v>
       </c>
@@ -14599,7 +14609,7 @@
         <v>352434</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="29.1">
+    <row r="84" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
         <v>342</v>
       </c>
@@ -14619,7 +14629,7 @@
         <v>353511</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
         <v>346</v>
       </c>
@@ -14639,7 +14649,7 @@
         <v>360647</v>
       </c>
     </row>
-    <row r="86" spans="1:6" ht="43.7">
+    <row r="86" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
         <v>350</v>
       </c>
@@ -14659,7 +14669,7 @@
         <v>365478</v>
       </c>
     </row>
-    <row r="87" spans="1:6" ht="43.7">
+    <row r="87" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A87" t="s">
         <v>354</v>
       </c>
@@ -14679,7 +14689,7 @@
         <v>365502</v>
       </c>
     </row>
-    <row r="88" spans="1:6" ht="29.1">
+    <row r="88" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A88" t="s">
         <v>358</v>
       </c>
@@ -14699,7 +14709,7 @@
         <v>375339</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="43.7">
+    <row r="89" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
         <v>362</v>
       </c>
@@ -14719,7 +14729,7 @@
         <v>375339</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="43.7">
+    <row r="90" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
         <v>365</v>
       </c>
@@ -14739,7 +14749,7 @@
         <v>391736</v>
       </c>
     </row>
-    <row r="91" spans="1:6" ht="43.7">
+    <row r="91" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
         <v>368</v>
       </c>
@@ -14759,7 +14769,7 @@
         <v>396248</v>
       </c>
     </row>
-    <row r="92" spans="1:6" ht="29.1">
+    <row r="92" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A92" t="s">
         <v>372</v>
       </c>
@@ -14779,7 +14789,7 @@
         <v>400413</v>
       </c>
     </row>
-    <row r="93" spans="1:6" ht="58.35">
+    <row r="93" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
         <v>376</v>
       </c>
@@ -14799,7 +14809,7 @@
         <v>403716</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="29.1">
+    <row r="94" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
         <v>380</v>
       </c>
@@ -14819,7 +14829,7 @@
         <v>404431</v>
       </c>
     </row>
-    <row r="95" spans="1:6">
+    <row r="95" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A95" t="s">
         <v>384</v>
       </c>
@@ -14839,7 +14849,7 @@
         <v>408750</v>
       </c>
     </row>
-    <row r="96" spans="1:6" ht="29.1">
+    <row r="96" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
         <v>388</v>
       </c>
@@ -14859,7 +14869,7 @@
         <v>412173</v>
       </c>
     </row>
-    <row r="97" spans="1:6" ht="29.1">
+    <row r="97" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
         <v>392</v>
       </c>
@@ -14879,7 +14889,7 @@
         <v>425589</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="29.1">
+    <row r="98" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A98" t="s">
         <v>396</v>
       </c>
@@ -14899,7 +14909,7 @@
         <v>432100</v>
       </c>
     </row>
-    <row r="99" spans="1:6" ht="29.1">
+    <row r="99" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A99" t="s">
         <v>400</v>
       </c>
@@ -14919,7 +14929,7 @@
         <v>432220</v>
       </c>
     </row>
-    <row r="100" spans="1:6">
+    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A100" t="s">
         <v>404</v>
       </c>
@@ -14939,7 +14949,7 @@
         <v>459262</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="29.1">
+    <row r="101" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
         <v>408</v>
       </c>
@@ -14959,7 +14969,7 @@
         <v>482600</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="29.1">
+    <row r="102" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A102" t="s">
         <v>412</v>
       </c>
@@ -14979,7 +14989,7 @@
         <v>484004</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="43.7">
+    <row r="103" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A103" t="s">
         <v>416</v>
       </c>
@@ -14999,7 +15009,7 @@
         <v>484462</v>
       </c>
     </row>
-    <row r="104" spans="1:6" ht="29.1">
+    <row r="104" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A104" t="s">
         <v>420</v>
       </c>
@@ -15019,7 +15029,7 @@
         <v>488913</v>
       </c>
     </row>
-    <row r="105" spans="1:6" ht="29.1">
+    <row r="105" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A105" t="s">
         <v>424</v>
       </c>
@@ -15039,7 +15049,7 @@
         <v>496016</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="29.1">
+    <row r="106" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A106" t="s">
         <v>428</v>
       </c>
@@ -15059,7 +15069,7 @@
         <v>500776</v>
       </c>
     </row>
-    <row r="107" spans="1:6">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A107" t="s">
         <v>432</v>
       </c>
@@ -15079,7 +15089,7 @@
         <v>505919</v>
       </c>
     </row>
-    <row r="108" spans="1:6" ht="29.1">
+    <row r="108" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A108" t="s">
         <v>436</v>
       </c>
@@ -15099,7 +15109,7 @@
         <v>507962</v>
       </c>
     </row>
-    <row r="109" spans="1:6" ht="58.35">
+    <row r="109" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A109" t="s">
         <v>440</v>
       </c>
@@ -15119,7 +15129,7 @@
         <v>509145</v>
       </c>
     </row>
-    <row r="110" spans="1:6" ht="29.1">
+    <row r="110" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A110" t="s">
         <v>444</v>
       </c>
@@ -15139,7 +15149,7 @@
         <v>510214</v>
       </c>
     </row>
-    <row r="111" spans="1:6" ht="29.1">
+    <row r="111" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A111" t="s">
         <v>448</v>
       </c>
@@ -15159,7 +15169,7 @@
         <v>519181</v>
       </c>
     </row>
-    <row r="112" spans="1:6" ht="43.7">
+    <row r="112" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A112" t="s">
         <v>452</v>
       </c>
@@ -15179,7 +15189,7 @@
         <v>520449</v>
       </c>
     </row>
-    <row r="113" spans="1:6" ht="29.1">
+    <row r="113" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A113" t="s">
         <v>456</v>
       </c>
@@ -15199,7 +15209,7 @@
         <v>530925</v>
       </c>
     </row>
-    <row r="114" spans="1:6" ht="29.1">
+    <row r="114" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A114" t="s">
         <v>460</v>
       </c>
@@ -15219,7 +15229,7 @@
         <v>531264</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="29.1">
+    <row r="115" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
         <v>464</v>
       </c>
@@ -15239,7 +15249,7 @@
         <v>543730</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="29.1">
+    <row r="116" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A116" t="s">
         <v>468</v>
       </c>
@@ -15259,7 +15269,7 @@
         <v>566993</v>
       </c>
     </row>
-    <row r="117" spans="1:6" ht="29.1">
+    <row r="117" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A117" t="s">
         <v>472</v>
       </c>
@@ -15279,7 +15289,7 @@
         <v>580034</v>
       </c>
     </row>
-    <row r="118" spans="1:6" ht="43.7">
+    <row r="118" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A118" t="s">
         <v>476</v>
       </c>
@@ -15299,7 +15309,7 @@
         <v>594664</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="58.35">
+    <row r="119" spans="1:6" ht="58.3" x14ac:dyDescent="0.4">
       <c r="A119" t="s">
         <v>480</v>
       </c>
@@ -15319,7 +15329,7 @@
         <v>643647</v>
       </c>
     </row>
-    <row r="120" spans="1:6" ht="29.1">
+    <row r="120" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A120" t="s">
         <v>484</v>
       </c>
@@ -15339,7 +15349,7 @@
         <v>660120</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="58.35">
+    <row r="121" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A121" t="s">
         <v>488</v>
       </c>
@@ -15359,7 +15369,7 @@
         <v>660838</v>
       </c>
     </row>
-    <row r="122" spans="1:6">
+    <row r="122" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A122" t="s">
         <v>492</v>
       </c>
@@ -15379,7 +15389,7 @@
         <v>701397</v>
       </c>
     </row>
-    <row r="123" spans="1:6" ht="29.1">
+    <row r="123" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A123" t="s">
         <v>496</v>
       </c>
@@ -15399,7 +15409,7 @@
         <v>702711</v>
       </c>
     </row>
-    <row r="124" spans="1:6" ht="43.7">
+    <row r="124" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A124" t="s">
         <v>500</v>
       </c>
@@ -15419,7 +15429,7 @@
         <v>718979</v>
       </c>
     </row>
-    <row r="125" spans="1:6" ht="43.7">
+    <row r="125" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A125" t="s">
         <v>504</v>
       </c>
@@ -15439,7 +15449,7 @@
         <v>726358</v>
       </c>
     </row>
-    <row r="126" spans="1:6" ht="29.1">
+    <row r="126" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A126" t="s">
         <v>508</v>
       </c>
@@ -15459,7 +15469,7 @@
         <v>731632</v>
       </c>
     </row>
-    <row r="127" spans="1:6" ht="29.1">
+    <row r="127" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A127" t="s">
         <v>512</v>
       </c>
@@ -15479,7 +15489,7 @@
         <v>745052</v>
       </c>
     </row>
-    <row r="128" spans="1:6" ht="29.1">
+    <row r="128" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A128" t="s">
         <v>516</v>
       </c>
@@ -15499,7 +15509,7 @@
         <v>757483</v>
       </c>
     </row>
-    <row r="129" spans="1:6" ht="29.1">
+    <row r="129" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A129" t="s">
         <v>520</v>
       </c>
@@ -15519,7 +15529,7 @@
         <v>761801</v>
       </c>
     </row>
-    <row r="130" spans="1:6" ht="29.1">
+    <row r="130" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A130" t="s">
         <v>524</v>
       </c>
@@ -15539,7 +15549,7 @@
         <v>780609</v>
       </c>
     </row>
-    <row r="131" spans="1:6" ht="43.7">
+    <row r="131" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A131" t="s">
         <v>528</v>
       </c>
@@ -15559,7 +15569,7 @@
         <v>806246</v>
       </c>
     </row>
-    <row r="132" spans="1:6" ht="29.1">
+    <row r="132" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A132" t="s">
         <v>532</v>
       </c>
@@ -15579,7 +15589,7 @@
         <v>817722</v>
       </c>
     </row>
-    <row r="133" spans="1:6">
+    <row r="133" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A133" t="s">
         <v>536</v>
       </c>
@@ -15599,7 +15609,7 @@
         <v>822846</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="43.7">
+    <row r="134" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A134" t="s">
         <v>540</v>
       </c>
@@ -15619,7 +15629,7 @@
         <v>849801</v>
       </c>
     </row>
-    <row r="135" spans="1:6">
+    <row r="135" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A135" t="s">
         <v>544</v>
       </c>
@@ -15639,7 +15649,7 @@
         <v>862955</v>
       </c>
     </row>
-    <row r="136" spans="1:6" ht="29.1">
+    <row r="136" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A136" t="s">
         <v>548</v>
       </c>
@@ -15659,7 +15669,7 @@
         <v>878311</v>
       </c>
     </row>
-    <row r="137" spans="1:6" ht="29.1">
+    <row r="137" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A137" t="s">
         <v>552</v>
       </c>
@@ -15679,7 +15689,7 @@
         <v>878726</v>
       </c>
     </row>
-    <row r="138" spans="1:6" ht="29.1">
+    <row r="138" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A138" t="s">
         <v>556</v>
       </c>
@@ -15699,7 +15709,7 @@
         <v>880360</v>
       </c>
     </row>
-    <row r="139" spans="1:6" ht="29.1">
+    <row r="139" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A139" t="s">
         <v>560</v>
       </c>
@@ -15719,7 +15729,7 @@
         <v>880605</v>
       </c>
     </row>
-    <row r="140" spans="1:6" ht="58.35">
+    <row r="140" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A140" t="s">
         <v>564</v>
       </c>
@@ -15739,7 +15749,7 @@
         <v>923831</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A141" t="s">
         <v>568</v>
       </c>
@@ -15759,7 +15769,7 @@
         <v>936370</v>
       </c>
     </row>
-    <row r="142" spans="1:6" ht="58.35">
+    <row r="142" spans="1:6" ht="58.3" x14ac:dyDescent="0.4">
       <c r="A142" t="s">
         <v>572</v>
       </c>
@@ -15779,7 +15789,7 @@
         <v>938812</v>
       </c>
     </row>
-    <row r="143" spans="1:6">
+    <row r="143" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A143" t="s">
         <v>576</v>
       </c>
@@ -15799,7 +15809,7 @@
         <v>951848</v>
       </c>
     </row>
-    <row r="144" spans="1:6" ht="29.1">
+    <row r="144" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A144" t="s">
         <v>580</v>
       </c>
@@ -15819,7 +15829,7 @@
         <v>960296</v>
       </c>
     </row>
-    <row r="145" spans="1:6" ht="29.1">
+    <row r="145" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A145" t="s">
         <v>584</v>
       </c>
@@ -15839,7 +15849,7 @@
         <v>963373</v>
       </c>
     </row>
-    <row r="146" spans="1:6" ht="43.7">
+    <row r="146" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A146" t="s">
         <v>588</v>
       </c>
@@ -15859,7 +15869,7 @@
         <v>973451</v>
       </c>
     </row>
-    <row r="147" spans="1:6" ht="43.7">
+    <row r="147" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A147" t="s">
         <v>592</v>
       </c>
@@ -15879,7 +15889,7 @@
         <v>975583</v>
       </c>
     </row>
-    <row r="148" spans="1:6" ht="29.1">
+    <row r="148" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A148" t="s">
         <v>596</v>
       </c>
@@ -15899,7 +15909,7 @@
         <v>978373</v>
       </c>
     </row>
-    <row r="149" spans="1:6" ht="29.1">
+    <row r="149" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A149" t="s">
         <v>600</v>
       </c>
@@ -15919,7 +15929,7 @@
         <v>979004</v>
       </c>
     </row>
-    <row r="150" spans="1:6" ht="29.1">
+    <row r="150" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A150" t="s">
         <v>604</v>
       </c>
@@ -15939,7 +15949,7 @@
         <v>996954</v>
       </c>
     </row>
-    <row r="151" spans="1:6" ht="29.1">
+    <row r="151" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A151" t="s">
         <v>608</v>
       </c>
@@ -15959,7 +15969,7 @@
         <v>1027628</v>
       </c>
     </row>
-    <row r="152" spans="1:6" ht="29.1">
+    <row r="152" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A152" t="s">
         <v>612</v>
       </c>
@@ -15979,7 +15989,7 @@
         <v>1030773</v>
       </c>
     </row>
-    <row r="153" spans="1:6" ht="29.1">
+    <row r="153" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A153" t="s">
         <v>616</v>
       </c>
@@ -15999,7 +16009,7 @@
         <v>1039619</v>
       </c>
     </row>
-    <row r="154" spans="1:6" ht="29.1">
+    <row r="154" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A154" t="s">
         <v>620</v>
       </c>
@@ -16019,7 +16029,7 @@
         <v>1050241</v>
       </c>
     </row>
-    <row r="155" spans="1:6" ht="29.1">
+    <row r="155" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A155" t="s">
         <v>624</v>
       </c>
@@ -16039,7 +16049,7 @@
         <v>1050495</v>
       </c>
     </row>
-    <row r="156" spans="1:6" ht="43.7">
+    <row r="156" spans="1:6" ht="43.75" x14ac:dyDescent="0.4">
       <c r="A156" t="s">
         <v>628</v>
       </c>
@@ -16059,7 +16069,7 @@
         <v>1062766</v>
       </c>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A157" t="s">
         <v>632</v>
       </c>
@@ -16079,7 +16089,7 @@
         <v>1065921</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="43.7">
+    <row r="158" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A158" t="s">
         <v>636</v>
       </c>
@@ -16099,7 +16109,7 @@
         <v>1072314</v>
       </c>
     </row>
-    <row r="159" spans="1:6" ht="29.1">
+    <row r="159" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A159" t="s">
         <v>640</v>
       </c>
@@ -16119,7 +16129,7 @@
         <v>1085744</v>
       </c>
     </row>
-    <row r="160" spans="1:6" ht="43.7">
+    <row r="160" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A160" t="s">
         <v>644</v>
       </c>
@@ -16139,7 +16149,7 @@
         <v>1097588</v>
       </c>
     </row>
-    <row r="161" spans="1:6" ht="43.7">
+    <row r="161" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A161" t="s">
         <v>648</v>
       </c>
@@ -16159,7 +16169,7 @@
         <v>1101776</v>
       </c>
     </row>
-    <row r="162" spans="1:6" ht="29.1">
+    <row r="162" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A162" t="s">
         <v>652</v>
       </c>
@@ -16179,7 +16189,7 @@
         <v>1107363</v>
       </c>
     </row>
-    <row r="163" spans="1:6" ht="29.1">
+    <row r="163" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A163" t="s">
         <v>656</v>
       </c>
@@ -16199,7 +16209,7 @@
         <v>1167150</v>
       </c>
     </row>
-    <row r="164" spans="1:6" ht="29.1">
+    <row r="164" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A164" t="s">
         <v>660</v>
       </c>
@@ -16219,7 +16229,7 @@
         <v>1167391</v>
       </c>
     </row>
-    <row r="165" spans="1:6">
+    <row r="165" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A165" t="s">
         <v>664</v>
       </c>
@@ -16239,7 +16249,7 @@
         <v>1189545</v>
       </c>
     </row>
-    <row r="166" spans="1:6" ht="43.7">
+    <row r="166" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A166" t="s">
         <v>668</v>
       </c>
@@ -16259,7 +16269,7 @@
         <v>1202479</v>
       </c>
     </row>
-    <row r="167" spans="1:6" ht="29.1">
+    <row r="167" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A167" t="s">
         <v>672</v>
       </c>
@@ -16279,7 +16289,7 @@
         <v>1233068</v>
       </c>
     </row>
-    <row r="168" spans="1:6">
+    <row r="168" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A168" t="s">
         <v>676</v>
       </c>
@@ -16299,7 +16309,7 @@
         <v>1295910</v>
       </c>
     </row>
-    <row r="169" spans="1:6" ht="43.7">
+    <row r="169" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A169" t="s">
         <v>680</v>
       </c>
@@ -16319,7 +16329,7 @@
         <v>1304280</v>
       </c>
     </row>
-    <row r="170" spans="1:6">
+    <row r="170" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A170" t="s">
         <v>684</v>
       </c>
@@ -16339,7 +16349,7 @@
         <v>1377774</v>
       </c>
     </row>
-    <row r="171" spans="1:6">
+    <row r="171" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A171" t="s">
         <v>688</v>
       </c>
@@ -16359,7 +16369,7 @@
         <v>1384098</v>
       </c>
     </row>
-    <row r="172" spans="1:6">
+    <row r="172" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A172" t="s">
         <v>692</v>
       </c>
@@ -16379,7 +16389,7 @@
         <v>1408095</v>
       </c>
     </row>
-    <row r="173" spans="1:6" ht="43.7">
+    <row r="173" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A173" t="s">
         <v>696</v>
       </c>
@@ -16399,7 +16409,7 @@
         <v>1410912</v>
       </c>
     </row>
-    <row r="174" spans="1:6" ht="29.1">
+    <row r="174" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A174" t="s">
         <v>700</v>
       </c>
@@ -16419,7 +16429,7 @@
         <v>1414728</v>
       </c>
     </row>
-    <row r="175" spans="1:6" ht="43.7">
+    <row r="175" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A175" t="s">
         <v>704</v>
       </c>
@@ -16439,7 +16449,7 @@
         <v>1429264</v>
       </c>
     </row>
-    <row r="176" spans="1:6" ht="29.1">
+    <row r="176" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A176" t="s">
         <v>708</v>
       </c>
@@ -16459,7 +16469,7 @@
         <v>1436107</v>
       </c>
     </row>
-    <row r="177" spans="1:6" ht="43.7">
+    <row r="177" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A177" t="s">
         <v>712</v>
       </c>
@@ -16479,7 +16489,7 @@
         <v>1440216</v>
       </c>
     </row>
-    <row r="178" spans="1:6" ht="29.1">
+    <row r="178" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A178" t="s">
         <v>716</v>
       </c>
@@ -16499,7 +16509,7 @@
         <v>1442744</v>
       </c>
     </row>
-    <row r="179" spans="1:6" ht="43.7">
+    <row r="179" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A179" t="s">
         <v>720</v>
       </c>
@@ -16519,7 +16529,7 @@
         <v>1446616</v>
       </c>
     </row>
-    <row r="180" spans="1:6" ht="29.1">
+    <row r="180" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A180" t="s">
         <v>724</v>
       </c>
@@ -16539,7 +16549,7 @@
         <v>1447763</v>
       </c>
     </row>
-    <row r="181" spans="1:6">
+    <row r="181" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A181" t="s">
         <v>728</v>
       </c>
@@ -16559,7 +16569,7 @@
         <v>1480067</v>
       </c>
     </row>
-    <row r="182" spans="1:6" ht="29.1">
+    <row r="182" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A182" t="s">
         <v>732</v>
       </c>
@@ -16579,7 +16589,7 @@
         <v>1489708</v>
       </c>
     </row>
-    <row r="183" spans="1:6" ht="29.1">
+    <row r="183" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A183" t="s">
         <v>736</v>
       </c>
@@ -16599,7 +16609,7 @@
         <v>1504224</v>
       </c>
     </row>
-    <row r="184" spans="1:6" ht="29.1">
+    <row r="184" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A184" t="s">
         <v>740</v>
       </c>
@@ -16619,7 +16629,7 @@
         <v>1518682</v>
       </c>
     </row>
-    <row r="185" spans="1:6" ht="29.1">
+    <row r="185" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A185" t="s">
         <v>744</v>
       </c>
@@ -16639,7 +16649,7 @@
         <v>1523057</v>
       </c>
     </row>
-    <row r="186" spans="1:6" ht="43.7">
+    <row r="186" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A186" t="s">
         <v>748</v>
       </c>
@@ -16659,7 +16669,7 @@
         <v>1534806</v>
       </c>
     </row>
-    <row r="187" spans="1:6" ht="58.35">
+    <row r="187" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A187" t="s">
         <v>752</v>
       </c>
@@ -16679,7 +16689,7 @@
         <v>1570581</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="72.95">
+    <row r="188" spans="1:6" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A188" t="s">
         <v>756</v>
       </c>
@@ -16699,7 +16709,7 @@
         <v>1571442</v>
       </c>
     </row>
-    <row r="189" spans="1:6" ht="43.7">
+    <row r="189" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A189" t="s">
         <v>760</v>
       </c>
@@ -16719,7 +16729,7 @@
         <v>1579334</v>
       </c>
     </row>
-    <row r="190" spans="1:6" ht="29.1">
+    <row r="190" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A190" t="s">
         <v>764</v>
       </c>
@@ -16739,7 +16749,7 @@
         <v>1606940</v>
       </c>
     </row>
-    <row r="191" spans="1:6">
+    <row r="191" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A191" t="s">
         <v>768</v>
       </c>
@@ -16759,7 +16769,7 @@
         <v>1628179</v>
       </c>
     </row>
-    <row r="192" spans="1:6" ht="29.1">
+    <row r="192" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A192" t="s">
         <v>772</v>
       </c>
@@ -16779,7 +16789,7 @@
         <v>1636558</v>
       </c>
     </row>
-    <row r="193" spans="1:6" ht="29.1">
+    <row r="193" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A193" t="s">
         <v>776</v>
       </c>
@@ -16799,7 +16809,7 @@
         <v>1653522</v>
       </c>
     </row>
-    <row r="194" spans="1:6" ht="43.7">
+    <row r="194" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A194" t="s">
         <v>780</v>
       </c>
@@ -16819,7 +16829,7 @@
         <v>1666252</v>
       </c>
     </row>
-    <row r="195" spans="1:6" ht="29.1">
+    <row r="195" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A195" t="s">
         <v>784</v>
       </c>
@@ -16839,7 +16849,7 @@
         <v>1674173</v>
       </c>
     </row>
-    <row r="196" spans="1:6" ht="43.7">
+    <row r="196" spans="1:6" ht="43.75" x14ac:dyDescent="0.4">
       <c r="A196" t="s">
         <v>788</v>
       </c>
@@ -16859,7 +16869,7 @@
         <v>1674968</v>
       </c>
     </row>
-    <row r="197" spans="1:6" ht="29.1">
+    <row r="197" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A197" t="s">
         <v>792</v>
       </c>
@@ -16879,7 +16889,7 @@
         <v>1688511</v>
       </c>
     </row>
-    <row r="198" spans="1:6" ht="29.1">
+    <row r="198" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A198" t="s">
         <v>796</v>
       </c>
@@ -16899,7 +16909,7 @@
         <v>1700544</v>
       </c>
     </row>
-    <row r="199" spans="1:6">
+    <row r="199" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A199" t="s">
         <v>800</v>
       </c>
@@ -16919,7 +16929,7 @@
         <v>1707827</v>
       </c>
     </row>
-    <row r="200" spans="1:6">
+    <row r="200" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A200" t="s">
         <v>804</v>
       </c>
@@ -16939,7 +16949,7 @@
         <v>1724370</v>
       </c>
     </row>
-    <row r="201" spans="1:6" ht="29.1">
+    <row r="201" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A201" t="s">
         <v>808</v>
       </c>
@@ -16959,7 +16969,7 @@
         <v>1734631</v>
       </c>
     </row>
-    <row r="202" spans="1:6" ht="43.7">
+    <row r="202" spans="1:6" ht="43.75" x14ac:dyDescent="0.4">
       <c r="A202" t="s">
         <v>812</v>
       </c>
@@ -16979,7 +16989,7 @@
         <v>1774603</v>
       </c>
     </row>
-    <row r="203" spans="1:6" ht="29.1">
+    <row r="203" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A203" t="s">
         <v>816</v>
       </c>
@@ -16999,7 +17009,7 @@
         <v>1776620</v>
       </c>
     </row>
-    <row r="204" spans="1:6" ht="72.95">
+    <row r="204" spans="1:6" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A204" t="s">
         <v>820</v>
       </c>
@@ -17019,7 +17029,7 @@
         <v>1795363</v>
       </c>
     </row>
-    <row r="205" spans="1:6" ht="43.7">
+    <row r="205" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A205" t="s">
         <v>824</v>
       </c>
@@ -17039,7 +17049,7 @@
         <v>1802331</v>
       </c>
     </row>
-    <row r="206" spans="1:6" ht="29.1">
+    <row r="206" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A206" t="s">
         <v>828</v>
       </c>
@@ -17059,7 +17069,7 @@
         <v>1807772</v>
       </c>
     </row>
-    <row r="207" spans="1:6">
+    <row r="207" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A207" t="s">
         <v>832</v>
       </c>
@@ -17079,7 +17089,7 @@
         <v>1809893</v>
       </c>
     </row>
-    <row r="208" spans="1:6" ht="43.7">
+    <row r="208" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A208" t="s">
         <v>836</v>
       </c>
@@ -17099,7 +17109,7 @@
         <v>1813144</v>
       </c>
     </row>
-    <row r="209" spans="1:6" ht="43.7">
+    <row r="209" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A209" t="s">
         <v>840</v>
       </c>
@@ -17119,7 +17129,7 @@
         <v>1824388</v>
       </c>
     </row>
-    <row r="210" spans="1:6" ht="87.4">
+    <row r="210" spans="1:6" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A210" t="s">
         <v>844</v>
       </c>
@@ -17139,7 +17149,7 @@
         <v>1835720</v>
       </c>
     </row>
-    <row r="211" spans="1:6" ht="29.1">
+    <row r="211" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A211" t="s">
         <v>848</v>
       </c>
@@ -17159,7 +17169,7 @@
         <v>1838496</v>
       </c>
     </row>
-    <row r="212" spans="1:6" ht="43.7">
+    <row r="212" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A212" t="s">
         <v>852</v>
       </c>
@@ -17179,7 +17189,7 @@
         <v>1858393</v>
       </c>
     </row>
-    <row r="213" spans="1:6" ht="29.1">
+    <row r="213" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A213" t="s">
         <v>856</v>
       </c>
@@ -17199,7 +17209,7 @@
         <v>1861798</v>
       </c>
     </row>
-    <row r="214" spans="1:6" ht="29.1">
+    <row r="214" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A214" t="s">
         <v>860</v>
       </c>
@@ -17219,7 +17229,7 @@
         <v>1870058</v>
       </c>
     </row>
-    <row r="215" spans="1:6" ht="43.7">
+    <row r="215" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A215" t="s">
         <v>864</v>
       </c>
@@ -17239,7 +17249,7 @@
         <v>1889232</v>
       </c>
     </row>
-    <row r="216" spans="1:6" ht="43.7">
+    <row r="216" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A216" t="s">
         <v>868</v>
       </c>
@@ -17259,7 +17269,7 @@
         <v>1901956</v>
       </c>
     </row>
-    <row r="217" spans="1:6" ht="43.7">
+    <row r="217" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A217" t="s">
         <v>872</v>
       </c>
@@ -17279,7 +17289,7 @@
         <v>1903190</v>
       </c>
     </row>
-    <row r="218" spans="1:6" ht="43.7">
+    <row r="218" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A218" t="s">
         <v>876</v>
       </c>
@@ -17299,7 +17309,7 @@
         <v>1907980</v>
       </c>
     </row>
-    <row r="219" spans="1:6" ht="29.1">
+    <row r="219" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A219" t="s">
         <v>880</v>
       </c>
@@ -17319,7 +17329,7 @@
         <v>1925431</v>
       </c>
     </row>
-    <row r="220" spans="1:6" ht="29.1">
+    <row r="220" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A220" t="s">
         <v>884</v>
       </c>
@@ -17339,7 +17349,7 @@
         <v>1933255</v>
       </c>
     </row>
-    <row r="221" spans="1:6" ht="43.7">
+    <row r="221" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A221" t="s">
         <v>888</v>
       </c>
@@ -17359,7 +17369,7 @@
         <v>1959066</v>
       </c>
     </row>
-    <row r="222" spans="1:6" ht="43.7">
+    <row r="222" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A222" t="s">
         <v>892</v>
       </c>
@@ -17379,7 +17389,7 @@
         <v>1962711</v>
       </c>
     </row>
-    <row r="223" spans="1:6" ht="43.7">
+    <row r="223" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A223" t="s">
         <v>896</v>
       </c>
@@ -17399,7 +17409,7 @@
         <v>1983579</v>
       </c>
     </row>
-    <row r="224" spans="1:6">
+    <row r="224" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A224" t="s">
         <v>900</v>
       </c>
@@ -17419,7 +17429,7 @@
         <v>2015995</v>
       </c>
     </row>
-    <row r="225" spans="1:6" ht="29.1">
+    <row r="225" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A225" t="s">
         <v>904</v>
       </c>
@@ -17439,7 +17449,7 @@
         <v>2025388</v>
       </c>
     </row>
-    <row r="226" spans="1:6" ht="29.1">
+    <row r="226" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A226" t="s">
         <v>908</v>
       </c>
@@ -17459,7 +17469,7 @@
         <v>2071710</v>
       </c>
     </row>
-    <row r="227" spans="1:6" ht="43.7">
+    <row r="227" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A227" t="s">
         <v>912</v>
       </c>
@@ -17479,7 +17489,7 @@
         <v>2079657</v>
       </c>
     </row>
-    <row r="228" spans="1:6" ht="29.1">
+    <row r="228" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A228" t="s">
         <v>916</v>
       </c>
@@ -17499,7 +17509,7 @@
         <v>2081700</v>
       </c>
     </row>
-    <row r="229" spans="1:6" ht="43.7">
+    <row r="229" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A229" t="s">
         <v>920</v>
       </c>
@@ -17519,7 +17529,7 @@
         <v>2084703</v>
       </c>
     </row>
-    <row r="230" spans="1:6">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A230" t="s">
         <v>924</v>
       </c>
@@ -17539,7 +17549,7 @@
         <v>2090451</v>
       </c>
     </row>
-    <row r="231" spans="1:6" ht="29.1">
+    <row r="231" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A231" t="s">
         <v>928</v>
       </c>
@@ -17559,7 +17569,7 @@
         <v>2095742</v>
       </c>
     </row>
-    <row r="232" spans="1:6" ht="43.7">
+    <row r="232" spans="1:6" ht="43.75" x14ac:dyDescent="0.4">
       <c r="A232" t="s">
         <v>932</v>
       </c>
@@ -17579,7 +17589,7 @@
         <v>2106317</v>
       </c>
     </row>
-    <row r="233" spans="1:6" ht="29.1">
+    <row r="233" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A233" t="s">
         <v>936</v>
       </c>
@@ -17599,7 +17609,7 @@
         <v>2126296</v>
       </c>
     </row>
-    <row r="234" spans="1:6" ht="29.1">
+    <row r="234" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A234" t="s">
         <v>940</v>
       </c>
@@ -17619,7 +17629,7 @@
         <v>2132945</v>
       </c>
     </row>
-    <row r="235" spans="1:6" ht="29.1">
+    <row r="235" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A235" t="s">
         <v>944</v>
       </c>
@@ -17639,7 +17649,7 @@
         <v>2164423</v>
       </c>
     </row>
-    <row r="236" spans="1:6" ht="43.7">
+    <row r="236" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A236" t="s">
         <v>948</v>
       </c>
@@ -17659,7 +17669,7 @@
         <v>2168867</v>
       </c>
     </row>
-    <row r="237" spans="1:6" ht="29.1">
+    <row r="237" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A237" t="s">
         <v>952</v>
       </c>
@@ -17679,7 +17689,7 @@
         <v>2197885</v>
       </c>
     </row>
-    <row r="238" spans="1:6" ht="29.1">
+    <row r="238" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A238" t="s">
         <v>956</v>
       </c>
@@ -17699,7 +17709,7 @@
         <v>2204217</v>
       </c>
     </row>
-    <row r="239" spans="1:6" ht="29.1">
+    <row r="239" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A239" t="s">
         <v>960</v>
       </c>
@@ -17719,7 +17729,7 @@
         <v>2231299</v>
       </c>
     </row>
-    <row r="240" spans="1:6" ht="29.1">
+    <row r="240" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A240" t="s">
         <v>964</v>
       </c>
@@ -17739,7 +17749,7 @@
         <v>2236851</v>
       </c>
     </row>
-    <row r="241" spans="1:6" ht="43.7">
+    <row r="241" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A241" t="s">
         <v>968</v>
       </c>
@@ -17759,7 +17769,7 @@
         <v>2247330</v>
       </c>
     </row>
-    <row r="242" spans="1:6" ht="29.1">
+    <row r="242" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A242" t="s">
         <v>972</v>
       </c>
@@ -17779,7 +17789,7 @@
         <v>2251934</v>
       </c>
     </row>
-    <row r="243" spans="1:6" ht="43.7">
+    <row r="243" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A243" t="s">
         <v>976</v>
       </c>
@@ -17799,7 +17809,7 @@
         <v>2254387</v>
       </c>
     </row>
-    <row r="244" spans="1:6" ht="29.1">
+    <row r="244" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A244" t="s">
         <v>980</v>
       </c>
@@ -17819,7 +17829,7 @@
         <v>2257437</v>
       </c>
     </row>
-    <row r="245" spans="1:6" ht="29.1">
+    <row r="245" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A245" t="s">
         <v>985</v>
       </c>
@@ -17839,7 +17849,7 @@
         <v>2280525</v>
       </c>
     </row>
-    <row r="246" spans="1:6" ht="29.1">
+    <row r="246" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A246" t="s">
         <v>989</v>
       </c>
@@ -17859,7 +17869,7 @@
         <v>2287509</v>
       </c>
     </row>
-    <row r="247" spans="1:6">
+    <row r="247" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A247" t="s">
         <v>993</v>
       </c>
@@ -17879,7 +17889,7 @@
         <v>2319121</v>
       </c>
     </row>
-    <row r="248" spans="1:6">
+    <row r="248" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A248" t="s">
         <v>997</v>
       </c>
@@ -17899,7 +17909,7 @@
         <v>2337797</v>
       </c>
     </row>
-    <row r="249" spans="1:6" ht="43.7">
+    <row r="249" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A249" t="s">
         <v>1001</v>
       </c>
@@ -17919,7 +17929,7 @@
         <v>2343433</v>
       </c>
     </row>
-    <row r="250" spans="1:6" ht="29.1">
+    <row r="250" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A250" t="s">
         <v>1005</v>
       </c>
@@ -17939,7 +17949,7 @@
         <v>2349133</v>
       </c>
     </row>
-    <row r="251" spans="1:6" ht="29.1">
+    <row r="251" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A251" t="s">
         <v>1009</v>
       </c>
@@ -17959,7 +17969,7 @@
         <v>2392365</v>
       </c>
     </row>
-    <row r="252" spans="1:6" ht="29.1">
+    <row r="252" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A252" t="s">
         <v>1013</v>
       </c>
@@ -17979,7 +17989,7 @@
         <v>2423032</v>
       </c>
     </row>
-    <row r="253" spans="1:6" ht="29.1">
+    <row r="253" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A253" t="s">
         <v>1017</v>
       </c>
@@ -17999,7 +18009,7 @@
         <v>2435177</v>
       </c>
     </row>
-    <row r="254" spans="1:6" ht="29.1">
+    <row r="254" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A254" t="s">
         <v>1021</v>
       </c>
@@ -18019,7 +18029,7 @@
         <v>2440747</v>
       </c>
     </row>
-    <row r="255" spans="1:6" ht="29.1">
+    <row r="255" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A255" t="s">
         <v>1025</v>
       </c>
@@ -18039,7 +18049,7 @@
         <v>2450709</v>
       </c>
     </row>
-    <row r="256" spans="1:6" ht="29.1">
+    <row r="256" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A256" t="s">
         <v>1029</v>
       </c>
@@ -18059,7 +18069,7 @@
         <v>2465706</v>
       </c>
     </row>
-    <row r="257" spans="1:6" ht="29.1">
+    <row r="257" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A257" t="s">
         <v>1033</v>
       </c>
@@ -18079,7 +18089,7 @@
         <v>2466893</v>
       </c>
     </row>
-    <row r="258" spans="1:6" ht="29.1">
+    <row r="258" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A258" t="s">
         <v>1037</v>
       </c>
@@ -18099,7 +18109,7 @@
         <v>2473880</v>
       </c>
     </row>
-    <row r="259" spans="1:6" ht="43.7">
+    <row r="259" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A259" t="s">
         <v>1041</v>
       </c>
@@ -18119,7 +18129,7 @@
         <v>2502392</v>
       </c>
     </row>
-    <row r="260" spans="1:6">
+    <row r="260" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A260" t="s">
         <v>1045</v>
       </c>
@@ -18139,7 +18149,7 @@
         <v>2525783</v>
       </c>
     </row>
-    <row r="261" spans="1:6" ht="29.1">
+    <row r="261" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A261" t="s">
         <v>1049</v>
       </c>
@@ -18159,7 +18169,7 @@
         <v>2548089</v>
       </c>
     </row>
-    <row r="262" spans="1:6" ht="29.1">
+    <row r="262" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A262" t="s">
         <v>1053</v>
       </c>
@@ -18179,7 +18189,7 @@
         <v>2553959</v>
       </c>
     </row>
-    <row r="263" spans="1:6" ht="29.1">
+    <row r="263" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A263" t="s">
         <v>1057</v>
       </c>
@@ -18199,7 +18209,7 @@
         <v>2566893</v>
       </c>
     </row>
-    <row r="264" spans="1:6" ht="29.1">
+    <row r="264" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A264" t="s">
         <v>1061</v>
       </c>
@@ -18219,7 +18229,7 @@
         <v>2570540</v>
       </c>
     </row>
-    <row r="265" spans="1:6" ht="29.1">
+    <row r="265" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A265" t="s">
         <v>1065</v>
       </c>
@@ -18239,7 +18249,7 @@
         <v>2598046</v>
       </c>
     </row>
-    <row r="266" spans="1:6" ht="29.1">
+    <row r="266" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A266" t="s">
         <v>1069</v>
       </c>
@@ -18259,7 +18269,7 @@
         <v>2601065</v>
       </c>
     </row>
-    <row r="267" spans="1:6" ht="29.1">
+    <row r="267" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A267" t="s">
         <v>1073</v>
       </c>
@@ -18279,7 +18289,7 @@
         <v>2627818</v>
       </c>
     </row>
-    <row r="268" spans="1:6">
+    <row r="268" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A268" t="s">
         <v>1077</v>
       </c>
@@ -18299,7 +18309,7 @@
         <v>2628470</v>
       </c>
     </row>
-    <row r="269" spans="1:6" ht="29.1">
+    <row r="269" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A269" t="s">
         <v>1081</v>
       </c>
@@ -18319,7 +18329,7 @@
         <v>2645260</v>
       </c>
     </row>
-    <row r="270" spans="1:6" ht="29.1">
+    <row r="270" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A270" t="s">
         <v>1085</v>
       </c>
@@ -18339,7 +18349,7 @@
         <v>2647370</v>
       </c>
     </row>
-    <row r="271" spans="1:6" ht="43.7">
+    <row r="271" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A271" t="s">
         <v>1089</v>
       </c>
@@ -18359,7 +18369,7 @@
         <v>2660218</v>
       </c>
     </row>
-    <row r="272" spans="1:6" ht="29.1">
+    <row r="272" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A272" t="s">
         <v>1093</v>
       </c>
@@ -18379,7 +18389,7 @@
         <v>2675484</v>
       </c>
     </row>
-    <row r="273" spans="1:6" ht="43.7">
+    <row r="273" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A273" t="s">
         <v>1097</v>
       </c>
@@ -18399,7 +18409,7 @@
         <v>2703614</v>
       </c>
     </row>
-    <row r="274" spans="1:6">
+    <row r="274" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A274" t="s">
         <v>1101</v>
       </c>
@@ -18419,7 +18429,7 @@
         <v>2711646</v>
       </c>
     </row>
-    <row r="275" spans="1:6" ht="29.1">
+    <row r="275" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A275" t="s">
         <v>1105</v>
       </c>
@@ -18439,7 +18449,7 @@
         <v>2758759</v>
       </c>
     </row>
-    <row r="276" spans="1:6" ht="43.7">
+    <row r="276" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A276" t="s">
         <v>1109</v>
       </c>
@@ -18459,7 +18469,7 @@
         <v>2776427</v>
       </c>
     </row>
-    <row r="277" spans="1:6" ht="43.7">
+    <row r="277" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A277" t="s">
         <v>1113</v>
       </c>
@@ -18479,7 +18489,7 @@
         <v>2833469</v>
       </c>
     </row>
-    <row r="278" spans="1:6" ht="29.1">
+    <row r="278" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A278" t="s">
         <v>1117</v>
       </c>
@@ -18499,7 +18509,7 @@
         <v>2843537</v>
       </c>
     </row>
-    <row r="279" spans="1:6" ht="29.1">
+    <row r="279" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A279" t="s">
         <v>1121</v>
       </c>
@@ -18519,7 +18529,7 @@
         <v>2849951</v>
       </c>
     </row>
-    <row r="280" spans="1:6" ht="43.7">
+    <row r="280" spans="1:6" ht="43.75" x14ac:dyDescent="0.4">
       <c r="A280" t="s">
         <v>1125</v>
       </c>
@@ -18539,7 +18549,7 @@
         <v>2850446</v>
       </c>
     </row>
-    <row r="281" spans="1:6" ht="29.1">
+    <row r="281" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A281" t="s">
         <v>1129</v>
       </c>
@@ -18559,7 +18569,7 @@
         <v>2868126</v>
       </c>
     </row>
-    <row r="282" spans="1:6" ht="29.1">
+    <row r="282" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A282" t="s">
         <v>1133</v>
       </c>
@@ -18579,7 +18589,7 @@
         <v>2868797</v>
       </c>
     </row>
-    <row r="283" spans="1:6" ht="43.7">
+    <row r="283" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A283" t="s">
         <v>1137</v>
       </c>
@@ -18599,7 +18609,7 @@
         <v>2876995</v>
       </c>
     </row>
-    <row r="284" spans="1:6" ht="58.35">
+    <row r="284" spans="1:6" ht="58.3" x14ac:dyDescent="0.4">
       <c r="A284" t="s">
         <v>1141</v>
       </c>
@@ -18619,7 +18629,7 @@
         <v>2881047</v>
       </c>
     </row>
-    <row r="285" spans="1:6" ht="29.1">
+    <row r="285" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A285" t="s">
         <v>1145</v>
       </c>
@@ -18639,7 +18649,7 @@
         <v>2894951</v>
       </c>
     </row>
-    <row r="286" spans="1:6" ht="43.7">
+    <row r="286" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A286" t="s">
         <v>1149</v>
       </c>
@@ -18659,7 +18669,7 @@
         <v>2914970</v>
       </c>
     </row>
-    <row r="287" spans="1:6" ht="29.1">
+    <row r="287" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A287" t="s">
         <v>1153</v>
       </c>
@@ -18679,7 +18689,7 @@
         <v>2935416</v>
       </c>
     </row>
-    <row r="288" spans="1:6" ht="87.4">
+    <row r="288" spans="1:6" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A288" t="s">
         <v>1157</v>
       </c>
@@ -18699,7 +18709,7 @@
         <v>2948429</v>
       </c>
     </row>
-    <row r="289" spans="1:6" ht="29.1">
+    <row r="289" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A289" t="s">
         <v>1161</v>
       </c>
@@ -18719,7 +18729,7 @@
         <v>2958172</v>
       </c>
     </row>
-    <row r="290" spans="1:6" ht="29.1">
+    <row r="290" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A290" t="s">
         <v>1165</v>
       </c>
@@ -18739,7 +18749,7 @@
         <v>2969584</v>
       </c>
     </row>
-    <row r="291" spans="1:6" ht="43.7">
+    <row r="291" spans="1:6" ht="43.75" x14ac:dyDescent="0.4">
       <c r="A291" t="s">
         <v>1169</v>
       </c>
@@ -18759,7 +18769,7 @@
         <v>3020436</v>
       </c>
     </row>
-    <row r="292" spans="1:6" ht="29.1">
+    <row r="292" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A292" t="s">
         <v>1173</v>
       </c>
@@ -18779,7 +18789,7 @@
         <v>3046804</v>
       </c>
     </row>
-    <row r="293" spans="1:6" ht="43.7">
+    <row r="293" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A293" t="s">
         <v>1177</v>
       </c>
@@ -18799,7 +18809,7 @@
         <v>3074835</v>
       </c>
     </row>
-    <row r="294" spans="1:6" ht="29.1">
+    <row r="294" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A294" t="s">
         <v>1181</v>
       </c>
@@ -18819,7 +18829,7 @@
         <v>3084667</v>
       </c>
     </row>
-    <row r="295" spans="1:6" ht="43.7">
+    <row r="295" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A295" t="s">
         <v>1185</v>
       </c>
@@ -18839,7 +18849,7 @@
         <v>3123460</v>
       </c>
     </row>
-    <row r="296" spans="1:6" ht="29.1">
+    <row r="296" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A296" t="s">
         <v>1189</v>
       </c>
@@ -18859,7 +18869,7 @@
         <v>3133883</v>
       </c>
     </row>
-    <row r="297" spans="1:6" ht="43.7">
+    <row r="297" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A297" t="s">
         <v>1193</v>
       </c>
@@ -18879,7 +18889,7 @@
         <v>3168075</v>
       </c>
     </row>
-    <row r="298" spans="1:6" ht="29.1">
+    <row r="298" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A298" t="s">
         <v>1197</v>
       </c>
@@ -18899,7 +18909,7 @@
         <v>3182877</v>
       </c>
     </row>
-    <row r="299" spans="1:6" ht="29.1">
+    <row r="299" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A299" t="s">
         <v>1201</v>
       </c>
@@ -18919,7 +18929,7 @@
         <v>3204280</v>
       </c>
     </row>
-    <row r="300" spans="1:6" ht="29.1">
+    <row r="300" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A300" t="s">
         <v>1205</v>
       </c>
@@ -18939,7 +18949,7 @@
         <v>3204762</v>
       </c>
     </row>
-    <row r="301" spans="1:6" ht="29.1">
+    <row r="301" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A301" t="s">
         <v>1209</v>
       </c>
@@ -18959,7 +18969,7 @@
         <v>3225693</v>
       </c>
     </row>
-    <row r="302" spans="1:6" ht="58.35">
+    <row r="302" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A302" t="s">
         <v>1213</v>
       </c>
@@ -18979,7 +18989,7 @@
         <v>3239061</v>
       </c>
     </row>
-    <row r="303" spans="1:6" ht="29.1">
+    <row r="303" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A303" t="s">
         <v>1217</v>
       </c>
@@ -18999,7 +19009,7 @@
         <v>3249470</v>
       </c>
     </row>
-    <row r="304" spans="1:6" ht="43.7">
+    <row r="304" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A304" t="s">
         <v>1221</v>
       </c>
@@ -19019,7 +19029,7 @@
         <v>3259912</v>
       </c>
     </row>
-    <row r="305" spans="1:6" ht="29.1">
+    <row r="305" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A305" t="s">
         <v>1225</v>
       </c>
@@ -19039,7 +19049,7 @@
         <v>3281083</v>
       </c>
     </row>
-    <row r="306" spans="1:6" ht="29.1">
+    <row r="306" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A306" t="s">
         <v>1229</v>
       </c>
@@ -19059,7 +19069,7 @@
         <v>3325590</v>
       </c>
     </row>
-    <row r="307" spans="1:6" ht="58.35">
+    <row r="307" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A307" t="s">
         <v>1233</v>
       </c>
@@ -19079,7 +19089,7 @@
         <v>3331061</v>
       </c>
     </row>
-    <row r="308" spans="1:6" ht="29.1">
+    <row r="308" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A308" t="s">
         <v>1237</v>
       </c>
@@ -19099,7 +19109,7 @@
         <v>3333735</v>
       </c>
     </row>
-    <row r="309" spans="1:6" ht="29.1">
+    <row r="309" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A309" t="s">
         <v>1241</v>
       </c>
@@ -19119,7 +19129,7 @@
         <v>3336383</v>
       </c>
     </row>
-    <row r="310" spans="1:6" ht="43.7">
+    <row r="310" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A310" t="s">
         <v>1245</v>
       </c>
@@ -19139,7 +19149,7 @@
         <v>3375644</v>
       </c>
     </row>
-    <row r="311" spans="1:6" ht="58.35">
+    <row r="311" spans="1:6" ht="58.3" x14ac:dyDescent="0.4">
       <c r="A311" t="s">
         <v>1249</v>
       </c>
@@ -19159,7 +19169,7 @@
         <v>3405462</v>
       </c>
     </row>
-    <row r="312" spans="1:6" ht="29.1">
+    <row r="312" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A312" t="s">
         <v>1253</v>
       </c>
@@ -19179,7 +19189,7 @@
         <v>3413771</v>
       </c>
     </row>
-    <row r="313" spans="1:6" ht="43.7">
+    <row r="313" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A313" t="s">
         <v>1257</v>
       </c>
@@ -19199,7 +19209,7 @@
         <v>3420792</v>
       </c>
     </row>
-    <row r="314" spans="1:6" ht="29.1">
+    <row r="314" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A314" t="s">
         <v>1261</v>
       </c>
@@ -19219,7 +19229,7 @@
         <v>3422332</v>
       </c>
     </row>
-    <row r="315" spans="1:6" ht="29.1">
+    <row r="315" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A315" t="s">
         <v>1265</v>
       </c>
@@ -19239,7 +19249,7 @@
         <v>3430512</v>
       </c>
     </row>
-    <row r="316" spans="1:6" ht="29.1">
+    <row r="316" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A316" t="s">
         <v>1269</v>
       </c>
@@ -19259,7 +19269,7 @@
         <v>3433331</v>
       </c>
     </row>
-    <row r="317" spans="1:6" ht="29.1">
+    <row r="317" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A317" t="s">
         <v>1273</v>
       </c>
@@ -19279,7 +19289,7 @@
         <v>3436940</v>
       </c>
     </row>
-    <row r="318" spans="1:6">
+    <row r="318" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A318" t="s">
         <v>1277</v>
       </c>
@@ -19299,7 +19309,7 @@
         <v>3438008</v>
       </c>
     </row>
-    <row r="319" spans="1:6" ht="43.7">
+    <row r="319" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A319" t="s">
         <v>1281</v>
       </c>
@@ -19319,7 +19329,7 @@
         <v>3444370</v>
       </c>
     </row>
-    <row r="320" spans="1:6" ht="43.7">
+    <row r="320" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A320" t="s">
         <v>1285</v>
       </c>
@@ -19339,7 +19349,7 @@
         <v>3455409</v>
       </c>
     </row>
-    <row r="321" spans="1:6" ht="58.35">
+    <row r="321" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A321" t="s">
         <v>1289</v>
       </c>
@@ -19359,7 +19369,7 @@
         <v>3465113</v>
       </c>
     </row>
-    <row r="322" spans="1:6" ht="29.1">
+    <row r="322" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A322" t="s">
         <v>1293</v>
       </c>
@@ -19379,7 +19389,7 @@
         <v>3468572</v>
       </c>
     </row>
-    <row r="323" spans="1:6" ht="43.7">
+    <row r="323" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A323" t="s">
         <v>1297</v>
       </c>
@@ -19399,7 +19409,7 @@
         <v>3483713</v>
       </c>
     </row>
-    <row r="324" spans="1:6" ht="29.1">
+    <row r="324" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A324" t="s">
         <v>1301</v>
       </c>
@@ -19419,7 +19429,7 @@
         <v>3485620</v>
       </c>
     </row>
-    <row r="325" spans="1:6" ht="29.1">
+    <row r="325" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A325" t="s">
         <v>1305</v>
       </c>
@@ -19439,7 +19449,7 @@
         <v>3500618</v>
       </c>
     </row>
-    <row r="326" spans="1:6" ht="43.7">
+    <row r="326" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A326" t="s">
         <v>1309</v>
       </c>
@@ -19459,7 +19469,7 @@
         <v>3538303</v>
       </c>
     </row>
-    <row r="327" spans="1:6" ht="29.1">
+    <row r="327" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A327" t="s">
         <v>1313</v>
       </c>
@@ -19479,7 +19489,7 @@
         <v>3574800</v>
       </c>
     </row>
-    <row r="328" spans="1:6" ht="29.1">
+    <row r="328" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A328" t="s">
         <v>1317</v>
       </c>
@@ -19499,7 +19509,7 @@
         <v>3608094</v>
       </c>
     </row>
-    <row r="329" spans="1:6" ht="29.1">
+    <row r="329" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A329" t="s">
         <v>1321</v>
       </c>
@@ -19519,7 +19529,7 @@
         <v>3647282</v>
       </c>
     </row>
-    <row r="330" spans="1:6" ht="43.7">
+    <row r="330" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A330" t="s">
         <v>1325</v>
       </c>
@@ -19539,7 +19549,7 @@
         <v>3669837</v>
       </c>
     </row>
-    <row r="331" spans="1:6" ht="29.1">
+    <row r="331" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A331" t="s">
         <v>1329</v>
       </c>
@@ -19559,7 +19569,7 @@
         <v>3684619</v>
       </c>
     </row>
-    <row r="332" spans="1:6" ht="29.1">
+    <row r="332" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A332" t="s">
         <v>1333</v>
       </c>
@@ -19579,7 +19589,7 @@
         <v>3690852</v>
       </c>
     </row>
-    <row r="333" spans="1:6" ht="43.7">
+    <row r="333" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A333" t="s">
         <v>1337</v>
       </c>
@@ -19599,7 +19609,7 @@
         <v>3709812</v>
       </c>
     </row>
-    <row r="334" spans="1:6" ht="58.35">
+    <row r="334" spans="1:6" ht="58.3" x14ac:dyDescent="0.4">
       <c r="A334" t="s">
         <v>1341</v>
       </c>
@@ -19619,7 +19629,7 @@
         <v>3713348</v>
       </c>
     </row>
-    <row r="335" spans="1:6" ht="29.1">
+    <row r="335" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A335" t="s">
         <v>1345</v>
       </c>
@@ -19639,7 +19649,7 @@
         <v>3729764</v>
       </c>
     </row>
-    <row r="336" spans="1:6" ht="29.1">
+    <row r="336" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A336" t="s">
         <v>1349</v>
       </c>
@@ -19659,7 +19669,7 @@
         <v>3730989</v>
       </c>
     </row>
-    <row r="337" spans="1:6" ht="58.35">
+    <row r="337" spans="1:6" ht="58.3" x14ac:dyDescent="0.4">
       <c r="A337" t="s">
         <v>1353</v>
       </c>
@@ -19679,7 +19689,7 @@
         <v>3733351</v>
       </c>
     </row>
-    <row r="338" spans="1:6" ht="29.1">
+    <row r="338" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A338" t="s">
         <v>1357</v>
       </c>
@@ -19699,7 +19709,7 @@
         <v>3751782</v>
       </c>
     </row>
-    <row r="339" spans="1:6" ht="43.7">
+    <row r="339" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A339" t="s">
         <v>1361</v>
       </c>
@@ -19719,7 +19729,7 @@
         <v>3764499</v>
       </c>
     </row>
-    <row r="340" spans="1:6" ht="29.1">
+    <row r="340" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A340" t="s">
         <v>1365</v>
       </c>
@@ -19739,7 +19749,7 @@
         <v>3797735</v>
       </c>
     </row>
-    <row r="341" spans="1:6" ht="29.1">
+    <row r="341" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A341" t="s">
         <v>1369</v>
       </c>
@@ -19759,7 +19769,7 @@
         <v>3840396</v>
       </c>
     </row>
-    <row r="342" spans="1:6" ht="29.1">
+    <row r="342" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A342" t="s">
         <v>1373</v>
       </c>
@@ -19779,7 +19789,7 @@
         <v>3855297</v>
       </c>
     </row>
-    <row r="343" spans="1:6" ht="43.7">
+    <row r="343" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A343" t="s">
         <v>1377</v>
       </c>
@@ -19799,7 +19809,7 @@
         <v>3855999</v>
       </c>
     </row>
-    <row r="344" spans="1:6" ht="29.1">
+    <row r="344" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A344" t="s">
         <v>1381</v>
       </c>
@@ -19819,7 +19829,7 @@
         <v>3863063</v>
       </c>
     </row>
-    <row r="345" spans="1:6" ht="29.1">
+    <row r="345" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A345" t="s">
         <v>1385</v>
       </c>
@@ -19839,7 +19849,7 @@
         <v>3872019</v>
       </c>
     </row>
-    <row r="346" spans="1:6" ht="43.7">
+    <row r="346" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A346" t="s">
         <v>1389</v>
       </c>
@@ -19859,7 +19869,7 @@
         <v>3919614</v>
       </c>
     </row>
-    <row r="347" spans="1:6" ht="29.1">
+    <row r="347" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A347" t="s">
         <v>1393</v>
       </c>
@@ -19879,7 +19889,7 @@
         <v>3933321</v>
       </c>
     </row>
-    <row r="348" spans="1:6" ht="29.1">
+    <row r="348" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A348" t="s">
         <v>1397</v>
       </c>
@@ -19899,7 +19909,7 @@
         <v>3933930</v>
       </c>
     </row>
-    <row r="349" spans="1:6" ht="29.1">
+    <row r="349" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A349" t="s">
         <v>1401</v>
       </c>
@@ -19919,7 +19929,7 @@
         <v>3950991</v>
       </c>
     </row>
-    <row r="350" spans="1:6" ht="29.1">
+    <row r="350" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A350" t="s">
         <v>1405</v>
       </c>
@@ -19939,7 +19949,7 @@
         <v>3963269</v>
       </c>
     </row>
-    <row r="351" spans="1:6" ht="29.1">
+    <row r="351" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A351" t="s">
         <v>1409</v>
       </c>
@@ -19959,7 +19969,7 @@
         <v>3980137</v>
       </c>
     </row>
-    <row r="352" spans="1:6" ht="29.1">
+    <row r="352" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A352" t="s">
         <v>1413</v>
       </c>
@@ -19979,7 +19989,7 @@
         <v>3984643</v>
       </c>
     </row>
-    <row r="353" spans="1:6" ht="29.1">
+    <row r="353" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A353" t="s">
         <v>1417</v>
       </c>
@@ -19999,7 +20009,7 @@
         <v>3989471</v>
       </c>
     </row>
-    <row r="354" spans="1:6" ht="29.1">
+    <row r="354" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A354" t="s">
         <v>1421</v>
       </c>
@@ -20019,7 +20029,7 @@
         <v>4029694</v>
       </c>
     </row>
-    <row r="355" spans="1:6" ht="29.1">
+    <row r="355" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A355" t="s">
         <v>1425</v>
       </c>
@@ -20039,7 +20049,7 @@
         <v>4032312</v>
       </c>
     </row>
-    <row r="356" spans="1:6" ht="43.7">
+    <row r="356" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A356" t="s">
         <v>1429</v>
       </c>
@@ -20059,7 +20069,7 @@
         <v>4033022</v>
       </c>
     </row>
-    <row r="357" spans="1:6" ht="72.95">
+    <row r="357" spans="1:6" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A357" t="s">
         <v>1433</v>
       </c>
@@ -20079,7 +20089,7 @@
         <v>4039516</v>
       </c>
     </row>
-    <row r="358" spans="1:6" ht="29.1">
+    <row r="358" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A358" t="s">
         <v>1437</v>
       </c>
@@ -20099,7 +20109,7 @@
         <v>4045004</v>
       </c>
     </row>
-    <row r="359" spans="1:6" ht="43.7">
+    <row r="359" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A359" t="s">
         <v>1441</v>
       </c>
@@ -20119,7 +20129,7 @@
         <v>4093097</v>
       </c>
     </row>
-    <row r="360" spans="1:6" ht="29.1">
+    <row r="360" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A360" t="s">
         <v>1445</v>
       </c>
@@ -20139,7 +20149,7 @@
         <v>4099400</v>
       </c>
     </row>
-    <row r="361" spans="1:6" ht="29.1">
+    <row r="361" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A361" t="s">
         <v>1449</v>
       </c>
@@ -20159,7 +20169,7 @@
         <v>4101664</v>
       </c>
     </row>
-    <row r="362" spans="1:6" ht="29.1">
+    <row r="362" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A362" t="s">
         <v>1453</v>
       </c>
@@ -20179,7 +20189,7 @@
         <v>4125828</v>
       </c>
     </row>
-    <row r="363" spans="1:6" ht="29.1">
+    <row r="363" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A363" t="s">
         <v>1457</v>
       </c>
@@ -20199,7 +20209,7 @@
         <v>4147620</v>
       </c>
     </row>
-    <row r="364" spans="1:6" ht="72.95">
+    <row r="364" spans="1:6" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A364" t="s">
         <v>1461</v>
       </c>
@@ -20219,7 +20229,7 @@
         <v>4178587</v>
       </c>
     </row>
-    <row r="365" spans="1:6" ht="29.1">
+    <row r="365" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A365" t="s">
         <v>1465</v>
       </c>
@@ -20239,7 +20249,7 @@
         <v>4193799</v>
       </c>
     </row>
-    <row r="366" spans="1:6" ht="43.7">
+    <row r="366" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A366" t="s">
         <v>1469</v>
       </c>
@@ -20259,7 +20269,7 @@
         <v>4210329</v>
       </c>
     </row>
-    <row r="367" spans="1:6">
+    <row r="367" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A367" t="s">
         <v>1473</v>
       </c>
@@ -20279,7 +20289,7 @@
         <v>4256809</v>
       </c>
     </row>
-    <row r="368" spans="1:6" ht="29.1">
+    <row r="368" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A368" t="s">
         <v>1477</v>
       </c>
@@ -20299,7 +20309,7 @@
         <v>4286692</v>
       </c>
     </row>
-    <row r="369" spans="1:6" ht="29.1">
+    <row r="369" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A369" t="s">
         <v>1481</v>
       </c>
@@ -20319,7 +20329,7 @@
         <v>4307628</v>
       </c>
     </row>
-    <row r="370" spans="1:6" ht="43.7">
+    <row r="370" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A370" t="s">
         <v>1485</v>
       </c>
@@ -20339,7 +20349,7 @@
         <v>4356925</v>
       </c>
     </row>
-    <row r="371" spans="1:6" ht="43.7">
+    <row r="371" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A371" t="s">
         <v>1489</v>
       </c>
@@ -20359,7 +20369,7 @@
         <v>4368535</v>
       </c>
     </row>
-    <row r="372" spans="1:6" ht="58.35">
+    <row r="372" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A372" t="s">
         <v>1493</v>
       </c>
@@ -20379,7 +20389,7 @@
         <v>4379154</v>
       </c>
     </row>
-    <row r="373" spans="1:6" ht="29.1">
+    <row r="373" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A373" t="s">
         <v>1497</v>
       </c>
@@ -20399,7 +20409,7 @@
         <v>4382945</v>
       </c>
     </row>
-    <row r="374" spans="1:6" ht="43.7">
+    <row r="374" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A374" t="s">
         <v>1501</v>
       </c>
@@ -20419,7 +20429,7 @@
         <v>4430520</v>
       </c>
     </row>
-    <row r="375" spans="1:6" ht="29.1">
+    <row r="375" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A375" t="s">
         <v>1505</v>
       </c>
@@ -20439,7 +20449,7 @@
         <v>4440899</v>
       </c>
     </row>
-    <row r="376" spans="1:6" ht="43.7">
+    <row r="376" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A376" t="s">
         <v>1509</v>
       </c>
@@ -20459,7 +20469,7 @@
         <v>4469680</v>
       </c>
     </row>
-    <row r="377" spans="1:6" ht="43.7">
+    <row r="377" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A377" t="s">
         <v>1513</v>
       </c>
@@ -20479,7 +20489,7 @@
         <v>4472382</v>
       </c>
     </row>
-    <row r="378" spans="1:6" ht="29.1">
+    <row r="378" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A378" t="s">
         <v>1517</v>
       </c>
@@ -20499,7 +20509,7 @@
         <v>4477233</v>
       </c>
     </row>
-    <row r="379" spans="1:6" ht="29.1">
+    <row r="379" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A379" t="s">
         <v>1521</v>
       </c>
@@ -20519,7 +20529,7 @@
         <v>4507299</v>
       </c>
     </row>
-    <row r="380" spans="1:6" ht="29.1">
+    <row r="380" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A380" t="s">
         <v>1525</v>
       </c>
@@ -20539,7 +20549,7 @@
         <v>4551016</v>
       </c>
     </row>
-    <row r="381" spans="1:6">
+    <row r="381" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A381" t="s">
         <v>1529</v>
       </c>
@@ -20559,7 +20569,7 @@
         <v>4572993</v>
       </c>
     </row>
-    <row r="382" spans="1:6" ht="29.1">
+    <row r="382" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A382" t="s">
         <v>1533</v>
       </c>
@@ -20579,7 +20589,7 @@
         <v>4588878</v>
       </c>
     </row>
-    <row r="383" spans="1:6" ht="43.7">
+    <row r="383" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A383" t="s">
         <v>1537</v>
       </c>
@@ -20599,7 +20609,7 @@
         <v>4589584</v>
       </c>
     </row>
-    <row r="384" spans="1:6" ht="43.7">
+    <row r="384" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A384" t="s">
         <v>1541</v>
       </c>
@@ -20619,7 +20629,7 @@
         <v>4602218</v>
       </c>
     </row>
-    <row r="385" spans="1:6" ht="43.7">
+    <row r="385" spans="1:6" ht="43.75" x14ac:dyDescent="0.4">
       <c r="A385" t="s">
         <v>1545</v>
       </c>
@@ -20639,7 +20649,7 @@
         <v>4637803</v>
       </c>
     </row>
-    <row r="386" spans="1:6" ht="58.35">
+    <row r="386" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A386" t="s">
         <v>1549</v>
       </c>
@@ -20659,7 +20669,7 @@
         <v>4639978</v>
       </c>
     </row>
-    <row r="387" spans="1:6" ht="29.1">
+    <row r="387" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A387" t="s">
         <v>1553</v>
       </c>
@@ -20679,7 +20689,7 @@
         <v>4654032</v>
       </c>
     </row>
-    <row r="388" spans="1:6" ht="43.7">
+    <row r="388" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A388" t="s">
         <v>1557</v>
       </c>
@@ -20699,7 +20709,7 @@
         <v>4670894</v>
       </c>
     </row>
-    <row r="389" spans="1:6" ht="29.1">
+    <row r="389" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A389" t="s">
         <v>1561</v>
       </c>
@@ -20719,7 +20729,7 @@
         <v>4702084</v>
       </c>
     </row>
-    <row r="390" spans="1:6" ht="43.7">
+    <row r="390" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A390" t="s">
         <v>1565</v>
       </c>
@@ -20739,7 +20749,7 @@
         <v>4714292</v>
       </c>
     </row>
-    <row r="391" spans="1:6" ht="43.7">
+    <row r="391" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A391" t="s">
         <v>1569</v>
       </c>
@@ -20759,7 +20769,7 @@
         <v>4722912</v>
       </c>
     </row>
-    <row r="392" spans="1:6" ht="43.7">
+    <row r="392" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A392" t="s">
         <v>1573</v>
       </c>
@@ -20779,7 +20789,7 @@
         <v>4749411</v>
       </c>
     </row>
-    <row r="393" spans="1:6" ht="29.1">
+    <row r="393" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A393" t="s">
         <v>1577</v>
       </c>
@@ -20799,7 +20809,7 @@
         <v>4768424</v>
       </c>
     </row>
-    <row r="394" spans="1:6" ht="43.7">
+    <row r="394" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A394" t="s">
         <v>1581</v>
       </c>
@@ -20819,7 +20829,7 @@
         <v>4781077</v>
       </c>
     </row>
-    <row r="395" spans="1:6" ht="29.1">
+    <row r="395" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A395" t="s">
         <v>1585</v>
       </c>
@@ -20839,7 +20849,7 @@
         <v>4792916</v>
       </c>
     </row>
-    <row r="396" spans="1:6" ht="43.7">
+    <row r="396" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A396" t="s">
         <v>1589</v>
       </c>
@@ -20859,7 +20869,7 @@
         <v>4794620</v>
       </c>
     </row>
-    <row r="397" spans="1:6" ht="29.1">
+    <row r="397" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A397" t="s">
         <v>1593</v>
       </c>
@@ -20879,7 +20889,7 @@
         <v>4817849</v>
       </c>
     </row>
-    <row r="398" spans="1:6" ht="29.1">
+    <row r="398" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A398" t="s">
         <v>1597</v>
       </c>
@@ -20899,7 +20909,7 @@
         <v>4834749</v>
       </c>
     </row>
-    <row r="399" spans="1:6" ht="29.1">
+    <row r="399" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A399" t="s">
         <v>1601</v>
       </c>
@@ -20919,7 +20929,7 @@
         <v>4847049</v>
       </c>
     </row>
-    <row r="400" spans="1:6" ht="43.7">
+    <row r="400" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A400" t="s">
         <v>1605</v>
       </c>
@@ -20939,7 +20949,7 @@
         <v>4896148</v>
       </c>
     </row>
-    <row r="401" spans="1:6" ht="29.1">
+    <row r="401" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A401" t="s">
         <v>1609</v>
       </c>
@@ -20959,7 +20969,7 @@
         <v>4906616</v>
       </c>
     </row>
-    <row r="402" spans="1:6" ht="58.35">
+    <row r="402" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A402" t="s">
         <v>1613</v>
       </c>
@@ -20979,7 +20989,7 @@
         <v>4921016</v>
       </c>
     </row>
-    <row r="403" spans="1:6" ht="29.1">
+    <row r="403" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A403" t="s">
         <v>1617</v>
       </c>
@@ -20999,7 +21009,7 @@
         <v>4938410</v>
       </c>
     </row>
-    <row r="404" spans="1:6" ht="29.1">
+    <row r="404" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A404" t="s">
         <v>1621</v>
       </c>
@@ -21019,7 +21029,7 @@
         <v>5002011</v>
       </c>
     </row>
-    <row r="405" spans="1:6" ht="29.1">
+    <row r="405" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A405" t="s">
         <v>1625</v>
       </c>
@@ -21039,7 +21049,7 @@
         <v>5012629</v>
       </c>
     </row>
-    <row r="406" spans="1:6" ht="29.1">
+    <row r="406" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A406" t="s">
         <v>1629</v>
       </c>
@@ -21059,7 +21069,7 @@
         <v>5023486</v>
       </c>
     </row>
-    <row r="407" spans="1:6" ht="43.7">
+    <row r="407" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A407" t="s">
         <v>1633</v>
       </c>
@@ -21079,7 +21089,7 @@
         <v>5029184</v>
       </c>
     </row>
-    <row r="408" spans="1:6" ht="29.1">
+    <row r="408" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A408" t="s">
         <v>1637</v>
       </c>
@@ -21099,7 +21109,7 @@
         <v>5102384</v>
       </c>
     </row>
-    <row r="409" spans="1:6" ht="58.35">
+    <row r="409" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A409" t="s">
         <v>1641</v>
       </c>
@@ -21119,7 +21129,7 @@
         <v>5102839</v>
       </c>
     </row>
-    <row r="410" spans="1:6" ht="116.65">
+    <row r="410" spans="1:6" ht="116.6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A410" t="s">
         <v>1645</v>
       </c>
@@ -21139,7 +21149,7 @@
         <v>5123416</v>
       </c>
     </row>
-    <row r="411" spans="1:6" ht="43.7">
+    <row r="411" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A411" t="s">
         <v>1649</v>
       </c>
@@ -21159,7 +21169,7 @@
         <v>5147178</v>
       </c>
     </row>
-    <row r="412" spans="1:6" ht="58.35">
+    <row r="412" spans="1:6" ht="58.3" x14ac:dyDescent="0.4">
       <c r="A412" t="s">
         <v>1653</v>
       </c>
@@ -21179,7 +21189,7 @@
         <v>5147365</v>
       </c>
     </row>
-    <row r="413" spans="1:6" ht="29.1">
+    <row r="413" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A413" t="s">
         <v>1657</v>
       </c>
@@ -21199,7 +21209,7 @@
         <v>5150111</v>
       </c>
     </row>
-    <row r="414" spans="1:6" ht="29.1">
+    <row r="414" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A414" t="s">
         <v>1661</v>
       </c>
@@ -21219,7 +21229,7 @@
         <v>5160736</v>
       </c>
     </row>
-    <row r="415" spans="1:6" ht="29.1">
+    <row r="415" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A415" t="s">
         <v>1665</v>
       </c>
@@ -21239,7 +21249,7 @@
         <v>5185368</v>
       </c>
     </row>
-    <row r="416" spans="1:6" ht="43.7">
+    <row r="416" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A416" t="s">
         <v>1669</v>
       </c>
@@ -21259,7 +21269,7 @@
         <v>5193179</v>
       </c>
     </row>
-    <row r="417" spans="1:6" ht="43.7">
+    <row r="417" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A417" t="s">
         <v>1673</v>
       </c>
@@ -21279,7 +21289,7 @@
         <v>5208092</v>
       </c>
     </row>
-    <row r="418" spans="1:6" ht="29.1">
+    <row r="418" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A418" t="s">
         <v>1677</v>
       </c>
@@ -21299,7 +21309,7 @@
         <v>5223999</v>
       </c>
     </row>
-    <row r="419" spans="1:6" ht="29.1">
+    <row r="419" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A419" t="s">
         <v>1681</v>
       </c>
@@ -21319,7 +21329,7 @@
         <v>5224621</v>
       </c>
     </row>
-    <row r="420" spans="1:6" ht="29.1">
+    <row r="420" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A420" t="s">
         <v>1685</v>
       </c>
@@ -21339,7 +21349,7 @@
         <v>5251603</v>
       </c>
     </row>
-    <row r="421" spans="1:6" ht="29.1">
+    <row r="421" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A421" t="s">
         <v>1689</v>
       </c>
@@ -21359,7 +21369,7 @@
         <v>5253268</v>
       </c>
     </row>
-    <row r="422" spans="1:6" ht="29.1">
+    <row r="422" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A422" t="s">
         <v>1693</v>
       </c>
@@ -21379,7 +21389,7 @@
         <v>5279317</v>
       </c>
     </row>
-    <row r="423" spans="1:6" ht="29.1">
+    <row r="423" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A423" t="s">
         <v>1697</v>
       </c>
@@ -21399,7 +21409,7 @@
         <v>5288880</v>
       </c>
     </row>
-    <row r="424" spans="1:6">
+    <row r="424" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A424" t="s">
         <v>1701</v>
       </c>
@@ -21419,7 +21429,7 @@
         <v>5296719</v>
       </c>
     </row>
-    <row r="425" spans="1:6" ht="29.1">
+    <row r="425" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A425" t="s">
         <v>1705</v>
       </c>
@@ -21439,7 +21449,7 @@
         <v>5343266</v>
       </c>
     </row>
-    <row r="426" spans="1:6" ht="29.1">
+    <row r="426" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A426" t="s">
         <v>1709</v>
       </c>
@@ -21459,7 +21469,7 @@
         <v>5415677</v>
       </c>
     </row>
-    <row r="427" spans="1:6" ht="29.1">
+    <row r="427" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A427" t="s">
         <v>1713</v>
       </c>
@@ -21479,7 +21489,7 @@
         <v>5416387</v>
       </c>
     </row>
-    <row r="428" spans="1:6" ht="29.1">
+    <row r="428" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A428" t="s">
         <v>1717</v>
       </c>
@@ -21499,7 +21509,7 @@
         <v>5448619</v>
       </c>
     </row>
-    <row r="429" spans="1:6" ht="29.1">
+    <row r="429" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A429" t="s">
         <v>1721</v>
       </c>
@@ -21519,7 +21529,7 @@
         <v>5567173</v>
       </c>
     </row>
-    <row r="430" spans="1:6" ht="29.1">
+    <row r="430" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A430" t="s">
         <v>1725</v>
       </c>
@@ -21539,7 +21549,7 @@
         <v>5578161</v>
       </c>
     </row>
-    <row r="431" spans="1:6" ht="29.1">
+    <row r="431" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A431" t="s">
         <v>1729</v>
       </c>
@@ -21559,7 +21569,7 @@
         <v>5623192</v>
       </c>
     </row>
-    <row r="432" spans="1:6" ht="29.1">
+    <row r="432" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A432" t="s">
         <v>1733</v>
       </c>
@@ -21579,7 +21589,7 @@
         <v>5661480</v>
       </c>
     </row>
-    <row r="433" spans="1:6">
+    <row r="433" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A433" t="s">
         <v>1737</v>
       </c>
@@ -21599,7 +21609,7 @@
         <v>5724256</v>
       </c>
     </row>
-    <row r="434" spans="1:6" ht="58.35">
+    <row r="434" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A434" t="s">
         <v>1741</v>
       </c>
@@ -21619,7 +21629,7 @@
         <v>5724624</v>
       </c>
     </row>
-    <row r="435" spans="1:6" ht="29.1">
+    <row r="435" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A435" t="s">
         <v>1745</v>
       </c>
@@ -21639,7 +21649,7 @@
         <v>5753144</v>
       </c>
     </row>
-    <row r="436" spans="1:6" ht="29.1">
+    <row r="436" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A436" t="s">
         <v>1749</v>
       </c>
@@ -21659,7 +21669,7 @@
         <v>5794671</v>
       </c>
     </row>
-    <row r="437" spans="1:6" ht="29.1">
+    <row r="437" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A437" t="s">
         <v>1753</v>
       </c>
@@ -21679,7 +21689,7 @@
         <v>5807045</v>
       </c>
     </row>
-    <row r="438" spans="1:6" ht="43.7">
+    <row r="438" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A438" t="s">
         <v>1757</v>
       </c>
@@ -21699,7 +21709,7 @@
         <v>5817678</v>
       </c>
     </row>
-    <row r="439" spans="1:6" ht="58.35">
+    <row r="439" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A439" t="s">
         <v>1761</v>
       </c>
@@ -21719,7 +21729,7 @@
         <v>5825191</v>
       </c>
     </row>
-    <row r="440" spans="1:6" ht="43.7">
+    <row r="440" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A440" t="s">
         <v>1765</v>
       </c>
@@ -21739,7 +21749,7 @@
         <v>5828509</v>
       </c>
     </row>
-    <row r="441" spans="1:6">
+    <row r="441" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A441" t="s">
         <v>1769</v>
       </c>
@@ -21759,7 +21769,7 @@
         <v>5866946</v>
       </c>
     </row>
-    <row r="442" spans="1:6" ht="58.35">
+    <row r="442" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A442" t="s">
         <v>1773</v>
       </c>
@@ -21779,7 +21789,7 @@
         <v>5871198</v>
       </c>
     </row>
-    <row r="443" spans="1:6">
+    <row r="443" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A443" t="s">
         <v>1777</v>
       </c>
@@ -21799,7 +21809,7 @@
         <v>5872912</v>
       </c>
     </row>
-    <row r="444" spans="1:6" ht="29.1">
+    <row r="444" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A444" t="s">
         <v>1781</v>
       </c>
@@ -21819,7 +21829,7 @@
         <v>5877157</v>
       </c>
     </row>
-    <row r="445" spans="1:6" ht="43.7">
+    <row r="445" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A445" t="s">
         <v>1785</v>
       </c>
@@ -21839,7 +21849,7 @@
         <v>5881286</v>
       </c>
     </row>
-    <row r="446" spans="1:6" ht="29.1">
+    <row r="446" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A446" t="s">
         <v>1789</v>
       </c>
@@ -21859,7 +21869,7 @@
         <v>5886898</v>
       </c>
     </row>
-    <row r="447" spans="1:6" ht="43.7">
+    <row r="447" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A447" t="s">
         <v>1793</v>
       </c>
@@ -21879,7 +21889,7 @@
         <v>5889108</v>
       </c>
     </row>
-    <row r="448" spans="1:6" ht="29.1">
+    <row r="448" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A448" t="s">
         <v>1797</v>
       </c>
@@ -21899,7 +21909,7 @@
         <v>5920564</v>
       </c>
     </row>
-    <row r="449" spans="1:6" ht="29.1">
+    <row r="449" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A449" t="s">
         <v>1801</v>
       </c>
@@ -21919,7 +21929,7 @@
         <v>5923693</v>
       </c>
     </row>
-    <row r="450" spans="1:6" ht="58.35">
+    <row r="450" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A450" t="s">
         <v>1805</v>
       </c>
@@ -21939,7 +21949,7 @@
         <v>5936678</v>
       </c>
     </row>
-    <row r="451" spans="1:6" ht="43.7">
+    <row r="451" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A451" t="s">
         <v>1809</v>
       </c>
@@ -21959,7 +21969,7 @@
         <v>5943229</v>
       </c>
     </row>
-    <row r="452" spans="1:6" ht="58.35">
+    <row r="452" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A452" t="s">
         <v>1813</v>
       </c>
@@ -21979,7 +21989,7 @@
         <v>5950400</v>
       </c>
     </row>
-    <row r="453" spans="1:6" ht="29.1">
+    <row r="453" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A453" t="s">
         <v>1817</v>
       </c>
@@ -21999,7 +22009,7 @@
         <v>5968319</v>
       </c>
     </row>
-    <row r="454" spans="1:6" ht="29.1">
+    <row r="454" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A454" t="s">
         <v>1821</v>
       </c>
@@ -22019,7 +22029,7 @@
         <v>5979417</v>
       </c>
     </row>
-    <row r="455" spans="1:6">
+    <row r="455" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A455" t="s">
         <v>1825</v>
       </c>
@@ -22039,7 +22049,7 @@
         <v>5981319</v>
       </c>
     </row>
-    <row r="456" spans="1:6" ht="43.7">
+    <row r="456" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A456" t="s">
         <v>1829</v>
       </c>
@@ -22059,7 +22069,7 @@
         <v>5983095</v>
       </c>
     </row>
-    <row r="457" spans="1:6" ht="29.1">
+    <row r="457" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A457" t="s">
         <v>1833</v>
       </c>
@@ -22079,7 +22089,7 @@
         <v>6006841</v>
       </c>
     </row>
-    <row r="458" spans="1:6" ht="58.35">
+    <row r="458" spans="1:6" ht="58.3" x14ac:dyDescent="0.4">
       <c r="A458" t="s">
         <v>1837</v>
       </c>
@@ -22099,7 +22109,7 @@
         <v>6028080</v>
       </c>
     </row>
-    <row r="459" spans="1:6" ht="58.35">
+    <row r="459" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A459" t="s">
         <v>1841</v>
       </c>
@@ -22119,7 +22129,7 @@
         <v>6093394</v>
       </c>
     </row>
-    <row r="460" spans="1:6" ht="43.7">
+    <row r="460" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A460" t="s">
         <v>1845</v>
       </c>
@@ -22139,7 +22149,7 @@
         <v>6096994</v>
       </c>
     </row>
-    <row r="461" spans="1:6" ht="29.1">
+    <row r="461" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A461" t="s">
         <v>1849</v>
       </c>
@@ -22159,7 +22169,7 @@
         <v>6103148</v>
       </c>
     </row>
-    <row r="462" spans="1:6" ht="43.7">
+    <row r="462" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A462" t="s">
         <v>1853</v>
       </c>
@@ -22179,7 +22189,7 @@
         <v>6138817</v>
       </c>
     </row>
-    <row r="463" spans="1:6" ht="43.7">
+    <row r="463" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A463" t="s">
         <v>1857</v>
       </c>
@@ -22199,7 +22209,7 @@
         <v>6159028</v>
       </c>
     </row>
-    <row r="464" spans="1:6" ht="29.1">
+    <row r="464" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A464" t="s">
         <v>1861</v>
       </c>
@@ -22219,7 +22229,7 @@
         <v>6164457</v>
       </c>
     </row>
-    <row r="465" spans="1:6" ht="29.1">
+    <row r="465" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A465" t="s">
         <v>1865</v>
       </c>
@@ -22239,7 +22249,7 @@
         <v>6168820</v>
       </c>
     </row>
-    <row r="466" spans="1:6" ht="29.1">
+    <row r="466" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A466" t="s">
         <v>1869</v>
       </c>
@@ -22259,7 +22269,7 @@
         <v>6193115</v>
       </c>
     </row>
-    <row r="467" spans="1:6" ht="43.7">
+    <row r="467" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A467" t="s">
         <v>1873</v>
       </c>
@@ -22279,7 +22289,7 @@
         <v>6207675</v>
       </c>
     </row>
-    <row r="468" spans="1:6" ht="29.1">
+    <row r="468" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A468" t="s">
         <v>1877</v>
       </c>
@@ -22299,7 +22309,7 @@
         <v>6284528</v>
       </c>
     </row>
-    <row r="469" spans="1:6" ht="29.1">
+    <row r="469" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A469" t="s">
         <v>1881</v>
       </c>
@@ -22319,7 +22329,7 @@
         <v>6292763</v>
       </c>
     </row>
-    <row r="470" spans="1:6" ht="29.1">
+    <row r="470" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A470" t="s">
         <v>1885</v>
       </c>
@@ -22339,7 +22349,7 @@
         <v>6312475</v>
       </c>
     </row>
-    <row r="471" spans="1:6" ht="29.1">
+    <row r="471" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A471" t="s">
         <v>1889</v>
       </c>
@@ -22359,7 +22369,7 @@
         <v>6359294</v>
       </c>
     </row>
-    <row r="472" spans="1:6" ht="29.1">
+    <row r="472" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A472" t="s">
         <v>1893</v>
       </c>
@@ -22379,7 +22389,7 @@
         <v>6386469</v>
       </c>
     </row>
-    <row r="473" spans="1:6" ht="29.1">
+    <row r="473" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A473" t="s">
         <v>1897</v>
       </c>
@@ -22399,7 +22409,7 @@
         <v>6413610</v>
       </c>
     </row>
-    <row r="474" spans="1:6" ht="43.7">
+    <row r="474" spans="1:6" ht="43.75" x14ac:dyDescent="0.4">
       <c r="A474" t="s">
         <v>1901</v>
       </c>
@@ -22419,7 +22429,7 @@
         <v>6506456</v>
       </c>
     </row>
-    <row r="475" spans="1:6" ht="58.35">
+    <row r="475" spans="1:6" ht="58.3" x14ac:dyDescent="0.4">
       <c r="A475" t="s">
         <v>1905</v>
       </c>
@@ -22439,7 +22449,7 @@
         <v>6512378</v>
       </c>
     </row>
-    <row r="476" spans="1:6" ht="29.1">
+    <row r="476" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A476" t="s">
         <v>1909</v>
       </c>
@@ -22459,7 +22469,7 @@
         <v>6528430</v>
       </c>
     </row>
-    <row r="477" spans="1:6" ht="29.1">
+    <row r="477" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A477" t="s">
         <v>1913</v>
       </c>
@@ -22479,7 +22489,7 @@
         <v>6554024</v>
       </c>
     </row>
-    <row r="478" spans="1:6" ht="29.1">
+    <row r="478" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A478" t="s">
         <v>1917</v>
       </c>
@@ -22499,7 +22509,7 @@
         <v>6587373</v>
       </c>
     </row>
-    <row r="479" spans="1:6" ht="29.1">
+    <row r="479" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A479" t="s">
         <v>1921</v>
       </c>
@@ -22519,7 +22529,7 @@
         <v>6592790</v>
       </c>
     </row>
-    <row r="480" spans="1:6" ht="29.1">
+    <row r="480" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A480" t="s">
         <v>1925</v>
       </c>
@@ -22539,7 +22549,7 @@
         <v>6613743</v>
       </c>
     </row>
-    <row r="481" spans="1:6" ht="43.7">
+    <row r="481" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A481" t="s">
         <v>1929</v>
       </c>
@@ -22559,7 +22569,7 @@
         <v>6617067</v>
       </c>
     </row>
-    <row r="482" spans="1:6">
+    <row r="482" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A482" t="s">
         <v>1933</v>
       </c>
@@ -22579,7 +22589,7 @@
         <v>6625905</v>
       </c>
     </row>
-    <row r="483" spans="1:6" ht="29.1">
+    <row r="483" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A483" t="s">
         <v>1937</v>
       </c>
@@ -22599,7 +22609,7 @@
         <v>6630756</v>
       </c>
     </row>
-    <row r="484" spans="1:6">
+    <row r="484" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A484" t="s">
         <v>1941</v>
       </c>
@@ -22619,7 +22629,7 @@
         <v>6635881</v>
       </c>
     </row>
-    <row r="485" spans="1:6" ht="29.1">
+    <row r="485" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A485" t="s">
         <v>1945</v>
       </c>
@@ -22639,7 +22649,7 @@
         <v>6664516</v>
       </c>
     </row>
-    <row r="486" spans="1:6" ht="43.7">
+    <row r="486" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A486" t="s">
         <v>1949</v>
       </c>
@@ -22659,7 +22669,7 @@
         <v>6783471</v>
       </c>
     </row>
-    <row r="487" spans="1:6" ht="72.95">
+    <row r="487" spans="1:6" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A487" t="s">
         <v>1953</v>
       </c>
@@ -22679,7 +22689,7 @@
         <v>6803691</v>
       </c>
     </row>
-    <row r="488" spans="1:6" ht="29.1">
+    <row r="488" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A488" t="s">
         <v>1957</v>
       </c>
@@ -22699,7 +22709,7 @@
         <v>6823646</v>
       </c>
     </row>
-    <row r="489" spans="1:6" ht="43.7">
+    <row r="489" spans="1:6" ht="43.75" x14ac:dyDescent="0.4">
       <c r="A489" t="s">
         <v>1961</v>
       </c>
@@ -22719,7 +22729,7 @@
         <v>6833439</v>
       </c>
     </row>
-    <row r="490" spans="1:6" ht="29.1">
+    <row r="490" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A490" t="s">
         <v>1965</v>
       </c>
@@ -22739,7 +22749,7 @@
         <v>6835095</v>
       </c>
     </row>
-    <row r="491" spans="1:6" ht="29.1">
+    <row r="491" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A491" t="s">
         <v>1969</v>
       </c>
@@ -22759,7 +22769,7 @@
         <v>6841265</v>
       </c>
     </row>
-    <row r="492" spans="1:6" ht="72.95">
+    <row r="492" spans="1:6" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A492" t="s">
         <v>1973</v>
       </c>
@@ -22779,7 +22789,7 @@
         <v>6878663</v>
       </c>
     </row>
-    <row r="493" spans="1:6">
+    <row r="493" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A493" t="s">
         <v>1977</v>
       </c>
@@ -22799,7 +22809,7 @@
         <v>6886947</v>
       </c>
     </row>
-    <row r="494" spans="1:6" ht="29.1">
+    <row r="494" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A494" t="s">
         <v>1981</v>
       </c>
@@ -22819,7 +22829,7 @@
         <v>6912777</v>
       </c>
     </row>
-    <row r="495" spans="1:6" ht="29.1">
+    <row r="495" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A495" t="s">
         <v>1985</v>
       </c>
@@ -22839,7 +22849,7 @@
         <v>6924492</v>
       </c>
     </row>
-    <row r="496" spans="1:6" ht="43.7">
+    <row r="496" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A496" t="s">
         <v>1989</v>
       </c>
@@ -22859,7 +22869,7 @@
         <v>6961175</v>
       </c>
     </row>
-    <row r="497" spans="1:6" ht="43.7">
+    <row r="497" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A497" t="s">
         <v>1993</v>
       </c>
@@ -22879,7 +22889,7 @@
         <v>6962572</v>
       </c>
     </row>
-    <row r="498" spans="1:6" ht="29.1">
+    <row r="498" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A498" t="s">
         <v>1997</v>
       </c>
@@ -22899,7 +22909,7 @@
         <v>7004365</v>
       </c>
     </row>
-    <row r="499" spans="1:6">
+    <row r="499" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A499" t="s">
         <v>2001</v>
       </c>
@@ -22919,7 +22929,7 @@
         <v>7008078</v>
       </c>
     </row>
-    <row r="500" spans="1:6" ht="29.1">
+    <row r="500" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A500" t="s">
         <v>2005</v>
       </c>
@@ -22939,7 +22949,7 @@
         <v>7026002</v>
       </c>
     </row>
-    <row r="501" spans="1:6">
+    <row r="501" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A501" t="s">
         <v>2009</v>
       </c>
@@ -22959,7 +22969,7 @@
         <v>7043686</v>
       </c>
     </row>
-    <row r="502" spans="1:6" ht="72.95">
+    <row r="502" spans="1:6" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A502" t="s">
         <v>2013</v>
       </c>
@@ -22979,7 +22989,7 @@
         <v>7049812</v>
       </c>
     </row>
-    <row r="503" spans="1:6">
+    <row r="503" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A503" t="s">
         <v>2017</v>
       </c>
@@ -22999,7 +23009,7 @@
         <v>7063096</v>
       </c>
     </row>
-    <row r="504" spans="1:6" ht="43.7">
+    <row r="504" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A504" t="s">
         <v>2021</v>
       </c>
@@ -23019,7 +23029,7 @@
         <v>7073277</v>
       </c>
     </row>
-    <row r="505" spans="1:6" ht="29.1">
+    <row r="505" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A505" t="s">
         <v>2025</v>
       </c>
@@ -23039,7 +23049,7 @@
         <v>7077786</v>
       </c>
     </row>
-    <row r="506" spans="1:6">
+    <row r="506" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A506" t="s">
         <v>2029</v>
       </c>
@@ -23059,7 +23069,7 @@
         <v>7081319</v>
       </c>
     </row>
-    <row r="507" spans="1:6">
+    <row r="507" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A507" t="s">
         <v>2033</v>
       </c>
@@ -23079,7 +23089,7 @@
         <v>7081495</v>
       </c>
     </row>
-    <row r="508" spans="1:6" ht="29.1">
+    <row r="508" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A508" t="s">
         <v>2036</v>
       </c>
@@ -23099,7 +23109,7 @@
         <v>7081568</v>
       </c>
     </row>
-    <row r="509" spans="1:6" ht="29.1">
+    <row r="509" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A509" t="s">
         <v>2040</v>
       </c>
@@ -23119,7 +23129,7 @@
         <v>7083995</v>
       </c>
     </row>
-    <row r="510" spans="1:6">
+    <row r="510" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A510" t="s">
         <v>2044</v>
       </c>
@@ -23139,7 +23149,7 @@
         <v>7097949</v>
       </c>
     </row>
-    <row r="511" spans="1:6" ht="29.1">
+    <row r="511" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A511" t="s">
         <v>2048</v>
       </c>
@@ -23159,7 +23169,7 @@
         <v>7120442</v>
       </c>
     </row>
-    <row r="512" spans="1:6" ht="29.1">
+    <row r="512" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A512" t="s">
         <v>2052</v>
       </c>
@@ -23179,7 +23189,7 @@
         <v>7126236</v>
       </c>
     </row>
-    <row r="513" spans="1:6">
+    <row r="513" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A513" t="s">
         <v>2056</v>
       </c>
@@ -23199,7 +23209,7 @@
         <v>7127240</v>
       </c>
     </row>
-    <row r="514" spans="1:6" ht="29.1">
+    <row r="514" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A514" t="s">
         <v>2060</v>
       </c>
@@ -23219,7 +23229,7 @@
         <v>7135846</v>
       </c>
     </row>
-    <row r="515" spans="1:6" ht="29.1">
+    <row r="515" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A515" t="s">
         <v>2064</v>
       </c>
@@ -23239,7 +23249,7 @@
         <v>7137364</v>
       </c>
     </row>
-    <row r="516" spans="1:6" ht="58.35">
+    <row r="516" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A516" t="s">
         <v>2068</v>
       </c>
@@ -23259,7 +23269,7 @@
         <v>7143464</v>
       </c>
     </row>
-    <row r="517" spans="1:6" ht="58.35">
+    <row r="517" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A517" t="s">
         <v>2072</v>
       </c>
@@ -23279,7 +23289,7 @@
         <v>7148644</v>
       </c>
     </row>
-    <row r="518" spans="1:6" ht="29.1">
+    <row r="518" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A518" t="s">
         <v>2076</v>
       </c>
@@ -23299,7 +23309,7 @@
         <v>7156345</v>
       </c>
     </row>
-    <row r="519" spans="1:6" ht="43.7">
+    <row r="519" spans="1:6" ht="43.75" x14ac:dyDescent="0.4">
       <c r="A519" t="s">
         <v>2080</v>
       </c>
@@ -23319,7 +23329,7 @@
         <v>7163784</v>
       </c>
     </row>
-    <row r="520" spans="1:6" ht="43.7">
+    <row r="520" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A520" t="s">
         <v>2084</v>
       </c>
@@ -23339,7 +23349,7 @@
         <v>7206108</v>
       </c>
     </row>
-    <row r="521" spans="1:6" ht="43.7">
+    <row r="521" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A521" t="s">
         <v>2088</v>
       </c>
@@ -23359,7 +23369,7 @@
         <v>7341585</v>
       </c>
     </row>
-    <row r="522" spans="1:6" ht="29.1">
+    <row r="522" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A522" t="s">
         <v>2092</v>
       </c>
@@ -23379,7 +23389,7 @@
         <v>7341811</v>
       </c>
     </row>
-    <row r="523" spans="1:6" ht="43.7">
+    <row r="523" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A523" t="s">
         <v>2096</v>
       </c>
@@ -23399,7 +23409,7 @@
         <v>7384749</v>
       </c>
     </row>
-    <row r="524" spans="1:6" ht="29.1">
+    <row r="524" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A524" t="s">
         <v>2100</v>
       </c>
@@ -23419,7 +23429,7 @@
         <v>7390103</v>
       </c>
     </row>
-    <row r="525" spans="1:6" ht="102">
+    <row r="525" spans="1:6" ht="102" hidden="1" x14ac:dyDescent="0.4">
       <c r="A525" t="s">
         <v>2104</v>
       </c>
@@ -23439,7 +23449,7 @@
         <v>7398201</v>
       </c>
     </row>
-    <row r="526" spans="1:6" ht="29.1">
+    <row r="526" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A526" t="s">
         <v>2108</v>
       </c>
@@ -23459,7 +23469,7 @@
         <v>7398898</v>
       </c>
     </row>
-    <row r="527" spans="1:6">
+    <row r="527" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A527" t="s">
         <v>2112</v>
       </c>
@@ -23479,7 +23489,7 @@
         <v>7411106</v>
       </c>
     </row>
-    <row r="528" spans="1:6" ht="29.1">
+    <row r="528" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A528" t="s">
         <v>2116</v>
       </c>
@@ -23499,7 +23509,7 @@
         <v>7453329</v>
       </c>
     </row>
-    <row r="529" spans="1:6" ht="43.7">
+    <row r="529" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A529" t="s">
         <v>2120</v>
       </c>
@@ -23519,7 +23529,7 @@
         <v>7476620</v>
       </c>
     </row>
-    <row r="530" spans="1:6" ht="29.1">
+    <row r="530" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A530" t="s">
         <v>2124</v>
       </c>
@@ -23539,7 +23549,7 @@
         <v>7482201</v>
       </c>
     </row>
-    <row r="531" spans="1:6" ht="29.1">
+    <row r="531" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A531" t="s">
         <v>2128</v>
       </c>
@@ -23559,7 +23569,7 @@
         <v>7496895</v>
       </c>
     </row>
-    <row r="532" spans="1:6" ht="29.1">
+    <row r="532" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A532" t="s">
         <v>2132</v>
       </c>
@@ -23579,7 +23589,7 @@
         <v>7496979</v>
       </c>
     </row>
-    <row r="533" spans="1:6">
+    <row r="533" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A533" t="s">
         <v>2136</v>
       </c>
@@ -23599,7 +23609,7 @@
         <v>7531956</v>
       </c>
     </row>
-    <row r="534" spans="1:6" ht="29.1">
+    <row r="534" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A534" t="s">
         <v>2140</v>
       </c>
@@ -23619,7 +23629,7 @@
         <v>7537221</v>
       </c>
     </row>
-    <row r="535" spans="1:6">
+    <row r="535" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A535" t="s">
         <v>2144</v>
       </c>
@@ -23639,7 +23649,7 @@
         <v>7541190</v>
       </c>
     </row>
-    <row r="536" spans="1:6" ht="43.7">
+    <row r="536" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A536" t="s">
         <v>2148</v>
       </c>
@@ -23659,7 +23669,7 @@
         <v>7561016</v>
       </c>
     </row>
-    <row r="537" spans="1:6" ht="29.1">
+    <row r="537" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A537" t="s">
         <v>2152</v>
       </c>
@@ -23679,7 +23689,7 @@
         <v>7624507</v>
       </c>
     </row>
-    <row r="538" spans="1:6">
+    <row r="538" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A538" t="s">
         <v>2156</v>
       </c>
@@ -23699,7 +23709,7 @@
         <v>7685420</v>
       </c>
     </row>
-    <row r="539" spans="1:6" ht="29.1">
+    <row r="539" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A539" t="s">
         <v>2160</v>
       </c>
@@ -23719,7 +23729,7 @@
         <v>7704612</v>
       </c>
     </row>
-    <row r="540" spans="1:6" ht="29.1">
+    <row r="540" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A540" t="s">
         <v>2164</v>
       </c>
@@ -23739,7 +23749,7 @@
         <v>7729504</v>
       </c>
     </row>
-    <row r="541" spans="1:6" ht="174.95">
+    <row r="541" spans="1:6" ht="174.9" hidden="1" x14ac:dyDescent="0.4">
       <c r="A541" t="s">
         <v>2168</v>
       </c>
@@ -23759,7 +23769,7 @@
         <v>7730401</v>
       </c>
     </row>
-    <row r="542" spans="1:6" ht="29.1">
+    <row r="542" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A542" t="s">
         <v>2172</v>
       </c>
@@ -23779,7 +23789,7 @@
         <v>7731837</v>
       </c>
     </row>
-    <row r="543" spans="1:6" ht="29.1">
+    <row r="543" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A543" t="s">
         <v>2176</v>
       </c>
@@ -23799,7 +23809,7 @@
         <v>7743942</v>
       </c>
     </row>
-    <row r="544" spans="1:6" ht="29.1">
+    <row r="544" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A544" t="s">
         <v>2180</v>
       </c>
@@ -23819,7 +23829,7 @@
         <v>7743942</v>
       </c>
     </row>
-    <row r="545" spans="1:6" ht="29.1">
+    <row r="545" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A545" t="s">
         <v>2182</v>
       </c>
@@ -23839,7 +23849,7 @@
         <v>7769409</v>
       </c>
     </row>
-    <row r="546" spans="1:6">
+    <row r="546" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A546" t="s">
         <v>2186</v>
       </c>
@@ -23859,7 +23869,7 @@
         <v>7784278</v>
       </c>
     </row>
-    <row r="547" spans="1:6" ht="29.1">
+    <row r="547" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A547" t="s">
         <v>2190</v>
       </c>
@@ -23879,7 +23889,7 @@
         <v>7857182</v>
       </c>
     </row>
-    <row r="548" spans="1:6" ht="43.7">
+    <row r="548" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A548" t="s">
         <v>2194</v>
       </c>
@@ -23899,7 +23909,7 @@
         <v>7875987</v>
       </c>
     </row>
-    <row r="549" spans="1:6" ht="43.7">
+    <row r="549" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A549" t="s">
         <v>2198</v>
       </c>
@@ -23919,7 +23929,7 @@
         <v>7905075</v>
       </c>
     </row>
-    <row r="550" spans="1:6" ht="29.1">
+    <row r="550" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A550" t="s">
         <v>2202</v>
       </c>
@@ -23939,7 +23949,7 @@
         <v>7916146</v>
       </c>
     </row>
-    <row r="551" spans="1:6" ht="29.1">
+    <row r="551" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A551" t="s">
         <v>2206</v>
       </c>
@@ -23959,7 +23969,7 @@
         <v>7920604</v>
       </c>
     </row>
-    <row r="552" spans="1:6">
+    <row r="552" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A552" t="s">
         <v>2210</v>
       </c>
@@ -23979,7 +23989,7 @@
         <v>7927880</v>
       </c>
     </row>
-    <row r="553" spans="1:6">
+    <row r="553" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A553" t="s">
         <v>2214</v>
       </c>
@@ -23999,7 +24009,7 @@
         <v>7930993</v>
       </c>
     </row>
-    <row r="554" spans="1:6">
+    <row r="554" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A554" t="s">
         <v>2218</v>
       </c>
@@ -24019,7 +24029,7 @@
         <v>7935917</v>
       </c>
     </row>
-    <row r="555" spans="1:6" ht="29.1">
+    <row r="555" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A555" t="s">
         <v>2221</v>
       </c>
@@ -24039,7 +24049,7 @@
         <v>7948047</v>
       </c>
     </row>
-    <row r="556" spans="1:6">
+    <row r="556" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A556" t="s">
         <v>2225</v>
       </c>
@@ -24059,7 +24069,7 @@
         <v>7952568</v>
       </c>
     </row>
-    <row r="557" spans="1:6">
+    <row r="557" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A557" t="s">
         <v>2229</v>
       </c>
@@ -24079,7 +24089,7 @@
         <v>7953659</v>
       </c>
     </row>
-    <row r="558" spans="1:6" ht="29.1">
+    <row r="558" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A558" t="s">
         <v>2233</v>
       </c>
@@ -24099,7 +24109,7 @@
         <v>7968143</v>
       </c>
     </row>
-    <row r="559" spans="1:6" ht="29.1">
+    <row r="559" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A559" t="s">
         <v>2237</v>
       </c>
@@ -24119,7 +24129,7 @@
         <v>8026990</v>
       </c>
     </row>
-    <row r="560" spans="1:6" ht="29.1">
+    <row r="560" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A560" t="s">
         <v>2241</v>
       </c>
@@ -24139,7 +24149,7 @@
         <v>8030430</v>
       </c>
     </row>
-    <row r="561" spans="1:6" ht="43.7">
+    <row r="561" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A561" t="s">
         <v>2245</v>
       </c>
@@ -24159,7 +24169,7 @@
         <v>8051038</v>
       </c>
     </row>
-    <row r="562" spans="1:6" ht="43.7">
+    <row r="562" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A562" t="s">
         <v>2249</v>
       </c>
@@ -24179,7 +24189,7 @@
         <v>8098545</v>
       </c>
     </row>
-    <row r="563" spans="1:6" ht="43.7">
+    <row r="563" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A563" t="s">
         <v>2253</v>
       </c>
@@ -24199,7 +24209,7 @@
         <v>8122306</v>
       </c>
     </row>
-    <row r="564" spans="1:6">
+    <row r="564" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A564" t="s">
         <v>2257</v>
       </c>
@@ -24219,7 +24229,7 @@
         <v>8191348</v>
       </c>
     </row>
-    <row r="565" spans="1:6" ht="29.1">
+    <row r="565" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A565" t="s">
         <v>2261</v>
       </c>
@@ -24239,7 +24249,7 @@
         <v>8211413</v>
       </c>
     </row>
-    <row r="566" spans="1:6" ht="29.1">
+    <row r="566" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A566" t="s">
         <v>2265</v>
       </c>
@@ -24259,7 +24269,7 @@
         <v>8213045</v>
       </c>
     </row>
-    <row r="567" spans="1:6" ht="29.1">
+    <row r="567" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A567" t="s">
         <v>2269</v>
       </c>
@@ -24279,7 +24289,7 @@
         <v>8213207</v>
       </c>
     </row>
-    <row r="568" spans="1:6" ht="43.7">
+    <row r="568" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A568" t="s">
         <v>2273</v>
       </c>
@@ -24299,7 +24309,7 @@
         <v>8225208</v>
       </c>
     </row>
-    <row r="569" spans="1:6" ht="29.1">
+    <row r="569" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A569" t="s">
         <v>2277</v>
       </c>
@@ -24319,7 +24329,7 @@
         <v>8254418</v>
       </c>
     </row>
-    <row r="570" spans="1:6">
+    <row r="570" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A570" t="s">
         <v>2281</v>
       </c>
@@ -24339,7 +24349,7 @@
         <v>8265209</v>
       </c>
     </row>
-    <row r="571" spans="1:6" ht="29.1">
+    <row r="571" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A571" t="s">
         <v>2285</v>
       </c>
@@ -24359,7 +24369,7 @@
         <v>8266046</v>
       </c>
     </row>
-    <row r="572" spans="1:6" ht="29.1">
+    <row r="572" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A572" t="s">
         <v>2289</v>
       </c>
@@ -24379,7 +24389,7 @@
         <v>8272137</v>
       </c>
     </row>
-    <row r="573" spans="1:6">
+    <row r="573" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A573" t="s">
         <v>2293</v>
       </c>
@@ -24399,7 +24409,7 @@
         <v>8309535</v>
       </c>
     </row>
-    <row r="574" spans="1:6" ht="29.1">
+    <row r="574" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A574" t="s">
         <v>2297</v>
       </c>
@@ -24419,7 +24429,7 @@
         <v>8366453</v>
       </c>
     </row>
-    <row r="575" spans="1:6" ht="29.1">
+    <row r="575" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A575" t="s">
         <v>2301</v>
       </c>
@@ -24439,7 +24449,7 @@
         <v>8376696</v>
       </c>
     </row>
-    <row r="576" spans="1:6" ht="29.1">
+    <row r="576" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A576" t="s">
         <v>2305</v>
       </c>
@@ -24459,7 +24469,7 @@
         <v>8378681</v>
       </c>
     </row>
-    <row r="577" spans="1:6" ht="116.65">
+    <row r="577" spans="1:6" ht="116.6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A577" t="s">
         <v>2309</v>
       </c>
@@ -24479,7 +24489,7 @@
         <v>8429134</v>
       </c>
     </row>
-    <row r="578" spans="1:6" ht="29.1">
+    <row r="578" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A578" t="s">
         <v>2313</v>
       </c>
@@ -24499,7 +24509,7 @@
         <v>8505853</v>
       </c>
     </row>
-    <row r="579" spans="1:6" ht="29.1">
+    <row r="579" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A579" t="s">
         <v>2317</v>
       </c>
@@ -24519,7 +24529,7 @@
         <v>8522323</v>
       </c>
     </row>
-    <row r="580" spans="1:6" ht="58.35">
+    <row r="580" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A580" t="s">
         <v>2321</v>
       </c>
@@ -24539,7 +24549,7 @@
         <v>8522799</v>
       </c>
     </row>
-    <row r="581" spans="1:6" ht="43.7">
+    <row r="581" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A581" t="s">
         <v>2325</v>
       </c>
@@ -24559,7 +24569,7 @@
         <v>8532508</v>
       </c>
     </row>
-    <row r="582" spans="1:6" ht="29.1">
+    <row r="582" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A582" t="s">
         <v>2329</v>
       </c>
@@ -24579,7 +24589,7 @@
         <v>8556548</v>
       </c>
     </row>
-    <row r="583" spans="1:6" ht="29.1">
+    <row r="583" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A583" t="s">
         <v>2333</v>
       </c>
@@ -24599,7 +24609,7 @@
         <v>8593731</v>
       </c>
     </row>
-    <row r="584" spans="1:6" ht="43.7">
+    <row r="584" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A584" t="s">
         <v>2337</v>
       </c>
@@ -24619,7 +24629,7 @@
         <v>8593985</v>
       </c>
     </row>
-    <row r="585" spans="1:6" ht="29.1">
+    <row r="585" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A585" t="s">
         <v>2341</v>
       </c>
@@ -24639,7 +24649,7 @@
         <v>8600345</v>
       </c>
     </row>
-    <row r="586" spans="1:6" ht="29.1">
+    <row r="586" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A586" t="s">
         <v>2345</v>
       </c>
@@ -24659,7 +24669,7 @@
         <v>8614718</v>
       </c>
     </row>
-    <row r="587" spans="1:6" ht="29.1">
+    <row r="587" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A587" t="s">
         <v>2349</v>
       </c>
@@ -24679,7 +24689,7 @@
         <v>8617677</v>
       </c>
     </row>
-    <row r="588" spans="1:6" ht="43.7">
+    <row r="588" spans="1:6" ht="43.75" x14ac:dyDescent="0.4">
       <c r="A588" t="s">
         <v>2353</v>
       </c>
@@ -24699,7 +24709,7 @@
         <v>8626159</v>
       </c>
     </row>
-    <row r="589" spans="1:6" ht="29.1">
+    <row r="589" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A589" t="s">
         <v>2357</v>
       </c>
@@ -24719,7 +24729,7 @@
         <v>8657783</v>
       </c>
     </row>
-    <row r="590" spans="1:6" ht="29.1">
+    <row r="590" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A590" t="s">
         <v>2361</v>
       </c>
@@ -24739,7 +24749,7 @@
         <v>8658550</v>
       </c>
     </row>
-    <row r="591" spans="1:6" ht="29.1">
+    <row r="591" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A591" t="s">
         <v>2365</v>
       </c>
@@ -24759,7 +24769,7 @@
         <v>8669470</v>
       </c>
     </row>
-    <row r="592" spans="1:6" ht="43.7">
+    <row r="592" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A592" t="s">
         <v>2369</v>
       </c>
@@ -24779,7 +24789,7 @@
         <v>8692193</v>
       </c>
     </row>
-    <row r="593" spans="1:6">
+    <row r="593" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A593" t="s">
         <v>2373</v>
       </c>
@@ -24799,7 +24809,7 @@
         <v>8692845</v>
       </c>
     </row>
-    <row r="594" spans="1:6" ht="29.1">
+    <row r="594" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A594" t="s">
         <v>2377</v>
       </c>
@@ -24819,7 +24829,7 @@
         <v>8696096</v>
       </c>
     </row>
-    <row r="595" spans="1:6" ht="29.1">
+    <row r="595" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A595" t="s">
         <v>2381</v>
       </c>
@@ -24839,7 +24849,7 @@
         <v>8701803</v>
       </c>
     </row>
-    <row r="596" spans="1:6">
+    <row r="596" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A596" t="s">
         <v>2385</v>
       </c>
@@ -24859,7 +24869,7 @@
         <v>8726805</v>
       </c>
     </row>
-    <row r="597" spans="1:6" ht="29.1">
+    <row r="597" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A597" t="s">
         <v>2389</v>
       </c>
@@ -24879,7 +24889,7 @@
         <v>8743748</v>
       </c>
     </row>
-    <row r="598" spans="1:6" ht="29.1">
+    <row r="598" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A598" t="s">
         <v>2393</v>
       </c>
@@ -24899,7 +24909,7 @@
         <v>8744305</v>
       </c>
     </row>
-    <row r="599" spans="1:6" ht="29.1">
+    <row r="599" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A599" t="s">
         <v>2397</v>
       </c>
@@ -24919,7 +24929,7 @@
         <v>8748356</v>
       </c>
     </row>
-    <row r="600" spans="1:6">
+    <row r="600" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A600" t="s">
         <v>2401</v>
       </c>
@@ -24939,7 +24949,7 @@
         <v>8755894</v>
       </c>
     </row>
-    <row r="601" spans="1:6" ht="43.7">
+    <row r="601" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A601" t="s">
         <v>2405</v>
       </c>
@@ -24959,7 +24969,7 @@
         <v>8761428</v>
       </c>
     </row>
-    <row r="602" spans="1:6" ht="29.1">
+    <row r="602" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A602" t="s">
         <v>2409</v>
       </c>
@@ -24979,7 +24989,7 @@
         <v>8769146</v>
       </c>
     </row>
-    <row r="603" spans="1:6" ht="43.7">
+    <row r="603" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A603" t="s">
         <v>2413</v>
       </c>
@@ -24999,7 +25009,7 @@
         <v>8776517</v>
       </c>
     </row>
-    <row r="604" spans="1:6" ht="29.1">
+    <row r="604" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A604" t="s">
         <v>2417</v>
       </c>
@@ -25019,7 +25029,7 @@
         <v>8805846</v>
       </c>
     </row>
-    <row r="605" spans="1:6" ht="29.1">
+    <row r="605" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A605" t="s">
         <v>2421</v>
       </c>
@@ -25039,7 +25049,7 @@
         <v>8808190</v>
       </c>
     </row>
-    <row r="606" spans="1:6" ht="58.35">
+    <row r="606" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A606" t="s">
         <v>2425</v>
       </c>
@@ -25059,7 +25069,7 @@
         <v>8813635</v>
       </c>
     </row>
-    <row r="607" spans="1:6" ht="43.7">
+    <row r="607" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A607" t="s">
         <v>2429</v>
       </c>
@@ -25079,7 +25089,7 @@
         <v>8816459</v>
       </c>
     </row>
-    <row r="608" spans="1:6" ht="29.1">
+    <row r="608" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A608" t="s">
         <v>2433</v>
       </c>
@@ -25099,7 +25109,7 @@
         <v>8818295</v>
       </c>
     </row>
-    <row r="609" spans="1:6" ht="29.1">
+    <row r="609" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A609" t="s">
         <v>2437</v>
       </c>
@@ -25119,7 +25129,7 @@
         <v>8818767</v>
       </c>
     </row>
-    <row r="610" spans="1:6" ht="29.1">
+    <row r="610" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A610" t="s">
         <v>2441</v>
       </c>
@@ -25139,7 +25149,7 @@
         <v>8820878</v>
       </c>
     </row>
-    <row r="611" spans="1:6" ht="29.1">
+    <row r="611" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A611" t="s">
         <v>2445</v>
       </c>
@@ -25159,7 +25169,7 @@
         <v>8836891</v>
       </c>
     </row>
-    <row r="612" spans="1:6" ht="29.1">
+    <row r="612" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A612" t="s">
         <v>2449</v>
       </c>
@@ -25179,7 +25189,7 @@
         <v>8844396</v>
       </c>
     </row>
-    <row r="613" spans="1:6" ht="58.35">
+    <row r="613" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A613" t="s">
         <v>2453</v>
       </c>
@@ -25199,7 +25209,7 @@
         <v>8847638</v>
       </c>
     </row>
-    <row r="614" spans="1:6" ht="43.7">
+    <row r="614" spans="1:6" ht="43.75" x14ac:dyDescent="0.4">
       <c r="A614" t="s">
         <v>2457</v>
       </c>
@@ -25219,7 +25229,7 @@
         <v>8862006</v>
       </c>
     </row>
-    <row r="615" spans="1:6" ht="29.1">
+    <row r="615" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A615" t="s">
         <v>2461</v>
       </c>
@@ -25239,7 +25249,7 @@
         <v>8865793</v>
       </c>
     </row>
-    <row r="616" spans="1:6" ht="29.1">
+    <row r="616" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A616" t="s">
         <v>2465</v>
       </c>
@@ -25259,7 +25269,7 @@
         <v>8879236</v>
       </c>
     </row>
-    <row r="617" spans="1:6" ht="29.1">
+    <row r="617" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A617" t="s">
         <v>2469</v>
       </c>
@@ -25279,7 +25289,7 @@
         <v>8899290</v>
       </c>
     </row>
-    <row r="618" spans="1:6" ht="29.1">
+    <row r="618" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A618" t="s">
         <v>2473</v>
       </c>
@@ -25299,7 +25309,7 @@
         <v>8943170</v>
       </c>
     </row>
-    <row r="619" spans="1:6" ht="43.7">
+    <row r="619" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A619" t="s">
         <v>2477</v>
       </c>
@@ -25319,7 +25329,7 @@
         <v>8945890</v>
       </c>
     </row>
-    <row r="620" spans="1:6" ht="29.1">
+    <row r="620" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A620" t="s">
         <v>2481</v>
       </c>
@@ -25339,7 +25349,7 @@
         <v>8957509</v>
       </c>
     </row>
-    <row r="621" spans="1:6" ht="58.35">
+    <row r="621" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A621" t="s">
         <v>2485</v>
       </c>
@@ -25359,7 +25369,7 @@
         <v>8959572</v>
       </c>
     </row>
-    <row r="622" spans="1:6" ht="29.1">
+    <row r="622" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A622" t="s">
         <v>2489</v>
       </c>
@@ -25379,7 +25389,7 @@
         <v>8977721</v>
       </c>
     </row>
-    <row r="623" spans="1:6">
+    <row r="623" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A623" t="s">
         <v>2493</v>
       </c>
@@ -25399,7 +25409,7 @@
         <v>8998740</v>
       </c>
     </row>
-    <row r="624" spans="1:6" ht="58.35">
+    <row r="624" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A624" t="s">
         <v>2497</v>
       </c>
@@ -25419,7 +25429,7 @@
         <v>9016843</v>
       </c>
     </row>
-    <row r="625" spans="1:6" ht="43.7">
+    <row r="625" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A625" t="s">
         <v>2501</v>
       </c>
@@ -25439,7 +25449,7 @@
         <v>9035606</v>
       </c>
     </row>
-    <row r="626" spans="1:6" ht="29.1">
+    <row r="626" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A626" t="s">
         <v>2505</v>
       </c>
@@ -25459,7 +25469,7 @@
         <v>9035731</v>
       </c>
     </row>
-    <row r="627" spans="1:6">
+    <row r="627" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A627" t="s">
         <v>2509</v>
       </c>
@@ -25479,7 +25489,7 @@
         <v>9076519</v>
       </c>
     </row>
-    <row r="628" spans="1:6">
+    <row r="628" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A628" t="s">
         <v>2513</v>
       </c>
@@ -25499,7 +25509,7 @@
         <v>9081218</v>
       </c>
     </row>
-    <row r="629" spans="1:6" ht="29.1">
+    <row r="629" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A629" t="s">
         <v>2517</v>
       </c>
@@ -25519,7 +25529,7 @@
         <v>9141304</v>
       </c>
     </row>
-    <row r="630" spans="1:6" ht="29.1">
+    <row r="630" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A630" t="s">
         <v>2521</v>
       </c>
@@ -25539,7 +25549,7 @@
         <v>9147889</v>
       </c>
     </row>
-    <row r="631" spans="1:6" ht="29.1">
+    <row r="631" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A631" t="s">
         <v>2525</v>
       </c>
@@ -25559,7 +25569,7 @@
         <v>9205355</v>
       </c>
     </row>
-    <row r="632" spans="1:6">
+    <row r="632" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A632" t="s">
         <v>2529</v>
       </c>
@@ -25579,7 +25589,7 @@
         <v>9241781</v>
       </c>
     </row>
-    <row r="633" spans="1:6">
+    <row r="633" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A633" t="s">
         <v>2533</v>
       </c>
@@ -25599,7 +25609,7 @@
         <v>9274385</v>
       </c>
     </row>
-    <row r="634" spans="1:6" ht="29.1">
+    <row r="634" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A634" t="s">
         <v>2537</v>
       </c>
@@ -25619,7 +25629,7 @@
         <v>9294448</v>
       </c>
     </row>
-    <row r="635" spans="1:6" ht="29.1">
+    <row r="635" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A635" t="s">
         <v>2541</v>
       </c>
@@ -25639,7 +25649,7 @@
         <v>9299401</v>
       </c>
     </row>
-    <row r="636" spans="1:6" ht="43.7">
+    <row r="636" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A636" t="s">
         <v>2545</v>
       </c>
@@ -25659,7 +25669,7 @@
         <v>9306553</v>
       </c>
     </row>
-    <row r="637" spans="1:6" ht="29.1">
+    <row r="637" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A637" t="s">
         <v>2549</v>
       </c>
@@ -25679,7 +25689,7 @@
         <v>9392072</v>
       </c>
     </row>
-    <row r="638" spans="1:6" ht="43.7">
+    <row r="638" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A638" t="s">
         <v>2553</v>
       </c>
@@ -25699,7 +25709,7 @@
         <v>9404263</v>
       </c>
     </row>
-    <row r="639" spans="1:6" ht="29.1">
+    <row r="639" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A639" t="s">
         <v>2557</v>
       </c>
@@ -25719,7 +25729,7 @@
         <v>9447614</v>
       </c>
     </row>
-    <row r="640" spans="1:6" ht="43.7">
+    <row r="640" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A640" t="s">
         <v>2561</v>
       </c>
@@ -25739,7 +25749,7 @@
         <v>9452570</v>
       </c>
     </row>
-    <row r="641" spans="1:6" ht="29.1">
+    <row r="641" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A641" t="s">
         <v>2565</v>
       </c>
@@ -25759,7 +25769,7 @@
         <v>9456242</v>
       </c>
     </row>
-    <row r="642" spans="1:6" ht="29.1">
+    <row r="642" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A642" t="s">
         <v>2569</v>
       </c>
@@ -25779,7 +25789,7 @@
         <v>9473523</v>
       </c>
     </row>
-    <row r="643" spans="1:6" ht="29.1">
+    <row r="643" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A643" t="s">
         <v>2573</v>
       </c>
@@ -25799,7 +25809,7 @@
         <v>9476190</v>
       </c>
     </row>
-    <row r="644" spans="1:6" ht="29.1">
+    <row r="644" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A644" t="s">
         <v>2577</v>
       </c>
@@ -25819,7 +25829,7 @@
         <v>9495741</v>
       </c>
     </row>
-    <row r="645" spans="1:6" ht="29.1">
+    <row r="645" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A645" t="s">
         <v>2581</v>
       </c>
@@ -25839,7 +25849,7 @@
         <v>9510818</v>
       </c>
     </row>
-    <row r="646" spans="1:6" ht="29.1">
+    <row r="646" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A646" t="s">
         <v>2585</v>
       </c>
@@ -25859,7 +25869,7 @@
         <v>9553773</v>
       </c>
     </row>
-    <row r="647" spans="1:6" ht="43.7">
+    <row r="647" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A647" t="s">
         <v>2589</v>
       </c>
@@ -25879,7 +25889,7 @@
         <v>9627754</v>
       </c>
     </row>
-    <row r="648" spans="1:6" ht="58.35">
+    <row r="648" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A648" t="s">
         <v>2593</v>
       </c>
@@ -25899,7 +25909,7 @@
         <v>9738668</v>
       </c>
     </row>
-    <row r="649" spans="1:6" ht="29.1">
+    <row r="649" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A649" t="s">
         <v>2597</v>
       </c>
@@ -25919,7 +25929,7 @@
         <v>9739879</v>
       </c>
     </row>
-    <row r="650" spans="1:6">
+    <row r="650" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A650" t="s">
         <v>2601</v>
       </c>
@@ -25939,7 +25949,7 @@
         <v>9751895</v>
       </c>
     </row>
-    <row r="651" spans="1:6" ht="58.35">
+    <row r="651" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A651" t="s">
         <v>2605</v>
       </c>
@@ -25959,7 +25969,7 @@
         <v>9807059</v>
       </c>
     </row>
-    <row r="652" spans="1:6" ht="29.1">
+    <row r="652" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A652" t="s">
         <v>2609</v>
       </c>
@@ -25979,7 +25989,7 @@
         <v>9810372</v>
       </c>
     </row>
-    <row r="653" spans="1:6" ht="43.7">
+    <row r="653" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A653" t="s">
         <v>2613</v>
       </c>
@@ -25999,7 +26009,7 @@
         <v>9818134</v>
       </c>
     </row>
-    <row r="654" spans="1:6" ht="29.1">
+    <row r="654" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A654" t="s">
         <v>2617</v>
       </c>
@@ -26019,7 +26029,7 @@
         <v>9831751</v>
       </c>
     </row>
-    <row r="655" spans="1:6" ht="43.7">
+    <row r="655" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A655" t="s">
         <v>2621</v>
       </c>
@@ -26039,7 +26049,7 @@
         <v>9852672</v>
       </c>
     </row>
-    <row r="656" spans="1:6" ht="29.1">
+    <row r="656" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A656" t="s">
         <v>2625</v>
       </c>
@@ -26059,7 +26069,7 @@
         <v>9861751</v>
       </c>
     </row>
-    <row r="657" spans="1:6" ht="43.7">
+    <row r="657" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A657" t="s">
         <v>2629</v>
       </c>
@@ -26079,7 +26089,7 @@
         <v>9894145</v>
       </c>
     </row>
-    <row r="658" spans="1:6">
+    <row r="658" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A658" t="s">
         <v>2633</v>
       </c>
@@ -26099,7 +26109,7 @@
         <v>9900305</v>
       </c>
     </row>
-    <row r="659" spans="1:6" ht="43.7">
+    <row r="659" spans="1:6" ht="43.75" x14ac:dyDescent="0.4">
       <c r="A659" t="s">
         <v>2637</v>
       </c>
@@ -26119,7 +26129,7 @@
         <v>9927805</v>
       </c>
     </row>
-    <row r="660" spans="1:6">
+    <row r="660" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A660" t="s">
         <v>2641</v>
       </c>
@@ -26139,7 +26149,7 @@
         <v>9971676</v>
       </c>
     </row>
-    <row r="661" spans="1:6" ht="29.1">
+    <row r="661" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A661" t="s">
         <v>2645</v>
       </c>
@@ -26159,7 +26169,7 @@
         <v>9975265</v>
       </c>
     </row>
-    <row r="662" spans="1:6" ht="43.7">
+    <row r="662" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A662" t="s">
         <v>2649</v>
       </c>
@@ -26179,7 +26189,7 @@
         <v>10067437</v>
       </c>
     </row>
-    <row r="663" spans="1:6" ht="43.7">
+    <row r="663" spans="1:6" ht="43.75" x14ac:dyDescent="0.4">
       <c r="A663" t="s">
         <v>2653</v>
       </c>
@@ -26199,7 +26209,7 @@
         <v>10089195</v>
       </c>
     </row>
-    <row r="664" spans="1:6" ht="58.35">
+    <row r="664" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A664" t="s">
         <v>2657</v>
       </c>
@@ -26219,7 +26229,7 @@
         <v>10091779</v>
       </c>
     </row>
-    <row r="665" spans="1:6" ht="29.1">
+    <row r="665" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A665" t="s">
         <v>2661</v>
       </c>
@@ -26239,7 +26249,7 @@
         <v>10119167</v>
       </c>
     </row>
-    <row r="666" spans="1:6" ht="29.1">
+    <row r="666" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A666" t="s">
         <v>2665</v>
       </c>
@@ -26259,7 +26269,7 @@
         <v>10139628</v>
       </c>
     </row>
-    <row r="667" spans="1:6" ht="43.7">
+    <row r="667" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A667" t="s">
         <v>2669</v>
       </c>
@@ -26279,7 +26289,7 @@
         <v>10147831</v>
       </c>
     </row>
-    <row r="668" spans="1:6" ht="29.1">
+    <row r="668" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A668" t="s">
         <v>2673</v>
       </c>
@@ -26299,7 +26309,7 @@
         <v>10151963</v>
       </c>
     </row>
-    <row r="669" spans="1:6" ht="43.7">
+    <row r="669" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A669" t="s">
         <v>2677</v>
       </c>
@@ -26319,7 +26329,7 @@
         <v>10162382</v>
       </c>
     </row>
-    <row r="670" spans="1:6" ht="29.1">
+    <row r="670" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A670" t="s">
         <v>2681</v>
       </c>
@@ -26339,7 +26349,7 @@
         <v>10164335</v>
       </c>
     </row>
-    <row r="671" spans="1:6" ht="29.1">
+    <row r="671" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A671" t="s">
         <v>2685</v>
       </c>
@@ -26359,7 +26369,7 @@
         <v>10203701</v>
       </c>
     </row>
-    <row r="672" spans="1:6" ht="58.35">
+    <row r="672" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A672" t="s">
         <v>2689</v>
       </c>
@@ -26379,7 +26389,7 @@
         <v>10205588</v>
       </c>
     </row>
-    <row r="673" spans="1:6" ht="43.7">
+    <row r="673" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A673" t="s">
         <v>2693</v>
       </c>
@@ -26399,7 +26409,7 @@
         <v>10227543</v>
       </c>
     </row>
-    <row r="674" spans="1:6" ht="43.7">
+    <row r="674" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A674" t="s">
         <v>2697</v>
       </c>
@@ -26419,7 +26429,7 @@
         <v>10315196</v>
       </c>
     </row>
-    <row r="675" spans="1:6" ht="72.95">
+    <row r="675" spans="1:6" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A675" t="s">
         <v>2701</v>
       </c>
@@ -26439,7 +26449,7 @@
         <v>10364101</v>
       </c>
     </row>
-    <row r="676" spans="1:6" ht="43.7">
+    <row r="676" spans="1:6" ht="43.75" x14ac:dyDescent="0.4">
       <c r="A676" t="s">
         <v>2705</v>
       </c>
@@ -26459,7 +26469,7 @@
         <v>10372729</v>
       </c>
     </row>
-    <row r="677" spans="1:6" ht="29.1">
+    <row r="677" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A677" t="s">
         <v>2709</v>
       </c>
@@ -26479,7 +26489,7 @@
         <v>10373538</v>
       </c>
     </row>
-    <row r="678" spans="1:6" ht="43.7">
+    <row r="678" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A678" t="s">
         <v>2713</v>
       </c>
@@ -26499,7 +26509,7 @@
         <v>10393576</v>
       </c>
     </row>
-    <row r="679" spans="1:6" ht="29.1">
+    <row r="679" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A679" t="s">
         <v>2717</v>
       </c>
@@ -26519,7 +26529,7 @@
         <v>10400016</v>
       </c>
     </row>
-    <row r="680" spans="1:6" ht="43.7">
+    <row r="680" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A680" t="s">
         <v>2721</v>
       </c>
@@ -26539,7 +26549,7 @@
         <v>10405060</v>
       </c>
     </row>
-    <row r="681" spans="1:6" ht="29.1">
+    <row r="681" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A681" t="s">
         <v>2725</v>
       </c>
@@ -26559,7 +26569,7 @@
         <v>10435378</v>
       </c>
     </row>
-    <row r="682" spans="1:6" ht="29.1">
+    <row r="682" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A682" t="s">
         <v>2729</v>
       </c>
@@ -26579,7 +26589,7 @@
         <v>10564832</v>
       </c>
     </row>
-    <row r="683" spans="1:6" ht="29.1">
+    <row r="683" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A683" t="s">
         <v>2733</v>
       </c>
@@ -26599,7 +26609,7 @@
         <v>10572879</v>
       </c>
     </row>
-    <row r="684" spans="1:6" ht="43.7">
+    <row r="684" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A684" t="s">
         <v>2737</v>
       </c>
@@ -26619,7 +26629,7 @@
         <v>10591972</v>
       </c>
     </row>
-    <row r="685" spans="1:6" ht="58.35">
+    <row r="685" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A685" t="s">
         <v>2741</v>
       </c>
@@ -26639,7 +26649,7 @@
         <v>10616305</v>
       </c>
     </row>
-    <row r="686" spans="1:6" ht="43.7">
+    <row r="686" spans="1:6" ht="43.75" x14ac:dyDescent="0.4">
       <c r="A686" t="s">
         <v>2745</v>
       </c>
@@ -26659,7 +26669,7 @@
         <v>10628614</v>
       </c>
     </row>
-    <row r="687" spans="1:6" ht="29.1">
+    <row r="687" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A687" t="s">
         <v>2749</v>
       </c>
@@ -26679,7 +26689,7 @@
         <v>10643554</v>
       </c>
     </row>
-    <row r="688" spans="1:6" ht="43.7">
+    <row r="688" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A688" t="s">
         <v>2753</v>
       </c>
@@ -26699,7 +26709,7 @@
         <v>10643702</v>
       </c>
     </row>
-    <row r="689" spans="1:6" ht="29.1">
+    <row r="689" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A689" t="s">
         <v>2757</v>
       </c>
@@ -26719,7 +26729,7 @@
         <v>10652734</v>
       </c>
     </row>
-    <row r="690" spans="1:6" ht="29.1">
+    <row r="690" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A690" t="s">
         <v>2761</v>
       </c>
@@ -26739,7 +26749,7 @@
         <v>10697965</v>
       </c>
     </row>
-    <row r="691" spans="1:6" ht="29.1">
+    <row r="691" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A691" t="s">
         <v>2765</v>
       </c>
@@ -26759,7 +26769,7 @@
         <v>10709559</v>
       </c>
     </row>
-    <row r="692" spans="1:6" ht="58.35">
+    <row r="692" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A692" t="s">
         <v>2769</v>
       </c>
@@ -26779,7 +26789,7 @@
         <v>10727109</v>
       </c>
     </row>
-    <row r="693" spans="1:6" ht="29.1">
+    <row r="693" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A693" t="s">
         <v>2773</v>
       </c>
@@ -26799,7 +26809,7 @@
         <v>10781122</v>
       </c>
     </row>
-    <row r="694" spans="1:6" ht="29.1">
+    <row r="694" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A694" t="s">
         <v>2777</v>
       </c>
@@ -26819,7 +26829,7 @@
         <v>10827850</v>
       </c>
     </row>
-    <row r="695" spans="1:6" ht="43.7">
+    <row r="695" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A695" t="s">
         <v>2781</v>
       </c>
@@ -26839,7 +26849,7 @@
         <v>10836539</v>
       </c>
     </row>
-    <row r="696" spans="1:6" ht="43.7">
+    <row r="696" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A696" t="s">
         <v>2785</v>
       </c>
@@ -26859,7 +26869,7 @@
         <v>10848547</v>
       </c>
     </row>
-    <row r="697" spans="1:6" ht="29.1">
+    <row r="697" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A697" t="s">
         <v>2789</v>
       </c>
@@ -26879,7 +26889,7 @@
         <v>10852992</v>
       </c>
     </row>
-    <row r="698" spans="1:6" ht="29.1">
+    <row r="698" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A698" t="s">
         <v>2793</v>
       </c>
@@ -26899,7 +26909,7 @@
         <v>10866173</v>
       </c>
     </row>
-    <row r="699" spans="1:6" ht="29.1">
+    <row r="699" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A699" t="s">
         <v>2797</v>
       </c>
@@ -26919,7 +26929,7 @@
         <v>10873061</v>
       </c>
     </row>
-    <row r="700" spans="1:6" ht="29.1">
+    <row r="700" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A700" t="s">
         <v>2801</v>
       </c>
@@ -26939,7 +26949,7 @@
         <v>10877469</v>
       </c>
     </row>
-    <row r="701" spans="1:6" ht="58.35">
+    <row r="701" spans="1:6" ht="58.3" x14ac:dyDescent="0.4">
       <c r="A701" t="s">
         <v>2805</v>
       </c>
@@ -26959,7 +26969,7 @@
         <v>10894140</v>
       </c>
     </row>
-    <row r="702" spans="1:6">
+    <row r="702" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A702" t="s">
         <v>2809</v>
       </c>
@@ -26979,7 +26989,7 @@
         <v>10900355</v>
       </c>
     </row>
-    <row r="703" spans="1:6" ht="58.35">
+    <row r="703" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A703" t="s">
         <v>2813</v>
       </c>
@@ -26999,7 +27009,7 @@
         <v>10915326</v>
       </c>
     </row>
-    <row r="704" spans="1:6">
+    <row r="704" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A704" t="s">
         <v>2817</v>
       </c>
@@ -27019,7 +27029,7 @@
         <v>10979731</v>
       </c>
     </row>
-    <row r="705" spans="1:6">
+    <row r="705" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A705" t="s">
         <v>2821</v>
       </c>
@@ -27039,7 +27049,7 @@
         <v>11001971</v>
       </c>
     </row>
-    <row r="706" spans="1:6">
+    <row r="706" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A706" t="s">
         <v>2825</v>
       </c>
@@ -27059,7 +27069,7 @@
         <v>11073541</v>
       </c>
     </row>
-    <row r="707" spans="1:6">
+    <row r="707" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A707" t="s">
         <v>2829</v>
       </c>
@@ -27079,7 +27089,7 @@
         <v>11073748</v>
       </c>
     </row>
-    <row r="708" spans="1:6" ht="43.7">
+    <row r="708" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A708" t="s">
         <v>2833</v>
       </c>
@@ -27099,7 +27109,7 @@
         <v>11083143</v>
       </c>
     </row>
-    <row r="709" spans="1:6" ht="29.1">
+    <row r="709" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A709" t="s">
         <v>2837</v>
       </c>
@@ -27119,7 +27129,7 @@
         <v>11100244</v>
       </c>
     </row>
-    <row r="710" spans="1:6" ht="29.1">
+    <row r="710" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A710" t="s">
         <v>2841</v>
       </c>
@@ -27139,7 +27149,7 @@
         <v>11105445</v>
       </c>
     </row>
-    <row r="711" spans="1:6" ht="29.1">
+    <row r="711" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A711" t="s">
         <v>2845</v>
       </c>
@@ -27159,7 +27169,7 @@
         <v>11105617</v>
       </c>
     </row>
-    <row r="712" spans="1:6" ht="29.1">
+    <row r="712" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A712" t="s">
         <v>2849</v>
       </c>
@@ -27179,7 +27189,7 @@
         <v>11132492</v>
       </c>
     </row>
-    <row r="713" spans="1:6" ht="29.1">
+    <row r="713" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A713" t="s">
         <v>2853</v>
       </c>
@@ -27199,7 +27209,7 @@
         <v>11149677</v>
       </c>
     </row>
-    <row r="714" spans="1:6" ht="29.1">
+    <row r="714" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A714" t="s">
         <v>2857</v>
       </c>
@@ -27219,7 +27229,7 @@
         <v>11165721</v>
       </c>
     </row>
-    <row r="715" spans="1:6" ht="43.7">
+    <row r="715" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A715" t="s">
         <v>2861</v>
       </c>
@@ -27239,7 +27249,7 @@
         <v>11172898</v>
       </c>
     </row>
-    <row r="716" spans="1:6" ht="29.1">
+    <row r="716" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A716" t="s">
         <v>2865</v>
       </c>
@@ -27259,7 +27269,7 @@
         <v>11185471</v>
       </c>
     </row>
-    <row r="717" spans="1:6" ht="43.7">
+    <row r="717" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A717" t="s">
         <v>2869</v>
       </c>
@@ -27279,7 +27289,7 @@
         <v>11193119</v>
       </c>
     </row>
-    <row r="718" spans="1:6" ht="43.7">
+    <row r="718" spans="1:6" ht="43.75" x14ac:dyDescent="0.4">
       <c r="A718" t="s">
         <v>2873</v>
       </c>
@@ -27299,7 +27309,7 @@
         <v>11203066</v>
       </c>
     </row>
-    <row r="719" spans="1:6">
+    <row r="719" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A719" t="s">
         <v>2877</v>
       </c>
@@ -27319,7 +27329,7 @@
         <v>11212686</v>
       </c>
     </row>
-    <row r="720" spans="1:6" ht="58.35">
+    <row r="720" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A720" t="s">
         <v>2881</v>
       </c>
@@ -27339,7 +27349,7 @@
         <v>11228831</v>
       </c>
     </row>
-    <row r="721" spans="1:6" ht="29.1">
+    <row r="721" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A721" t="s">
         <v>2885</v>
       </c>
@@ -27359,7 +27369,7 @@
         <v>11313588</v>
       </c>
     </row>
-    <row r="722" spans="1:6" ht="58.35">
+    <row r="722" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A722" t="s">
         <v>2889</v>
       </c>
@@ -27379,7 +27389,7 @@
         <v>11319980</v>
       </c>
     </row>
-    <row r="723" spans="1:6" ht="58.35">
+    <row r="723" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A723" t="s">
         <v>2893</v>
       </c>
@@ -27399,7 +27409,7 @@
         <v>11439105</v>
       </c>
     </row>
-    <row r="724" spans="1:6" ht="29.1">
+    <row r="724" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A724" t="s">
         <v>2897</v>
       </c>
@@ -27419,7 +27429,7 @@
         <v>11443609</v>
       </c>
     </row>
-    <row r="725" spans="1:6" ht="72.95">
+    <row r="725" spans="1:6" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A725" t="s">
         <v>2901</v>
       </c>
@@ -27439,7 +27449,7 @@
         <v>11464452</v>
       </c>
     </row>
-    <row r="726" spans="1:6" ht="43.7">
+    <row r="726" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A726" t="s">
         <v>2905</v>
       </c>
@@ -27459,7 +27469,7 @@
         <v>11465545</v>
       </c>
     </row>
-    <row r="727" spans="1:6" ht="29.1">
+    <row r="727" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A727" t="s">
         <v>2909</v>
       </c>
@@ -27479,7 +27489,7 @@
         <v>11483577</v>
       </c>
     </row>
-    <row r="728" spans="1:6" ht="29.1">
+    <row r="728" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A728" t="s">
         <v>2913</v>
       </c>
@@ -27499,7 +27509,7 @@
         <v>11501783</v>
       </c>
     </row>
-    <row r="729" spans="1:6" ht="29.1">
+    <row r="729" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A729" t="s">
         <v>2917</v>
       </c>
@@ -27519,7 +27529,7 @@
         <v>11526649</v>
       </c>
     </row>
-    <row r="730" spans="1:6">
+    <row r="730" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A730" t="s">
         <v>2921</v>
       </c>
@@ -27539,7 +27549,7 @@
         <v>11532314</v>
       </c>
     </row>
-    <row r="731" spans="1:6" ht="43.7">
+    <row r="731" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A731" t="s">
         <v>2925</v>
       </c>
@@ -27559,7 +27569,7 @@
         <v>11533465</v>
       </c>
     </row>
-    <row r="732" spans="1:6" ht="29.1">
+    <row r="732" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A732" t="s">
         <v>2929</v>
       </c>
@@ -27579,7 +27589,7 @@
         <v>11534786</v>
       </c>
     </row>
-    <row r="733" spans="1:6" ht="29.1">
+    <row r="733" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A733" t="s">
         <v>2933</v>
       </c>
@@ -27599,7 +27609,7 @@
         <v>11591486</v>
       </c>
     </row>
-    <row r="734" spans="1:6" ht="43.7">
+    <row r="734" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A734" t="s">
         <v>2937</v>
       </c>
@@ -27619,7 +27629,7 @@
         <v>11604048</v>
       </c>
     </row>
-    <row r="735" spans="1:6" ht="29.1">
+    <row r="735" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A735" t="s">
         <v>2941</v>
       </c>
@@ -27639,7 +27649,7 @@
         <v>11626218</v>
       </c>
     </row>
-    <row r="736" spans="1:6" ht="43.7">
+    <row r="736" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A736" t="s">
         <v>2945</v>
       </c>
@@ -27659,7 +27669,7 @@
         <v>11663259</v>
       </c>
     </row>
-    <row r="737" spans="1:6" ht="29.1">
+    <row r="737" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A737" t="s">
         <v>2949</v>
       </c>
@@ -27679,7 +27689,7 @@
         <v>11686717</v>
       </c>
     </row>
-    <row r="738" spans="1:6" ht="29.1">
+    <row r="738" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A738" t="s">
         <v>2953</v>
       </c>
@@ -27699,7 +27709,7 @@
         <v>11709376</v>
       </c>
     </row>
-    <row r="739" spans="1:6" ht="29.1">
+    <row r="739" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A739" t="s">
         <v>2957</v>
       </c>
@@ -27719,7 +27729,7 @@
         <v>11722213</v>
       </c>
     </row>
-    <row r="740" spans="1:6" ht="29.1">
+    <row r="740" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A740" t="s">
         <v>2961</v>
       </c>
@@ -27739,7 +27749,7 @@
         <v>11783505</v>
       </c>
     </row>
-    <row r="741" spans="1:6" ht="29.1">
+    <row r="741" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A741" t="s">
         <v>2965</v>
       </c>
@@ -27759,7 +27769,7 @@
         <v>11801159</v>
       </c>
     </row>
-    <row r="742" spans="1:6" ht="29.1">
+    <row r="742" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A742" t="s">
         <v>2969</v>
       </c>
@@ -27779,7 +27789,7 @@
         <v>11804165</v>
       </c>
     </row>
-    <row r="743" spans="1:6" ht="29.1">
+    <row r="743" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A743" t="s">
         <v>2973</v>
       </c>
@@ -27799,7 +27809,7 @@
         <v>11811386</v>
       </c>
     </row>
-    <row r="744" spans="1:6" ht="58.35">
+    <row r="744" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A744" t="s">
         <v>2977</v>
       </c>
@@ -27819,7 +27829,7 @@
         <v>11814086</v>
       </c>
     </row>
-    <row r="745" spans="1:6" ht="29.1">
+    <row r="745" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A745" t="s">
         <v>2981</v>
       </c>
@@ -27839,7 +27849,7 @@
         <v>11815977</v>
       </c>
     </row>
-    <row r="746" spans="1:6" ht="29.1">
+    <row r="746" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A746" t="s">
         <v>2985</v>
       </c>
@@ -27859,7 +27869,7 @@
         <v>11816622</v>
       </c>
     </row>
-    <row r="747" spans="1:6">
+    <row r="747" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A747" t="s">
         <v>2989</v>
       </c>
@@ -27879,7 +27889,7 @@
         <v>11821361</v>
       </c>
     </row>
-    <row r="748" spans="1:6" ht="43.7">
+    <row r="748" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A748" t="s">
         <v>2992</v>
       </c>
@@ -27899,7 +27909,7 @@
         <v>11874762</v>
       </c>
     </row>
-    <row r="749" spans="1:6">
+    <row r="749" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A749" t="s">
         <v>2996</v>
       </c>
@@ -27919,7 +27929,7 @@
         <v>11878784</v>
       </c>
     </row>
-    <row r="750" spans="1:6" ht="29.1">
+    <row r="750" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A750" t="s">
         <v>3000</v>
       </c>
@@ -27939,7 +27949,7 @@
         <v>11880831</v>
       </c>
     </row>
-    <row r="751" spans="1:6" ht="58.35">
+    <row r="751" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A751" t="s">
         <v>3004</v>
       </c>
@@ -27959,7 +27969,7 @@
         <v>11882724</v>
       </c>
     </row>
-    <row r="752" spans="1:6" ht="43.7">
+    <row r="752" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A752" t="s">
         <v>3008</v>
       </c>
@@ -27979,7 +27989,7 @@
         <v>11913319</v>
       </c>
     </row>
-    <row r="753" spans="1:6" ht="43.7">
+    <row r="753" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A753" t="s">
         <v>3012</v>
       </c>
@@ -27999,7 +28009,7 @@
         <v>11942665</v>
       </c>
     </row>
-    <row r="754" spans="1:6" ht="29.1">
+    <row r="754" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A754" t="s">
         <v>3016</v>
       </c>
@@ -28019,7 +28029,7 @@
         <v>11952546</v>
       </c>
     </row>
-    <row r="755" spans="1:6" ht="29.1">
+    <row r="755" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A755" t="s">
         <v>3020</v>
       </c>
@@ -28039,7 +28049,7 @@
         <v>11952998</v>
       </c>
     </row>
-    <row r="756" spans="1:6" ht="58.35">
+    <row r="756" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A756" t="s">
         <v>3024</v>
       </c>
@@ -28059,7 +28069,7 @@
         <v>11965980</v>
       </c>
     </row>
-    <row r="757" spans="1:6" ht="43.7">
+    <row r="757" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A757" t="s">
         <v>3028</v>
       </c>
@@ -28079,7 +28089,7 @@
         <v>11974438</v>
       </c>
     </row>
-    <row r="758" spans="1:6">
+    <row r="758" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A758" t="s">
         <v>3032</v>
       </c>
@@ -28099,7 +28109,7 @@
         <v>11996136</v>
       </c>
     </row>
-    <row r="759" spans="1:6">
+    <row r="759" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A759" t="s">
         <v>3036</v>
       </c>
@@ -28119,7 +28129,7 @@
         <v>12015119</v>
       </c>
     </row>
-    <row r="760" spans="1:6" ht="43.7">
+    <row r="760" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A760" t="s">
         <v>3040</v>
       </c>
@@ -28139,7 +28149,7 @@
         <v>12021599</v>
       </c>
     </row>
-    <row r="761" spans="1:6" ht="43.7">
+    <row r="761" spans="1:6" ht="43.75" x14ac:dyDescent="0.4">
       <c r="A761" t="s">
         <v>3044</v>
       </c>
@@ -28159,7 +28169,7 @@
         <v>12021605</v>
       </c>
     </row>
-    <row r="762" spans="1:6" ht="29.1">
+    <row r="762" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A762" t="s">
         <v>3048</v>
       </c>
@@ -28179,7 +28189,7 @@
         <v>12046888</v>
       </c>
     </row>
-    <row r="763" spans="1:6" ht="29.1">
+    <row r="763" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A763" t="s">
         <v>3052</v>
       </c>
@@ -28199,7 +28209,7 @@
         <v>12051668</v>
       </c>
     </row>
-    <row r="764" spans="1:6">
+    <row r="764" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A764" t="s">
         <v>3056</v>
       </c>
@@ -28219,7 +28229,7 @@
         <v>12051894</v>
       </c>
     </row>
-    <row r="765" spans="1:6" ht="29.1">
+    <row r="765" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A765" t="s">
         <v>3060</v>
       </c>
@@ -28239,7 +28249,7 @@
         <v>12065033</v>
       </c>
     </row>
-    <row r="766" spans="1:6" ht="43.7">
+    <row r="766" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A766" t="s">
         <v>3064</v>
       </c>
@@ -28259,7 +28269,7 @@
         <v>12074208</v>
       </c>
     </row>
-    <row r="767" spans="1:6">
+    <row r="767" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A767" t="s">
         <v>3068</v>
       </c>
@@ -28279,7 +28289,7 @@
         <v>12075390</v>
       </c>
     </row>
-    <row r="768" spans="1:6" ht="29.1">
+    <row r="768" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A768" t="s">
         <v>3072</v>
       </c>
@@ -28299,7 +28309,7 @@
         <v>12102235</v>
       </c>
     </row>
-    <row r="769" spans="1:6" ht="43.7">
+    <row r="769" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A769" t="s">
         <v>3076</v>
       </c>
@@ -28319,7 +28329,7 @@
         <v>12116383</v>
       </c>
     </row>
-    <row r="770" spans="1:6">
+    <row r="770" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A770" t="s">
         <v>3080</v>
       </c>
@@ -28339,7 +28349,7 @@
         <v>12137998</v>
       </c>
     </row>
-    <row r="771" spans="1:6" ht="29.1">
+    <row r="771" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A771" t="s">
         <v>3084</v>
       </c>
@@ -28359,7 +28369,7 @@
         <v>12176010</v>
       </c>
     </row>
-    <row r="772" spans="1:6">
+    <row r="772" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A772" t="s">
         <v>3088</v>
       </c>
@@ -28379,7 +28389,7 @@
         <v>12187131</v>
       </c>
     </row>
-    <row r="773" spans="1:6" ht="29.1">
+    <row r="773" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A773" t="s">
         <v>3092</v>
       </c>
@@ -28399,7 +28409,7 @@
         <v>12236135</v>
       </c>
     </row>
-    <row r="774" spans="1:6" ht="43.7">
+    <row r="774" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A774" t="s">
         <v>3096</v>
       </c>
@@ -28419,7 +28429,7 @@
         <v>12251090</v>
       </c>
     </row>
-    <row r="775" spans="1:6">
+    <row r="775" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A775" t="s">
         <v>3100</v>
       </c>
@@ -28439,7 +28449,7 @@
         <v>12257508</v>
       </c>
     </row>
-    <row r="776" spans="1:6" ht="43.7">
+    <row r="776" spans="1:6" ht="43.75" x14ac:dyDescent="0.4">
       <c r="A776" t="s">
         <v>3104</v>
       </c>
@@ -28459,7 +28469,7 @@
         <v>12263350</v>
       </c>
     </row>
-    <row r="777" spans="1:6" ht="29.1">
+    <row r="777" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A777" t="s">
         <v>3108</v>
       </c>
@@ -28479,7 +28489,7 @@
         <v>12306493</v>
       </c>
     </row>
-    <row r="778" spans="1:6">
+    <row r="778" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A778" t="s">
         <v>3112</v>
       </c>
@@ -28499,7 +28509,7 @@
         <v>12307538</v>
       </c>
     </row>
-    <row r="779" spans="1:6" ht="29.1">
+    <row r="779" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A779" t="s">
         <v>3116</v>
       </c>
@@ -28519,7 +28529,7 @@
         <v>12335788</v>
       </c>
     </row>
-    <row r="780" spans="1:6" ht="29.1">
+    <row r="780" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A780" t="s">
         <v>3120</v>
       </c>
@@ -28539,7 +28549,7 @@
         <v>12395655</v>
       </c>
     </row>
-    <row r="781" spans="1:6" ht="29.1">
+    <row r="781" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A781" t="s">
         <v>3124</v>
       </c>
@@ -28559,7 +28569,7 @@
         <v>12426352</v>
       </c>
     </row>
-    <row r="782" spans="1:6">
+    <row r="782" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A782" t="s">
         <v>3128</v>
       </c>
@@ -28579,7 +28589,7 @@
         <v>12436683</v>
       </c>
     </row>
-    <row r="783" spans="1:6" ht="29.1">
+    <row r="783" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A783" t="s">
         <v>3132</v>
       </c>
@@ -28599,7 +28609,7 @@
         <v>12461250</v>
       </c>
     </row>
-    <row r="784" spans="1:6" ht="29.1">
+    <row r="784" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A784" t="s">
         <v>3136</v>
       </c>
@@ -28619,7 +28629,7 @@
         <v>12497455</v>
       </c>
     </row>
-    <row r="785" spans="1:6" ht="29.1">
+    <row r="785" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A785" t="s">
         <v>3140</v>
       </c>
@@ -28639,7 +28649,7 @@
         <v>12532085</v>
       </c>
     </row>
-    <row r="786" spans="1:6" ht="29.1">
+    <row r="786" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A786" t="s">
         <v>3144</v>
       </c>
@@ -28659,7 +28669,7 @@
         <v>12552403</v>
       </c>
     </row>
-    <row r="787" spans="1:6" ht="58.35">
+    <row r="787" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A787" t="s">
         <v>3148</v>
       </c>
@@ -28679,7 +28689,7 @@
         <v>12557088</v>
       </c>
     </row>
-    <row r="788" spans="1:6">
+    <row r="788" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A788" t="s">
         <v>3152</v>
       </c>
@@ -28699,7 +28709,7 @@
         <v>12558859</v>
       </c>
     </row>
-    <row r="789" spans="1:6" ht="43.7">
+    <row r="789" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A789" t="s">
         <v>3156</v>
       </c>
@@ -28719,7 +28729,7 @@
         <v>12600372</v>
       </c>
     </row>
-    <row r="790" spans="1:6">
+    <row r="790" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A790" t="s">
         <v>3159</v>
       </c>
@@ -28739,7 +28749,7 @@
         <v>12672646</v>
       </c>
     </row>
-    <row r="791" spans="1:6" ht="29.1">
+    <row r="791" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A791" t="s">
         <v>3163</v>
       </c>
@@ -28759,7 +28769,7 @@
         <v>12687528</v>
       </c>
     </row>
-    <row r="792" spans="1:6" ht="29.1">
+    <row r="792" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A792" t="s">
         <v>3167</v>
       </c>
@@ -28779,7 +28789,7 @@
         <v>12740996</v>
       </c>
     </row>
-    <row r="793" spans="1:6">
+    <row r="793" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A793" t="s">
         <v>3170</v>
       </c>
@@ -28799,7 +28809,7 @@
         <v>12758691</v>
       </c>
     </row>
-    <row r="794" spans="1:6" ht="29.1">
+    <row r="794" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A794" t="s">
         <v>3174</v>
       </c>
@@ -28819,7 +28829,7 @@
         <v>12767054</v>
       </c>
     </row>
-    <row r="795" spans="1:6" ht="29.1">
+    <row r="795" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A795" t="s">
         <v>3178</v>
       </c>
@@ -28839,7 +28849,7 @@
         <v>12776583</v>
       </c>
     </row>
-    <row r="796" spans="1:6" ht="43.7">
+    <row r="796" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A796" t="s">
         <v>3182</v>
       </c>
@@ -28859,7 +28869,7 @@
         <v>12786105</v>
       </c>
     </row>
-    <row r="797" spans="1:6" ht="29.1">
+    <row r="797" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A797" t="s">
         <v>3186</v>
       </c>
@@ -28879,7 +28889,7 @@
         <v>12817657</v>
       </c>
     </row>
-    <row r="798" spans="1:6" ht="43.7">
+    <row r="798" spans="1:6" ht="43.75" x14ac:dyDescent="0.4">
       <c r="A798" t="s">
         <v>3190</v>
       </c>
@@ -28899,7 +28909,7 @@
         <v>12833578</v>
       </c>
     </row>
-    <row r="799" spans="1:6" ht="43.7">
+    <row r="799" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A799" t="s">
         <v>3194</v>
       </c>
@@ -28919,7 +28929,7 @@
         <v>12880561</v>
       </c>
     </row>
-    <row r="800" spans="1:6" ht="29.1">
+    <row r="800" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A800" t="s">
         <v>3198</v>
       </c>
@@ -28939,7 +28949,7 @@
         <v>12888434</v>
       </c>
     </row>
-    <row r="801" spans="1:6">
+    <row r="801" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A801" t="s">
         <v>3202</v>
       </c>
@@ -28959,7 +28969,7 @@
         <v>12915403</v>
       </c>
     </row>
-    <row r="802" spans="1:6" ht="29.1">
+    <row r="802" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A802" t="s">
         <v>3206</v>
       </c>
@@ -28979,7 +28989,7 @@
         <v>12922644</v>
       </c>
     </row>
-    <row r="803" spans="1:6" ht="29.1">
+    <row r="803" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A803" t="s">
         <v>3210</v>
       </c>
@@ -28999,7 +29009,7 @@
         <v>12946543</v>
       </c>
     </row>
-    <row r="804" spans="1:6" ht="29.1">
+    <row r="804" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A804" t="s">
         <v>3214</v>
       </c>
@@ -29019,7 +29029,7 @@
         <v>12950131</v>
       </c>
     </row>
-    <row r="805" spans="1:6" ht="87.4">
+    <row r="805" spans="1:6" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
       <c r="A805" t="s">
         <v>3218</v>
       </c>
@@ -29039,7 +29049,7 @@
         <v>12950393</v>
       </c>
     </row>
-    <row r="806" spans="1:6" ht="29.1">
+    <row r="806" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A806" t="s">
         <v>3222</v>
       </c>
@@ -29059,7 +29069,7 @@
         <v>12958928</v>
       </c>
     </row>
-    <row r="807" spans="1:6" ht="43.7">
+    <row r="807" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A807" t="s">
         <v>3226</v>
       </c>
@@ -29079,7 +29089,7 @@
         <v>12972208</v>
       </c>
     </row>
-    <row r="808" spans="1:6" ht="29.1">
+    <row r="808" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A808" t="s">
         <v>3230</v>
       </c>
@@ -29099,7 +29109,7 @@
         <v>12990755</v>
       </c>
     </row>
-    <row r="809" spans="1:6" ht="29.1">
+    <row r="809" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A809" t="s">
         <v>3234</v>
       </c>
@@ -29119,7 +29129,7 @@
         <v>13004259</v>
       </c>
     </row>
-    <row r="810" spans="1:6" ht="29.1">
+    <row r="810" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A810" t="s">
         <v>3238</v>
       </c>
@@ -29139,7 +29149,7 @@
         <v>13031651</v>
       </c>
     </row>
-    <row r="811" spans="1:6" ht="29.1">
+    <row r="811" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A811" t="s">
         <v>3242</v>
       </c>
@@ -29159,7 +29169,7 @@
         <v>13033507</v>
       </c>
     </row>
-    <row r="812" spans="1:6" ht="29.1">
+    <row r="812" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A812" t="s">
         <v>3246</v>
       </c>
@@ -29179,7 +29189,7 @@
         <v>13041452</v>
       </c>
     </row>
-    <row r="813" spans="1:6">
+    <row r="813" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A813" t="s">
         <v>3250</v>
       </c>
@@ -29199,7 +29209,7 @@
         <v>13045245</v>
       </c>
     </row>
-    <row r="814" spans="1:6" ht="29.1">
+    <row r="814" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A814" t="s">
         <v>3254</v>
       </c>
@@ -29219,7 +29229,7 @@
         <v>13061846</v>
       </c>
     </row>
-    <row r="815" spans="1:6" ht="29.1">
+    <row r="815" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A815" t="s">
         <v>3258</v>
       </c>
@@ -29239,7 +29249,7 @@
         <v>13082164</v>
       </c>
     </row>
-    <row r="816" spans="1:6" ht="29.1">
+    <row r="816" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A816" t="s">
         <v>3262</v>
       </c>
@@ -29259,7 +29269,7 @@
         <v>13100830</v>
       </c>
     </row>
-    <row r="817" spans="1:6" ht="29.1">
+    <row r="817" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A817" t="s">
         <v>3266</v>
       </c>
@@ -29279,7 +29289,7 @@
         <v>13133895</v>
       </c>
     </row>
-    <row r="818" spans="1:6">
+    <row r="818" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A818" t="s">
         <v>3270</v>
       </c>
@@ -29299,7 +29309,7 @@
         <v>13144508</v>
       </c>
     </row>
-    <row r="819" spans="1:6" ht="43.7">
+    <row r="819" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A819" t="s">
         <v>3274</v>
       </c>
@@ -29319,7 +29329,7 @@
         <v>13150901</v>
       </c>
     </row>
-    <row r="820" spans="1:6" ht="29.1">
+    <row r="820" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A820" t="s">
         <v>3278</v>
       </c>
@@ -29339,7 +29349,7 @@
         <v>13167346</v>
       </c>
     </row>
-    <row r="821" spans="1:6" ht="29.1">
+    <row r="821" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A821" t="s">
         <v>3282</v>
       </c>
@@ -29359,7 +29369,7 @@
         <v>13178337</v>
       </c>
     </row>
-    <row r="822" spans="1:6" ht="29.1">
+    <row r="822" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A822" t="s">
         <v>3286</v>
       </c>
@@ -29379,7 +29389,7 @@
         <v>13206368</v>
       </c>
     </row>
-    <row r="823" spans="1:6" ht="43.7">
+    <row r="823" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A823" t="s">
         <v>3290</v>
       </c>
@@ -29399,7 +29409,7 @@
         <v>13208654</v>
       </c>
     </row>
-    <row r="824" spans="1:6" ht="29.1">
+    <row r="824" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A824" t="s">
         <v>3294</v>
       </c>
@@ -29419,7 +29429,7 @@
         <v>13217830</v>
       </c>
     </row>
-    <row r="825" spans="1:6" ht="29.1">
+    <row r="825" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A825" t="s">
         <v>3298</v>
       </c>
@@ -29439,7 +29449,7 @@
         <v>13219320</v>
       </c>
     </row>
-    <row r="826" spans="1:6" ht="29.1">
+    <row r="826" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A826" t="s">
         <v>3302</v>
       </c>
@@ -29459,7 +29469,7 @@
         <v>13235057</v>
       </c>
     </row>
-    <row r="827" spans="1:6" ht="29.1">
+    <row r="827" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A827" t="s">
         <v>3306</v>
       </c>
@@ -29479,7 +29489,7 @@
         <v>13243824</v>
       </c>
     </row>
-    <row r="828" spans="1:6" ht="29.1">
+    <row r="828" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A828" t="s">
         <v>3310</v>
       </c>
@@ -29499,7 +29509,7 @@
         <v>13252265</v>
       </c>
     </row>
-    <row r="829" spans="1:6">
+    <row r="829" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A829" t="s">
         <v>3314</v>
       </c>
@@ -29519,7 +29529,7 @@
         <v>13276254</v>
       </c>
     </row>
-    <row r="830" spans="1:6" ht="29.1">
+    <row r="830" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A830" t="s">
         <v>3318</v>
       </c>
@@ -29539,7 +29549,7 @@
         <v>13292164</v>
       </c>
     </row>
-    <row r="831" spans="1:6" ht="29.1">
+    <row r="831" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A831" t="s">
         <v>3322</v>
       </c>
@@ -29559,7 +29569,7 @@
         <v>13351300</v>
       </c>
     </row>
-    <row r="832" spans="1:6" ht="43.7">
+    <row r="832" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A832" t="s">
         <v>3326</v>
       </c>
@@ -29579,7 +29589,7 @@
         <v>13375059</v>
       </c>
     </row>
-    <row r="833" spans="1:6" ht="29.1">
+    <row r="833" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A833" t="s">
         <v>3330</v>
       </c>
@@ -29599,7 +29609,7 @@
         <v>13407971</v>
       </c>
     </row>
-    <row r="834" spans="1:6" ht="58.35">
+    <row r="834" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A834" t="s">
         <v>3334</v>
       </c>
@@ -29619,7 +29629,7 @@
         <v>13439087</v>
       </c>
     </row>
-    <row r="835" spans="1:6" ht="58.35">
+    <row r="835" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A835" t="s">
         <v>3338</v>
       </c>
@@ -29639,7 +29649,7 @@
         <v>13444648</v>
       </c>
     </row>
-    <row r="836" spans="1:6" ht="43.7">
+    <row r="836" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A836" t="s">
         <v>3342</v>
       </c>
@@ -29659,7 +29669,7 @@
         <v>13550189</v>
       </c>
     </row>
-    <row r="837" spans="1:6" ht="29.1">
+    <row r="837" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A837" t="s">
         <v>3346</v>
       </c>
@@ -29679,7 +29689,7 @@
         <v>13556301</v>
       </c>
     </row>
-    <row r="838" spans="1:6" ht="29.1">
+    <row r="838" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A838" t="s">
         <v>3350</v>
       </c>
@@ -29699,7 +29709,7 @@
         <v>13574318</v>
       </c>
     </row>
-    <row r="839" spans="1:6" ht="29.1">
+    <row r="839" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A839" t="s">
         <v>3354</v>
       </c>
@@ -29719,7 +29729,7 @@
         <v>13578685</v>
       </c>
     </row>
-    <row r="840" spans="1:6" ht="29.1">
+    <row r="840" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A840" t="s">
         <v>3358</v>
       </c>
@@ -29739,7 +29749,7 @@
         <v>13653350</v>
       </c>
     </row>
-    <row r="841" spans="1:6" ht="43.7">
+    <row r="841" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A841" t="s">
         <v>3362</v>
       </c>
@@ -29759,7 +29769,7 @@
         <v>13668916</v>
       </c>
     </row>
-    <row r="842" spans="1:6" ht="43.7">
+    <row r="842" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A842" t="s">
         <v>3366</v>
       </c>
@@ -29779,7 +29789,7 @@
         <v>13714172</v>
       </c>
     </row>
-    <row r="843" spans="1:6" ht="29.1">
+    <row r="843" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A843" t="s">
         <v>3370</v>
       </c>
@@ -29799,7 +29809,7 @@
         <v>13721367</v>
       </c>
     </row>
-    <row r="844" spans="1:6" ht="29.1">
+    <row r="844" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A844" t="s">
         <v>3373</v>
       </c>
@@ -29819,7 +29829,7 @@
         <v>13848118</v>
       </c>
     </row>
-    <row r="845" spans="1:6" ht="43.7">
+    <row r="845" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A845" t="s">
         <v>3377</v>
       </c>
@@ -29839,7 +29849,7 @@
         <v>13859996</v>
       </c>
     </row>
-    <row r="846" spans="1:6" ht="58.35">
+    <row r="846" spans="1:6" ht="58.3" x14ac:dyDescent="0.4">
       <c r="A846" t="s">
         <v>3381</v>
       </c>
@@ -29859,7 +29869,7 @@
         <v>13899865</v>
       </c>
     </row>
-    <row r="847" spans="1:6" ht="43.7">
+    <row r="847" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A847" t="s">
         <v>3385</v>
       </c>
@@ -29879,7 +29889,7 @@
         <v>13900659</v>
       </c>
     </row>
-    <row r="848" spans="1:6" ht="29.1">
+    <row r="848" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A848" t="s">
         <v>3389</v>
       </c>
@@ -29899,7 +29909,7 @@
         <v>13957658</v>
       </c>
     </row>
-    <row r="849" spans="1:6" ht="29.1">
+    <row r="849" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A849" t="s">
         <v>3392</v>
       </c>
@@ -29919,7 +29929,7 @@
         <v>13961273</v>
       </c>
     </row>
-    <row r="850" spans="1:6">
+    <row r="850" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A850" t="s">
         <v>3396</v>
       </c>
@@ -29939,7 +29949,7 @@
         <v>13974719</v>
       </c>
     </row>
-    <row r="851" spans="1:6">
+    <row r="851" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A851" t="s">
         <v>3400</v>
       </c>
@@ -29959,7 +29969,7 @@
         <v>13978709</v>
       </c>
     </row>
-    <row r="852" spans="1:6" ht="29.1">
+    <row r="852" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A852" t="s">
         <v>3404</v>
       </c>
@@ -29979,7 +29989,7 @@
         <v>14058681</v>
       </c>
     </row>
-    <row r="853" spans="1:6" ht="29.1">
+    <row r="853" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A853" t="s">
         <v>3408</v>
       </c>
@@ -29999,7 +30009,7 @@
         <v>14065953</v>
       </c>
     </row>
-    <row r="854" spans="1:6" ht="29.1">
+    <row r="854" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A854" t="s">
         <v>3412</v>
       </c>
@@ -30019,7 +30029,7 @@
         <v>14081930</v>
       </c>
     </row>
-    <row r="855" spans="1:6" ht="29.1">
+    <row r="855" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A855" t="s">
         <v>3416</v>
       </c>
@@ -30039,7 +30049,7 @@
         <v>14175673</v>
       </c>
     </row>
-    <row r="856" spans="1:6" ht="29.1">
+    <row r="856" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A856" t="s">
         <v>3420</v>
       </c>
@@ -30059,7 +30069,7 @@
         <v>14183750</v>
       </c>
     </row>
-    <row r="857" spans="1:6" ht="29.1">
+    <row r="857" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A857" t="s">
         <v>3424</v>
       </c>
@@ -30079,7 +30089,7 @@
         <v>14190704</v>
       </c>
     </row>
-    <row r="858" spans="1:6" ht="29.1">
+    <row r="858" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A858" t="s">
         <v>3428</v>
       </c>
@@ -30099,7 +30109,7 @@
         <v>14267053</v>
       </c>
     </row>
-    <row r="859" spans="1:6" ht="29.1">
+    <row r="859" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A859" t="s">
         <v>3432</v>
       </c>
@@ -30119,7 +30129,7 @@
         <v>14289752</v>
       </c>
     </row>
-    <row r="860" spans="1:6">
+    <row r="860" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A860" t="s">
         <v>3436</v>
       </c>
@@ -30139,7 +30149,7 @@
         <v>14310536</v>
       </c>
     </row>
-    <row r="861" spans="1:6" ht="29.1">
+    <row r="861" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A861" t="s">
         <v>3440</v>
       </c>
@@ -30159,7 +30169,7 @@
         <v>14316091</v>
       </c>
     </row>
-    <row r="862" spans="1:6" ht="43.7">
+    <row r="862" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A862" t="s">
         <v>3444</v>
       </c>
@@ -30179,7 +30189,7 @@
         <v>14319659</v>
       </c>
     </row>
-    <row r="863" spans="1:6">
+    <row r="863" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A863" t="s">
         <v>3448</v>
       </c>
@@ -30199,7 +30209,7 @@
         <v>14329832</v>
       </c>
     </row>
-    <row r="864" spans="1:6" ht="29.1">
+    <row r="864" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A864" t="s">
         <v>3452</v>
       </c>
@@ -30219,7 +30229,7 @@
         <v>14499101</v>
       </c>
     </row>
-    <row r="865" spans="1:6" ht="58.35">
+    <row r="865" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A865" t="s">
         <v>3456</v>
       </c>
@@ -30239,7 +30249,7 @@
         <v>14501964</v>
       </c>
     </row>
-    <row r="866" spans="1:6" ht="43.7">
+    <row r="866" spans="1:6" ht="43.75" x14ac:dyDescent="0.4">
       <c r="A866" t="s">
         <v>3460</v>
       </c>
@@ -30259,7 +30269,7 @@
         <v>14586534</v>
       </c>
     </row>
-    <row r="867" spans="1:6" ht="29.1">
+    <row r="867" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A867" t="s">
         <v>3464</v>
       </c>
@@ -30279,7 +30289,7 @@
         <v>14726446</v>
       </c>
     </row>
-    <row r="868" spans="1:6" ht="29.1">
+    <row r="868" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A868" t="s">
         <v>3468</v>
       </c>
@@ -30299,7 +30309,7 @@
         <v>14729055</v>
       </c>
     </row>
-    <row r="869" spans="1:6" ht="29.1">
+    <row r="869" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A869" t="s">
         <v>3472</v>
       </c>
@@ -30319,7 +30329,7 @@
         <v>14790769</v>
       </c>
     </row>
-    <row r="870" spans="1:6" ht="29.1">
+    <row r="870" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A870" t="s">
         <v>3476</v>
       </c>
@@ -30339,7 +30349,7 @@
         <v>14793197</v>
       </c>
     </row>
-    <row r="871" spans="1:6" ht="29.1">
+    <row r="871" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A871" t="s">
         <v>3480</v>
       </c>
@@ -30359,7 +30369,7 @@
         <v>14797304</v>
       </c>
     </row>
-    <row r="872" spans="1:6" ht="58.35">
+    <row r="872" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A872" t="s">
         <v>3484</v>
       </c>
@@ -30379,7 +30389,7 @@
         <v>14881329</v>
       </c>
     </row>
-    <row r="873" spans="1:6" ht="29.1">
+    <row r="873" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A873" t="s">
         <v>3488</v>
       </c>
@@ -30399,7 +30409,7 @@
         <v>14896889</v>
       </c>
     </row>
-    <row r="874" spans="1:6" ht="29.1">
+    <row r="874" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A874" t="s">
         <v>3492</v>
       </c>
@@ -30419,7 +30429,7 @@
         <v>14943303</v>
       </c>
     </row>
-    <row r="875" spans="1:6">
+    <row r="875" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A875" t="s">
         <v>3496</v>
       </c>
@@ -30439,7 +30449,7 @@
         <v>14984957</v>
       </c>
     </row>
-    <row r="876" spans="1:6" ht="29.1">
+    <row r="876" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A876" t="s">
         <v>3500</v>
       </c>
@@ -30459,7 +30469,7 @@
         <v>14993592</v>
       </c>
     </row>
-    <row r="877" spans="1:6">
+    <row r="877" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A877" t="s">
         <v>3504</v>
       </c>
@@ -30479,7 +30489,7 @@
         <v>15067996</v>
       </c>
     </row>
-    <row r="878" spans="1:6" ht="29.1">
+    <row r="878" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A878" t="s">
         <v>3508</v>
       </c>
@@ -30499,7 +30509,7 @@
         <v>15093162</v>
       </c>
     </row>
-    <row r="879" spans="1:6" ht="72.95">
+    <row r="879" spans="1:6" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A879" t="s">
         <v>3511</v>
       </c>
@@ -30519,7 +30529,7 @@
         <v>15099055</v>
       </c>
     </row>
-    <row r="880" spans="1:6" ht="29.1">
+    <row r="880" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A880" t="s">
         <v>3515</v>
       </c>
@@ -30539,7 +30549,7 @@
         <v>15114280</v>
       </c>
     </row>
-    <row r="881" spans="1:6" ht="29.1">
+    <row r="881" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A881" t="s">
         <v>3519</v>
       </c>
@@ -30559,7 +30569,7 @@
         <v>15136664</v>
       </c>
     </row>
-    <row r="882" spans="1:6" ht="58.35">
+    <row r="882" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A882" t="s">
         <v>3523</v>
       </c>
@@ -30579,7 +30589,7 @@
         <v>15139564</v>
       </c>
     </row>
-    <row r="883" spans="1:6" ht="43.7">
+    <row r="883" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A883" t="s">
         <v>3527</v>
       </c>
@@ -30599,7 +30609,7 @@
         <v>15214944</v>
       </c>
     </row>
-    <row r="884" spans="1:6">
+    <row r="884" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A884" t="s">
         <v>3531</v>
       </c>
@@ -30619,7 +30629,7 @@
         <v>15218294</v>
       </c>
     </row>
-    <row r="885" spans="1:6" ht="58.35">
+    <row r="885" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A885" t="s">
         <v>3535</v>
       </c>
@@ -30639,7 +30649,7 @@
         <v>15301374</v>
       </c>
     </row>
-    <row r="886" spans="1:6" ht="29.1">
+    <row r="886" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A886" t="s">
         <v>3539</v>
       </c>
@@ -30659,7 +30669,7 @@
         <v>15314097</v>
       </c>
     </row>
-    <row r="887" spans="1:6" ht="29.1">
+    <row r="887" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A887" t="s">
         <v>3543</v>
       </c>
@@ -30679,7 +30689,7 @@
         <v>15314575</v>
       </c>
     </row>
-    <row r="888" spans="1:6">
+    <row r="888" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A888" t="s">
         <v>3547</v>
       </c>
@@ -30699,7 +30709,7 @@
         <v>15476795</v>
       </c>
     </row>
-    <row r="889" spans="1:6" ht="43.7">
+    <row r="889" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A889" t="s">
         <v>3551</v>
       </c>
@@ -30719,7 +30729,7 @@
         <v>15542079</v>
       </c>
     </row>
-    <row r="890" spans="1:6" ht="29.1">
+    <row r="890" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A890" t="s">
         <v>3555</v>
       </c>
@@ -30739,7 +30749,7 @@
         <v>15549069</v>
       </c>
     </row>
-    <row r="891" spans="1:6" ht="29.1">
+    <row r="891" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A891" t="s">
         <v>3559</v>
       </c>
@@ -30759,7 +30769,7 @@
         <v>15623441</v>
       </c>
     </row>
-    <row r="892" spans="1:6" ht="29.1">
+    <row r="892" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A892" t="s">
         <v>3563</v>
       </c>
@@ -30779,7 +30789,7 @@
         <v>15636811</v>
       </c>
     </row>
-    <row r="893" spans="1:6">
+    <row r="893" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A893" t="s">
         <v>3567</v>
       </c>
@@ -30799,7 +30809,7 @@
         <v>15641925</v>
       </c>
     </row>
-    <row r="894" spans="1:6" ht="29.1">
+    <row r="894" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A894" t="s">
         <v>3571</v>
       </c>
@@ -30819,7 +30829,7 @@
         <v>15662020</v>
       </c>
     </row>
-    <row r="895" spans="1:6" ht="29.1">
+    <row r="895" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A895" t="s">
         <v>3575</v>
       </c>
@@ -30839,7 +30849,7 @@
         <v>15665874</v>
       </c>
     </row>
-    <row r="896" spans="1:6" ht="29.1">
+    <row r="896" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A896" t="s">
         <v>3579</v>
       </c>
@@ -30859,7 +30869,7 @@
         <v>15702119</v>
       </c>
     </row>
-    <row r="897" spans="1:6" ht="29.1">
+    <row r="897" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A897" t="s">
         <v>3583</v>
       </c>
@@ -30879,7 +30889,7 @@
         <v>15715578</v>
       </c>
     </row>
-    <row r="898" spans="1:6" ht="29.1">
+    <row r="898" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A898" t="s">
         <v>3586</v>
       </c>
@@ -30899,7 +30909,7 @@
         <v>15903231</v>
       </c>
     </row>
-    <row r="899" spans="1:6" ht="43.7">
+    <row r="899" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A899" t="s">
         <v>3590</v>
       </c>
@@ -30919,7 +30929,7 @@
         <v>15927852</v>
       </c>
     </row>
-    <row r="900" spans="1:6">
+    <row r="900" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A900" t="s">
         <v>3594</v>
       </c>
@@ -30939,7 +30949,7 @@
         <v>15980759</v>
       </c>
     </row>
-    <row r="901" spans="1:6" ht="29.1">
+    <row r="901" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A901" t="s">
         <v>3598</v>
       </c>
@@ -30959,7 +30969,7 @@
         <v>15983771</v>
       </c>
     </row>
-    <row r="902" spans="1:6" ht="29.1">
+    <row r="902" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A902" t="s">
         <v>3602</v>
       </c>
@@ -30979,7 +30989,7 @@
         <v>16005129</v>
       </c>
     </row>
-    <row r="903" spans="1:6" ht="29.1">
+    <row r="903" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A903" t="s">
         <v>3606</v>
       </c>
@@ -30999,7 +31009,7 @@
         <v>16023017</v>
       </c>
     </row>
-    <row r="904" spans="1:6">
+    <row r="904" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A904" t="s">
         <v>3610</v>
       </c>
@@ -31019,7 +31029,7 @@
         <v>16027318</v>
       </c>
     </row>
-    <row r="905" spans="1:6" ht="29.1">
+    <row r="905" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A905" t="s">
         <v>3613</v>
       </c>
@@ -31039,7 +31049,7 @@
         <v>16090815</v>
       </c>
     </row>
-    <row r="906" spans="1:6" ht="29.1">
+    <row r="906" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A906" t="s">
         <v>3617</v>
       </c>
@@ -31059,7 +31069,7 @@
         <v>16100189</v>
       </c>
     </row>
-    <row r="907" spans="1:6" ht="29.1">
+    <row r="907" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A907" t="s">
         <v>3621</v>
       </c>
@@ -31079,7 +31089,7 @@
         <v>16104983</v>
       </c>
     </row>
-    <row r="908" spans="1:6" ht="29.1">
+    <row r="908" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A908" t="s">
         <v>3625</v>
       </c>
@@ -31099,7 +31109,7 @@
         <v>16226374</v>
       </c>
     </row>
-    <row r="909" spans="1:6">
+    <row r="909" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A909" t="s">
         <v>3629</v>
       </c>
@@ -31119,7 +31129,7 @@
         <v>16293278</v>
       </c>
     </row>
-    <row r="910" spans="1:6" ht="43.7">
+    <row r="910" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A910" t="s">
         <v>3632</v>
       </c>
@@ -31139,7 +31149,7 @@
         <v>16327816</v>
       </c>
     </row>
-    <row r="911" spans="1:6">
+    <row r="911" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A911" t="s">
         <v>3636</v>
       </c>
@@ -31159,7 +31169,7 @@
         <v>16335646</v>
       </c>
     </row>
-    <row r="912" spans="1:6" ht="29.1">
+    <row r="912" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A912" t="s">
         <v>3640</v>
       </c>
@@ -31179,7 +31189,7 @@
         <v>16420265</v>
       </c>
     </row>
-    <row r="913" spans="1:6">
+    <row r="913" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A913" t="s">
         <v>3644</v>
       </c>
@@ -31199,7 +31209,7 @@
         <v>16619074</v>
       </c>
     </row>
-    <row r="914" spans="1:6">
+    <row r="914" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A914" t="s">
         <v>3648</v>
       </c>
@@ -31219,7 +31229,7 @@
         <v>16622878</v>
       </c>
     </row>
-    <row r="915" spans="1:6" ht="29.1">
+    <row r="915" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A915" t="s">
         <v>3652</v>
       </c>
@@ -31239,7 +31249,7 @@
         <v>16634936</v>
       </c>
     </row>
-    <row r="916" spans="1:6">
+    <row r="916" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A916" t="s">
         <v>3656</v>
       </c>
@@ -31259,7 +31269,7 @@
         <v>16645903</v>
       </c>
     </row>
-    <row r="917" spans="1:6" ht="43.7">
+    <row r="917" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A917" t="s">
         <v>3660</v>
       </c>
@@ -31279,7 +31289,7 @@
         <v>16648208</v>
       </c>
     </row>
-    <row r="918" spans="1:6">
+    <row r="918" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A918" t="s">
         <v>3664</v>
       </c>
@@ -31299,7 +31309,7 @@
         <v>16655269</v>
       </c>
     </row>
-    <row r="919" spans="1:6" ht="29.1">
+    <row r="919" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A919" t="s">
         <v>3668</v>
       </c>
@@ -31319,7 +31329,7 @@
         <v>16706748</v>
       </c>
     </row>
-    <row r="920" spans="1:6" ht="29.1">
+    <row r="920" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A920" t="s">
         <v>3672</v>
       </c>
@@ -31339,7 +31349,7 @@
         <v>16749780</v>
       </c>
     </row>
-    <row r="921" spans="1:6" ht="29.1">
+    <row r="921" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A921" t="s">
         <v>3676</v>
       </c>
@@ -31359,7 +31369,7 @@
         <v>16762683</v>
       </c>
     </row>
-    <row r="922" spans="1:6" ht="29.1">
+    <row r="922" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A922" t="s">
         <v>3680</v>
       </c>
@@ -31379,7 +31389,7 @@
         <v>16763100</v>
       </c>
     </row>
-    <row r="923" spans="1:6">
+    <row r="923" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A923" t="s">
         <v>3684</v>
       </c>
@@ -31399,7 +31409,7 @@
         <v>16822542</v>
       </c>
     </row>
-    <row r="924" spans="1:6">
+    <row r="924" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A924" t="s">
         <v>3688</v>
       </c>
@@ -31419,7 +31429,7 @@
         <v>16841587</v>
       </c>
     </row>
-    <row r="925" spans="1:6">
+    <row r="925" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A925" t="s">
         <v>3692</v>
       </c>
@@ -31439,7 +31449,7 @@
         <v>16872380</v>
       </c>
     </row>
-    <row r="926" spans="1:6" ht="29.1">
+    <row r="926" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A926" t="s">
         <v>3696</v>
       </c>
@@ -31459,7 +31469,7 @@
         <v>16965632</v>
       </c>
     </row>
-    <row r="927" spans="1:6" ht="58.35">
+    <row r="927" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A927" t="s">
         <v>3700</v>
       </c>
@@ -31479,7 +31489,7 @@
         <v>17034456</v>
       </c>
     </row>
-    <row r="928" spans="1:6">
+    <row r="928" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A928" t="s">
         <v>3704</v>
       </c>
@@ -31499,7 +31509,7 @@
         <v>17091593</v>
       </c>
     </row>
-    <row r="929" spans="1:6" ht="29.1">
+    <row r="929" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A929" t="s">
         <v>3708</v>
       </c>
@@ -31519,7 +31529,7 @@
         <v>17146725</v>
       </c>
     </row>
-    <row r="930" spans="1:6" ht="29.1">
+    <row r="930" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A930" t="s">
         <v>3711</v>
       </c>
@@ -31539,7 +31549,7 @@
         <v>17154888</v>
       </c>
     </row>
-    <row r="931" spans="1:6" ht="43.7">
+    <row r="931" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A931" t="s">
         <v>3714</v>
       </c>
@@ -31559,7 +31569,7 @@
         <v>17158318</v>
       </c>
     </row>
-    <row r="932" spans="1:6" ht="29.1">
+    <row r="932" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A932" t="s">
         <v>3718</v>
       </c>
@@ -31579,7 +31589,7 @@
         <v>17248718</v>
       </c>
     </row>
-    <row r="933" spans="1:6">
+    <row r="933" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A933" t="s">
         <v>3722</v>
       </c>
@@ -31599,7 +31609,7 @@
         <v>17304929</v>
       </c>
     </row>
-    <row r="934" spans="1:6">
+    <row r="934" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A934" t="s">
         <v>3726</v>
       </c>
@@ -31619,7 +31629,7 @@
         <v>17342214</v>
       </c>
     </row>
-    <row r="935" spans="1:6" ht="29.1">
+    <row r="935" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A935" t="s">
         <v>3730</v>
       </c>
@@ -31639,7 +31649,7 @@
         <v>17351559</v>
       </c>
     </row>
-    <row r="936" spans="1:6" ht="43.7">
+    <row r="936" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A936" t="s">
         <v>3733</v>
       </c>
@@ -31659,7 +31669,7 @@
         <v>17352602</v>
       </c>
     </row>
-    <row r="937" spans="1:6" ht="29.1">
+    <row r="937" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A937" t="s">
         <v>3737</v>
       </c>
@@ -31679,7 +31689,7 @@
         <v>17410240</v>
       </c>
     </row>
-    <row r="938" spans="1:6" ht="29.1">
+    <row r="938" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A938" t="s">
         <v>3741</v>
       </c>
@@ -31699,7 +31709,7 @@
         <v>17499728</v>
       </c>
     </row>
-    <row r="939" spans="1:6" ht="43.7">
+    <row r="939" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A939" t="s">
         <v>3745</v>
       </c>
@@ -31719,7 +31729,7 @@
         <v>17503192</v>
       </c>
     </row>
-    <row r="940" spans="1:6" ht="43.7">
+    <row r="940" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A940" t="s">
         <v>3749</v>
       </c>
@@ -31739,7 +31749,7 @@
         <v>17506594</v>
       </c>
     </row>
-    <row r="941" spans="1:6" ht="29.1">
+    <row r="941" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A941" t="s">
         <v>3753</v>
       </c>
@@ -31759,7 +31769,7 @@
         <v>17670922</v>
       </c>
     </row>
-    <row r="942" spans="1:6" ht="43.7">
+    <row r="942" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A942" t="s">
         <v>3757</v>
       </c>
@@ -31779,7 +31789,7 @@
         <v>17731098</v>
       </c>
     </row>
-    <row r="943" spans="1:6" ht="29.1">
+    <row r="943" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A943" t="s">
         <v>3761</v>
       </c>
@@ -31799,7 +31809,7 @@
         <v>17749808</v>
       </c>
     </row>
-    <row r="944" spans="1:6">
+    <row r="944" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A944" t="s">
         <v>3765</v>
       </c>
@@ -31819,7 +31829,7 @@
         <v>17752270</v>
       </c>
     </row>
-    <row r="945" spans="1:6" ht="29.1">
+    <row r="945" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A945" t="s">
         <v>3769</v>
       </c>
@@ -31839,7 +31849,7 @@
         <v>17758261</v>
       </c>
     </row>
-    <row r="946" spans="1:6">
+    <row r="946" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A946" t="s">
         <v>3773</v>
       </c>
@@ -31859,7 +31869,7 @@
         <v>17789854</v>
       </c>
     </row>
-    <row r="947" spans="1:6">
+    <row r="947" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A947" t="s">
         <v>3777</v>
       </c>
@@ -31879,7 +31889,7 @@
         <v>17804502</v>
       </c>
     </row>
-    <row r="948" spans="1:6" ht="43.7">
+    <row r="948" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A948" t="s">
         <v>3781</v>
       </c>
@@ -31899,7 +31909,7 @@
         <v>17817066</v>
       </c>
     </row>
-    <row r="949" spans="1:6" ht="29.1">
+    <row r="949" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A949" t="s">
         <v>3785</v>
       </c>
@@ -31919,7 +31929,7 @@
         <v>18057819</v>
       </c>
     </row>
-    <row r="950" spans="1:6" ht="29.1">
+    <row r="950" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A950" t="s">
         <v>3789</v>
       </c>
@@ -31939,7 +31949,7 @@
         <v>18123672</v>
       </c>
     </row>
-    <row r="951" spans="1:6" ht="72.95">
+    <row r="951" spans="1:6" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
       <c r="A951" t="s">
         <v>3793</v>
       </c>
@@ -31959,7 +31969,7 @@
         <v>18323924</v>
       </c>
     </row>
-    <row r="952" spans="1:6">
+    <row r="952" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A952" t="s">
         <v>3797</v>
       </c>
@@ -31979,7 +31989,7 @@
         <v>18361877</v>
       </c>
     </row>
-    <row r="953" spans="1:6" ht="58.35">
+    <row r="953" spans="1:6" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
       <c r="A953" t="s">
         <v>3801</v>
       </c>
@@ -31999,7 +32009,7 @@
         <v>18379186</v>
       </c>
     </row>
-    <row r="954" spans="1:6" ht="29.1">
+    <row r="954" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A954" t="s">
         <v>3805</v>
       </c>
@@ -32019,7 +32029,7 @@
         <v>18446208</v>
       </c>
     </row>
-    <row r="955" spans="1:6" ht="29.1">
+    <row r="955" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A955" t="s">
         <v>3809</v>
       </c>
@@ -32039,7 +32049,7 @@
         <v>18512210</v>
       </c>
     </row>
-    <row r="956" spans="1:6" ht="29.1">
+    <row r="956" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A956" t="s">
         <v>3813</v>
       </c>
@@ -32059,7 +32069,7 @@
         <v>18532464</v>
       </c>
     </row>
-    <row r="957" spans="1:6" ht="43.7">
+    <row r="957" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A957" t="s">
         <v>3817</v>
       </c>
@@ -32079,7 +32089,7 @@
         <v>18532680</v>
       </c>
     </row>
-    <row r="958" spans="1:6">
+    <row r="958" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A958" t="s">
         <v>3821</v>
       </c>
@@ -32099,7 +32109,7 @@
         <v>18536648</v>
       </c>
     </row>
-    <row r="959" spans="1:6" ht="43.7">
+    <row r="959" spans="1:6" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
       <c r="A959" t="s">
         <v>3825</v>
       </c>
@@ -32119,7 +32129,7 @@
         <v>18650503</v>
       </c>
     </row>
-    <row r="960" spans="1:6" ht="29.1">
+    <row r="960" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A960" t="s">
         <v>3829</v>
       </c>
@@ -32139,7 +32149,7 @@
         <v>18703421</v>
       </c>
     </row>
-    <row r="961" spans="1:6" ht="29.1">
+    <row r="961" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A961" t="s">
         <v>3833</v>
       </c>
@@ -32159,7 +32169,7 @@
         <v>18744960</v>
       </c>
     </row>
-    <row r="962" spans="1:6">
+    <row r="962" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A962" t="s">
         <v>3837</v>
       </c>
@@ -32179,7 +32189,7 @@
         <v>18784564</v>
       </c>
     </row>
-    <row r="963" spans="1:6">
+    <row r="963" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A963" t="s">
         <v>3841</v>
       </c>
@@ -32199,7 +32209,7 @@
         <v>18792578</v>
       </c>
     </row>
-    <row r="964" spans="1:6">
+    <row r="964" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A964" t="s">
         <v>3845</v>
       </c>
@@ -32219,7 +32229,7 @@
         <v>19275668</v>
       </c>
     </row>
-    <row r="965" spans="1:6">
+    <row r="965" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A965" t="s">
         <v>3848</v>
       </c>
@@ -32239,7 +32249,7 @@
         <v>19307542</v>
       </c>
     </row>
-    <row r="966" spans="1:6">
+    <row r="966" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A966" t="s">
         <v>3851</v>
       </c>
@@ -32259,7 +32269,7 @@
         <v>19333249</v>
       </c>
     </row>
-    <row r="967" spans="1:6">
+    <row r="967" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A967" t="s">
         <v>3855</v>
       </c>
@@ -32279,7 +32289,7 @@
         <v>19445963</v>
       </c>
     </row>
-    <row r="968" spans="1:6">
+    <row r="968" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A968" t="s">
         <v>3859</v>
       </c>
@@ -32299,7 +32309,7 @@
         <v>19466662</v>
       </c>
     </row>
-    <row r="969" spans="1:6">
+    <row r="969" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A969" t="s">
         <v>3862</v>
       </c>
@@ -32319,7 +32329,7 @@
         <v>19479053</v>
       </c>
     </row>
-    <row r="970" spans="1:6">
+    <row r="970" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A970" t="s">
         <v>3866</v>
       </c>
@@ -32339,7 +32349,7 @@
         <v>19531001</v>
       </c>
     </row>
-    <row r="971" spans="1:6">
+    <row r="971" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A971" t="s">
         <v>3870</v>
       </c>
@@ -32359,7 +32369,7 @@
         <v>19531616</v>
       </c>
     </row>
-    <row r="972" spans="1:6" ht="29.1">
+    <row r="972" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A972" t="s">
         <v>3874</v>
       </c>
@@ -32379,7 +32389,7 @@
         <v>19622857</v>
       </c>
     </row>
-    <row r="973" spans="1:6">
+    <row r="973" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A973" t="s">
         <v>3878</v>
       </c>
@@ -32399,7 +32409,7 @@
         <v>19646712</v>
       </c>
     </row>
-    <row r="974" spans="1:6">
+    <row r="974" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A974" t="s">
         <v>3882</v>
       </c>
@@ -32419,7 +32429,7 @@
         <v>19704758</v>
       </c>
     </row>
-    <row r="975" spans="1:6">
+    <row r="975" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A975" t="s">
         <v>3885</v>
       </c>
@@ -32439,7 +32449,7 @@
         <v>19715957</v>
       </c>
     </row>
-    <row r="976" spans="1:6">
+    <row r="976" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A976" t="s">
         <v>3889</v>
       </c>
@@ -32459,7 +32469,7 @@
         <v>19794966</v>
       </c>
     </row>
-    <row r="977" spans="1:6">
+    <row r="977" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A977" t="s">
         <v>3892</v>
       </c>
@@ -32479,7 +32489,7 @@
         <v>19795436</v>
       </c>
     </row>
-    <row r="978" spans="1:6">
+    <row r="978" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A978" t="s">
         <v>3896</v>
       </c>
@@ -32499,7 +32509,7 @@
         <v>19836633</v>
       </c>
     </row>
-    <row r="979" spans="1:6" ht="29.1">
+    <row r="979" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A979" t="s">
         <v>3900</v>
       </c>
@@ -32519,7 +32529,7 @@
         <v>19854995</v>
       </c>
     </row>
-    <row r="980" spans="1:6">
+    <row r="980" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A980" t="s">
         <v>3904</v>
       </c>
@@ -32539,7 +32549,7 @@
         <v>19890576</v>
       </c>
     </row>
-    <row r="981" spans="1:6">
+    <row r="981" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A981" t="s">
         <v>3908</v>
       </c>
@@ -32559,7 +32569,7 @@
         <v>20184699</v>
       </c>
     </row>
-    <row r="982" spans="1:6">
+    <row r="982" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A982" t="s">
         <v>3912</v>
       </c>
@@ -32579,7 +32589,7 @@
         <v>20216650</v>
       </c>
     </row>
-    <row r="983" spans="1:6">
+    <row r="983" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A983" t="s">
         <v>3916</v>
       </c>
@@ -32599,7 +32609,7 @@
         <v>20270862</v>
       </c>
     </row>
-    <row r="984" spans="1:6">
+    <row r="984" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A984" t="s">
         <v>3920</v>
       </c>
@@ -32619,7 +32629,7 @@
         <v>20295350</v>
       </c>
     </row>
-    <row r="985" spans="1:6" ht="29.1">
+    <row r="985" spans="1:6" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A985" t="s">
         <v>3924</v>
       </c>
@@ -32639,7 +32649,7 @@
         <v>20471087</v>
       </c>
     </row>
-    <row r="986" spans="1:6">
+    <row r="986" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A986" t="s">
         <v>3928</v>
       </c>
@@ -32659,7 +32669,7 @@
         <v>20492301</v>
       </c>
     </row>
-    <row r="987" spans="1:6">
+    <row r="987" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A987" t="s">
         <v>3932</v>
       </c>
@@ -32679,7 +32689,7 @@
         <v>20517126</v>
       </c>
     </row>
-    <row r="988" spans="1:6">
+    <row r="988" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A988" t="s">
         <v>3935</v>
       </c>
@@ -32699,7 +32709,7 @@
         <v>20521290</v>
       </c>
     </row>
-    <row r="989" spans="1:6">
+    <row r="989" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A989" t="s">
         <v>3939</v>
       </c>
@@ -32719,7 +32729,7 @@
         <v>20548954</v>
       </c>
     </row>
-    <row r="990" spans="1:6">
+    <row r="990" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A990" t="s">
         <v>3943</v>
       </c>
@@ -32739,7 +32749,7 @@
         <v>20586947</v>
       </c>
     </row>
-    <row r="991" spans="1:6">
+    <row r="991" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A991" t="s">
         <v>3947</v>
       </c>
@@ -32759,7 +32769,7 @@
         <v>20644674</v>
       </c>
     </row>
-    <row r="992" spans="1:6" ht="29.1">
+    <row r="992" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A992" t="s">
         <v>3951</v>
       </c>
@@ -32779,7 +32789,7 @@
         <v>20848759</v>
       </c>
     </row>
-    <row r="993" spans="1:6">
+    <row r="993" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A993" t="s">
         <v>3955</v>
       </c>
@@ -32799,7 +32809,7 @@
         <v>20953232</v>
       </c>
     </row>
-    <row r="994" spans="1:6">
+    <row r="994" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A994" t="s">
         <v>3958</v>
       </c>
@@ -32819,7 +32829,7 @@
         <v>21074845</v>
       </c>
     </row>
-    <row r="995" spans="1:6" ht="29.1">
+    <row r="995" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A995" t="s">
         <v>3962</v>
       </c>
@@ -32839,7 +32849,7 @@
         <v>21086555</v>
       </c>
     </row>
-    <row r="996" spans="1:6">
+    <row r="996" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A996" t="s">
         <v>3966</v>
       </c>
@@ -32859,7 +32869,7 @@
         <v>21117602</v>
       </c>
     </row>
-    <row r="997" spans="1:6" ht="29.1">
+    <row r="997" spans="1:6" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A997" t="s">
         <v>3970</v>
       </c>
@@ -32879,7 +32889,7 @@
         <v>21138145</v>
       </c>
     </row>
-    <row r="998" spans="1:6">
+    <row r="998" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A998" t="s">
         <v>3974</v>
       </c>
@@ -32899,7 +32909,7 @@
         <v>21178354</v>
       </c>
     </row>
-    <row r="999" spans="1:6">
+    <row r="999" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A999" t="s">
         <v>3978</v>
       </c>
@@ -32919,7 +32929,7 @@
         <v>21253362</v>
       </c>
     </row>
-    <row r="1000" spans="1:6">
+    <row r="1000" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A1000" t="s">
         <v>3982</v>
       </c>
@@ -32939,7 +32949,7 @@
         <v>21321966</v>
       </c>
     </row>
-    <row r="1001" spans="1:6">
+    <row r="1001" spans="1:6" hidden="1" x14ac:dyDescent="0.4">
       <c r="A1001" t="s">
         <v>3985</v>
       </c>
@@ -32972,5 +32982,9 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1F7A4E2-8D69-4055-802A-BEBDCB785511}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1F7A4E2-8D69-4055-802A-BEBDCB785511}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/DataMashup"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>